--- a/1.xlsx
+++ b/1.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="40">
   <si>
     <t>模块</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -183,7 +183,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>26.4.4</t>
+    <t>26.4.6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -263,7 +267,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -289,9 +293,6 @@
     <xf numFmtId="58" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -304,19 +305,19 @@
     <xf numFmtId="9" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -631,33 +632,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A2" s="14"/>
-      <c r="B2" s="14"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
+      <c r="A2" s="16"/>
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A3" s="14"/>
-      <c r="B3" s="14"/>
-      <c r="C3" s="14"/>
-      <c r="D3" s="14"/>
-      <c r="E3" s="14"/>
-      <c r="F3" s="14"/>
-      <c r="G3" s="14"/>
+      <c r="A3" s="16"/>
+      <c r="B3" s="16"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="16"/>
+      <c r="G3" s="16"/>
     </row>
     <row r="4" spans="1:7" s="2" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="4" t="s">
@@ -684,19 +685,19 @@
       <c r="A5" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="10" t="s">
+      <c r="B5" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="C5" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="D5" s="11" t="s">
+      <c r="D5" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="E5" s="13">
+      <c r="E5" s="12">
         <v>1</v>
       </c>
-      <c r="F5" s="10" t="s">
+      <c r="F5" s="9" t="s">
         <v>23</v>
       </c>
       <c r="G5" s="7"/>
@@ -709,25 +710,25 @@
     </row>
     <row r="8" spans="1:7" ht="27" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="9" spans="1:7" ht="38.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="14" t="s">
+      <c r="A9" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="B9" s="16" t="s">
+      <c r="B9" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="C9" s="16" t="s">
+      <c r="C9" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="D9" s="16" t="s">
+      <c r="D9" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="E9" s="17">
+      <c r="E9" s="14">
         <v>1</v>
       </c>
-      <c r="F9" s="18"/>
+      <c r="F9" s="15"/>
     </row>
     <row r="10" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="14"/>
+      <c r="A10" s="16"/>
       <c r="B10" s="3" t="s">
         <v>29</v>
       </c>
@@ -741,25 +742,25 @@
       <c r="A11" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B11" s="10" t="s">
+      <c r="B11" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="C11" s="11" t="s">
+      <c r="C11" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="D11" s="12" t="s">
+      <c r="D11" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="E11" s="13">
+      <c r="E11" s="12">
         <v>1</v>
       </c>
-      <c r="F11" s="10" t="s">
+      <c r="F11" s="9" t="s">
         <v>22</v>
       </c>
       <c r="G11" s="7"/>
     </row>
     <row r="12" spans="1:7" s="2" customFormat="1" ht="47.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A12" s="15" t="s">
+      <c r="A12" s="17" t="s">
         <v>10</v>
       </c>
       <c r="B12" s="6" t="s">
@@ -772,24 +773,24 @@
       <c r="G12" s="7"/>
     </row>
     <row r="13" spans="1:7" s="2" customFormat="1" ht="47.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A13" s="15"/>
-      <c r="B13" s="10" t="s">
+      <c r="A13" s="17"/>
+      <c r="B13" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="C13" s="10" t="s">
+      <c r="C13" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="D13" s="10" t="s">
+      <c r="D13" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="E13" s="13">
+      <c r="E13" s="12">
         <v>1</v>
       </c>
-      <c r="F13" s="10"/>
+      <c r="F13" s="9"/>
       <c r="G13" s="7"/>
     </row>
     <row r="14" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A14" s="15" t="s">
+      <c r="A14" s="17" t="s">
         <v>8</v>
       </c>
       <c r="B14" s="6" t="s">
@@ -802,26 +803,26 @@
       <c r="G14" s="7"/>
     </row>
     <row r="15" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A15" s="15"/>
-      <c r="B15" s="10" t="s">
+      <c r="A15" s="17"/>
+      <c r="B15" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="C15" s="10" t="s">
+      <c r="C15" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="D15" s="12" t="s">
+      <c r="D15" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="E15" s="13">
+      <c r="E15" s="12">
         <v>1</v>
       </c>
-      <c r="F15" s="10" t="s">
+      <c r="F15" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G15" s="7"/>
     </row>
     <row r="16" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A16" s="15"/>
+      <c r="A16" s="17"/>
       <c r="B16" s="6" t="s">
         <v>34</v>
       </c>
@@ -836,37 +837,41 @@
       <c r="G16" s="7"/>
     </row>
     <row r="17" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A17" s="15"/>
-      <c r="B17" s="10" t="s">
+      <c r="A17" s="17"/>
+      <c r="B17" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="C17" s="10" t="s">
+      <c r="C17" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="D17" s="10" t="s">
+      <c r="D17" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="E17" s="13">
+      <c r="E17" s="12">
         <v>1</v>
       </c>
-      <c r="F17" s="10" t="s">
+      <c r="F17" s="9" t="s">
         <v>23</v>
       </c>
       <c r="G17" s="7"/>
     </row>
     <row r="18" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A18" s="15"/>
-      <c r="B18" s="6" t="s">
+      <c r="A18" s="17"/>
+      <c r="B18" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="C18" s="6" t="s">
+      <c r="C18" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="D18" s="6" t="s">
+      <c r="D18" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="E18" s="9"/>
-      <c r="F18" s="6"/>
+      <c r="E18" s="12">
+        <v>1</v>
+      </c>
+      <c r="F18" s="9" t="s">
+        <v>39</v>
+      </c>
       <c r="G18" s="7"/>
     </row>
     <row r="19" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.15">

--- a/1.xlsx
+++ b/1.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="44">
   <si>
     <t>模块</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -188,6 +188,22 @@
   </si>
   <si>
     <t>-</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>提示管理功能</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>拆分成传统弹窗和Tooltips。侧边属性. 传统弹窗同时只能存在一个</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>角色属性预览可用, 后续轻提示同样可用, Tooltips同时只能存在一个</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>26.4.7</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -267,7 +283,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -312,6 +328,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -619,7 +638,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G44"/>
+  <dimension ref="A1:G45"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="22.625" style="3" customWidth="1"/>
@@ -627,38 +646,38 @@
     <col min="3" max="3" width="32.5" style="3" customWidth="1"/>
     <col min="4" max="4" width="24.125" style="3" customWidth="1"/>
     <col min="5" max="5" width="17.25" style="3" customWidth="1"/>
-    <col min="6" max="6" width="20.25" customWidth="1"/>
+    <col min="6" max="6" width="53.625" customWidth="1"/>
     <col min="7" max="7" width="17.125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A2" s="16"/>
-      <c r="B2" s="16"/>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="16"/>
-      <c r="G2" s="16"/>
+      <c r="A2" s="17"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A3" s="16"/>
-      <c r="B3" s="16"/>
-      <c r="C3" s="16"/>
-      <c r="D3" s="16"/>
-      <c r="E3" s="16"/>
-      <c r="F3" s="16"/>
-      <c r="G3" s="16"/>
+      <c r="A3" s="17"/>
+      <c r="B3" s="17"/>
+      <c r="C3" s="17"/>
+      <c r="D3" s="17"/>
+      <c r="E3" s="17"/>
+      <c r="F3" s="17"/>
+      <c r="G3" s="17"/>
     </row>
     <row r="4" spans="1:7" s="2" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="4" t="s">
@@ -710,7 +729,7 @@
     </row>
     <row r="8" spans="1:7" ht="27" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="9" spans="1:7" ht="38.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="16" t="s">
+      <c r="A9" s="17" t="s">
         <v>27</v>
       </c>
       <c r="B9" s="13" t="s">
@@ -728,7 +747,7 @@
       <c r="F9" s="15"/>
     </row>
     <row r="10" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="16"/>
+      <c r="A10" s="17"/>
       <c r="B10" s="3" t="s">
         <v>29</v>
       </c>
@@ -760,7 +779,7 @@
       <c r="G11" s="7"/>
     </row>
     <row r="12" spans="1:7" s="2" customFormat="1" ht="47.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A12" s="17" t="s">
+      <c r="A12" s="18" t="s">
         <v>10</v>
       </c>
       <c r="B12" s="6" t="s">
@@ -773,7 +792,7 @@
       <c r="G12" s="7"/>
     </row>
     <row r="13" spans="1:7" s="2" customFormat="1" ht="47.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A13" s="17"/>
+      <c r="A13" s="18"/>
       <c r="B13" s="9" t="s">
         <v>30</v>
       </c>
@@ -790,7 +809,7 @@
       <c r="G13" s="7"/>
     </row>
     <row r="14" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A14" s="17" t="s">
+      <c r="A14" s="18" t="s">
         <v>8</v>
       </c>
       <c r="B14" s="6" t="s">
@@ -803,7 +822,7 @@
       <c r="G14" s="7"/>
     </row>
     <row r="15" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A15" s="17"/>
+      <c r="A15" s="18"/>
       <c r="B15" s="9" t="s">
         <v>25</v>
       </c>
@@ -821,8 +840,8 @@
       </c>
       <c r="G15" s="7"/>
     </row>
-    <row r="16" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A16" s="17"/>
+    <row r="16" spans="1:7" s="2" customFormat="1" ht="48.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A16" s="18"/>
       <c r="B16" s="6" t="s">
         <v>34</v>
       </c>
@@ -833,60 +852,70 @@
         <v>37</v>
       </c>
       <c r="E16" s="6"/>
-      <c r="F16" s="6"/>
+      <c r="F16" s="6" t="s">
+        <v>41</v>
+      </c>
       <c r="G16" s="7"/>
     </row>
-    <row r="17" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A17" s="17"/>
-      <c r="B17" s="9" t="s">
+    <row r="17" spans="1:7" s="2" customFormat="1" ht="48.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A17" s="18"/>
+      <c r="B17" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="C17" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="D17" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="E17" s="16"/>
+      <c r="F17" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="G17" s="7"/>
+    </row>
+    <row r="18" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A18" s="18"/>
+      <c r="B18" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="C17" s="9" t="s">
+      <c r="C18" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="D17" s="9" t="s">
+      <c r="D18" s="9" t="s">
         <v>21</v>
-      </c>
-      <c r="E17" s="12">
-        <v>1</v>
-      </c>
-      <c r="F17" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="G17" s="7"/>
-    </row>
-    <row r="18" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A18" s="17"/>
-      <c r="B18" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C18" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="D18" s="9" t="s">
-        <v>38</v>
       </c>
       <c r="E18" s="12">
         <v>1</v>
       </c>
       <c r="F18" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="G18" s="7"/>
+    </row>
+    <row r="19" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A19" s="18"/>
+      <c r="B19" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="E19" s="12">
+        <v>1</v>
+      </c>
+      <c r="F19" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="G18" s="7"/>
-    </row>
-    <row r="19" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A19" s="6" t="s">
+      <c r="G19" s="7"/>
+    </row>
+    <row r="20" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A20" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B19" s="6"/>
-      <c r="C19" s="6"/>
-      <c r="D19" s="6"/>
-      <c r="E19" s="6"/>
-      <c r="F19" s="6"/>
-      <c r="G19" s="7"/>
-    </row>
-    <row r="20" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A20" s="6"/>
       <c r="B20" s="6"/>
       <c r="C20" s="6"/>
       <c r="D20" s="6"/>
@@ -1075,28 +1104,37 @@
       <c r="G40" s="7"/>
     </row>
     <row r="41" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A41" s="3"/>
-      <c r="B41" s="3"/>
-      <c r="C41" s="3"/>
-      <c r="D41" s="3"/>
-      <c r="E41" s="3"/>
-      <c r="F41" s="3"/>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="F42" s="1"/>
+      <c r="A41" s="6"/>
+      <c r="B41" s="6"/>
+      <c r="C41" s="6"/>
+      <c r="D41" s="6"/>
+      <c r="E41" s="6"/>
+      <c r="F41" s="6"/>
+      <c r="G41" s="7"/>
+    </row>
+    <row r="42" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A42" s="3"/>
+      <c r="B42" s="3"/>
+      <c r="C42" s="3"/>
+      <c r="D42" s="3"/>
+      <c r="E42" s="3"/>
+      <c r="F42" s="3"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.15">
       <c r="F43" s="1"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.15">
       <c r="F44" s="1"/>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="F45" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A1:G3"/>
     <mergeCell ref="A9:A10"/>
     <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A14:A18"/>
+    <mergeCell ref="A14:A19"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/1.xlsx
+++ b/1.xlsx
@@ -199,11 +199,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>角色属性预览可用, 后续轻提示同样可用, Tooltips同时只能存在一个</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>26.4.7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>角色属性预览, 道具预览, 核心预览, 核心强化预览, 可用, 后续轻提示同样可用, Tooltips同时只能存在一个</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -863,14 +863,14 @@
         <v>40</v>
       </c>
       <c r="C17" s="16" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D17" s="16" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E17" s="16"/>
       <c r="F17" s="16" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G17" s="7"/>
     </row>

--- a/1.xlsx
+++ b/1.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="45">
   <si>
     <t>模块</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -179,10 +179,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>26.4.3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>26.4.6</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -204,6 +200,14 @@
   </si>
   <si>
     <t>角色属性预览, 道具预览, 核心预览, 核心强化预览, 可用, 后续轻提示同样可用, Tooltips同时只能存在一个</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>26.4.8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>26.4.8</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -283,7 +287,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -335,6 +339,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -842,35 +852,37 @@
     </row>
     <row r="16" spans="1:7" s="2" customFormat="1" ht="48.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="18"/>
-      <c r="B16" s="6" t="s">
+      <c r="B16" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="C16" s="6" t="s">
+      <c r="C16" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="D16" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="E16" s="6"/>
-      <c r="F16" s="6" t="s">
-        <v>41</v>
+      <c r="D16" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="E16" s="20">
+        <v>0.8</v>
+      </c>
+      <c r="F16" s="19" t="s">
+        <v>40</v>
       </c>
       <c r="G16" s="7"/>
     </row>
     <row r="17" spans="1:7" s="2" customFormat="1" ht="48.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="18"/>
       <c r="B17" s="16" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C17" s="16" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D17" s="16" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E17" s="16"/>
       <c r="F17" s="16" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G17" s="7"/>
     </row>
@@ -902,13 +914,13 @@
         <v>33</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E19" s="12">
         <v>1</v>
       </c>
       <c r="F19" s="9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G19" s="7"/>
     </row>

--- a/1.xlsx
+++ b/1.xlsx
@@ -287,7 +287,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -339,12 +339,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -852,19 +846,19 @@
     </row>
     <row r="16" spans="1:7" s="2" customFormat="1" ht="48.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="18"/>
-      <c r="B16" s="19" t="s">
+      <c r="B16" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="C16" s="19" t="s">
+      <c r="C16" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="D16" s="19" t="s">
+      <c r="D16" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="E16" s="20">
-        <v>0.8</v>
-      </c>
-      <c r="F16" s="19" t="s">
+      <c r="E16" s="12">
+        <v>1</v>
+      </c>
+      <c r="F16" s="9" t="s">
         <v>40</v>
       </c>
       <c r="G16" s="7"/>

--- a/1.xlsx
+++ b/1.xlsx
@@ -287,7 +287,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -332,9 +332,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -655,33 +652,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A2" s="17"/>
-      <c r="B2" s="17"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="17"/>
-      <c r="G2" s="17"/>
+      <c r="A2" s="16"/>
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A3" s="17"/>
-      <c r="B3" s="17"/>
-      <c r="C3" s="17"/>
-      <c r="D3" s="17"/>
-      <c r="E3" s="17"/>
-      <c r="F3" s="17"/>
-      <c r="G3" s="17"/>
+      <c r="A3" s="16"/>
+      <c r="B3" s="16"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="16"/>
+      <c r="G3" s="16"/>
     </row>
     <row r="4" spans="1:7" s="2" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="4" t="s">
@@ -733,7 +730,7 @@
     </row>
     <row r="8" spans="1:7" ht="27" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="9" spans="1:7" ht="38.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="17" t="s">
+      <c r="A9" s="16" t="s">
         <v>27</v>
       </c>
       <c r="B9" s="13" t="s">
@@ -751,7 +748,7 @@
       <c r="F9" s="15"/>
     </row>
     <row r="10" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="17"/>
+      <c r="A10" s="16"/>
       <c r="B10" s="3" t="s">
         <v>29</v>
       </c>
@@ -783,7 +780,7 @@
       <c r="G11" s="7"/>
     </row>
     <row r="12" spans="1:7" s="2" customFormat="1" ht="47.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A12" s="18" t="s">
+      <c r="A12" s="17" t="s">
         <v>10</v>
       </c>
       <c r="B12" s="6" t="s">
@@ -796,7 +793,7 @@
       <c r="G12" s="7"/>
     </row>
     <row r="13" spans="1:7" s="2" customFormat="1" ht="47.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A13" s="18"/>
+      <c r="A13" s="17"/>
       <c r="B13" s="9" t="s">
         <v>30</v>
       </c>
@@ -813,7 +810,7 @@
       <c r="G13" s="7"/>
     </row>
     <row r="14" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A14" s="18" t="s">
+      <c r="A14" s="17" t="s">
         <v>8</v>
       </c>
       <c r="B14" s="6" t="s">
@@ -826,7 +823,7 @@
       <c r="G14" s="7"/>
     </row>
     <row r="15" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A15" s="18"/>
+      <c r="A15" s="17"/>
       <c r="B15" s="9" t="s">
         <v>25</v>
       </c>
@@ -845,7 +842,7 @@
       <c r="G15" s="7"/>
     </row>
     <row r="16" spans="1:7" s="2" customFormat="1" ht="48.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A16" s="18"/>
+      <c r="A16" s="17"/>
       <c r="B16" s="9" t="s">
         <v>34</v>
       </c>
@@ -864,24 +861,26 @@
       <c r="G16" s="7"/>
     </row>
     <row r="17" spans="1:7" s="2" customFormat="1" ht="48.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A17" s="18"/>
-      <c r="B17" s="16" t="s">
+      <c r="A17" s="17"/>
+      <c r="B17" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="C17" s="16" t="s">
+      <c r="C17" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="D17" s="16" t="s">
+      <c r="D17" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="E17" s="16"/>
-      <c r="F17" s="16" t="s">
+      <c r="E17" s="12">
+        <v>1</v>
+      </c>
+      <c r="F17" s="9" t="s">
         <v>42</v>
       </c>
       <c r="G17" s="7"/>
     </row>
     <row r="18" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A18" s="18"/>
+      <c r="A18" s="17"/>
       <c r="B18" s="9" t="s">
         <v>9</v>
       </c>
@@ -900,7 +899,7 @@
       <c r="G18" s="7"/>
     </row>
     <row r="19" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A19" s="18"/>
+      <c r="A19" s="17"/>
       <c r="B19" s="9" t="s">
         <v>32</v>
       </c>

--- a/1.xlsx
+++ b/1.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="53">
   <si>
     <t>模块</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -207,7 +207,39 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>26.4.8</t>
+    <t>26.4.10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>26.4.9</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>26.4.10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>部分核心强化包图标</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>26.4.11</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>左右开弓,饱和散射,急速散射,风暴聚集;(开花,穿云重新命名)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>备战界面核心经验进度条</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>26.4.10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>弹窗功能重做不会再出现此问题</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -287,7 +319,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -336,6 +368,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -639,7 +677,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G45"/>
+  <dimension ref="A1:G46"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="22.625" style="3" customWidth="1"/>
@@ -702,7 +740,7 @@
       <c r="G4" s="5"/>
     </row>
     <row r="5" spans="1:7" s="2" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="17" t="s">
         <v>2</v>
       </c>
       <c r="B5" s="9" t="s">
@@ -722,13 +760,17 @@
       </c>
       <c r="G5" s="7"/>
     </row>
-    <row r="6" spans="1:7" ht="30.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="6" spans="1:7" ht="30.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A6" s="17"/>
+    </row>
     <row r="7" spans="1:7" ht="29.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="16" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="27" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="8" spans="1:7" ht="27" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A8" s="16"/>
+    </row>
     <row r="9" spans="1:7" ht="38.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="16" t="s">
         <v>27</v>
@@ -786,8 +828,12 @@
       <c r="B12" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C12" s="6"/>
-      <c r="D12" s="6"/>
+      <c r="C12" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>46</v>
+      </c>
       <c r="E12" s="6"/>
       <c r="F12" s="6"/>
       <c r="G12" s="7"/>
@@ -806,7 +852,9 @@
       <c r="E13" s="12">
         <v>1</v>
       </c>
-      <c r="F13" s="9"/>
+      <c r="F13" s="9" t="s">
+        <v>52</v>
+      </c>
       <c r="G13" s="7"/>
     </row>
     <row r="14" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -850,7 +898,7 @@
         <v>33</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E16" s="12">
         <v>1</v>
@@ -917,24 +965,38 @@
       </c>
       <c r="G19" s="7"/>
     </row>
-    <row r="20" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A20" s="6" t="s">
+    <row r="20" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A20" s="17"/>
+      <c r="B20" s="18" t="s">
+        <v>50</v>
+      </c>
+      <c r="C20" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="D20" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="E20" s="19"/>
+      <c r="F20" s="18"/>
+      <c r="G20" s="7"/>
+    </row>
+    <row r="21" spans="1:7" s="2" customFormat="1" ht="33.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A21" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B20" s="6"/>
-      <c r="C20" s="6"/>
-      <c r="D20" s="6"/>
-      <c r="E20" s="6"/>
-      <c r="F20" s="6"/>
-      <c r="G20" s="7"/>
-    </row>
-    <row r="21" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A21" s="6"/>
-      <c r="B21" s="6"/>
-      <c r="C21" s="6"/>
-      <c r="D21" s="6"/>
+      <c r="B21" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>48</v>
+      </c>
       <c r="E21" s="6"/>
-      <c r="F21" s="6"/>
+      <c r="F21" s="6" t="s">
+        <v>49</v>
+      </c>
       <c r="G21" s="7"/>
     </row>
     <row r="22" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.15">
@@ -1118,15 +1180,21 @@
       <c r="G41" s="7"/>
     </row>
     <row r="42" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A42" s="3"/>
-      <c r="B42" s="3"/>
-      <c r="C42" s="3"/>
-      <c r="D42" s="3"/>
-      <c r="E42" s="3"/>
-      <c r="F42" s="3"/>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="F43" s="1"/>
+      <c r="A42" s="6"/>
+      <c r="B42" s="6"/>
+      <c r="C42" s="6"/>
+      <c r="D42" s="6"/>
+      <c r="E42" s="6"/>
+      <c r="F42" s="6"/>
+      <c r="G42" s="7"/>
+    </row>
+    <row r="43" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A43" s="3"/>
+      <c r="B43" s="3"/>
+      <c r="C43" s="3"/>
+      <c r="D43" s="3"/>
+      <c r="E43" s="3"/>
+      <c r="F43" s="3"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.15">
       <c r="F44" s="1"/>
@@ -1134,12 +1202,17 @@
     <row r="45" spans="1:7" x14ac:dyDescent="0.15">
       <c r="F45" s="1"/>
     </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="F46" s="1"/>
+    </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="6">
     <mergeCell ref="A1:G3"/>
     <mergeCell ref="A9:A10"/>
     <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A14:A19"/>
+    <mergeCell ref="A14:A20"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="A7:A8"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/1.xlsx
+++ b/1.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="69">
   <si>
     <t>模块</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -223,10 +223,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>26.4.11</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>左右开弓,饱和散射,急速散射,风暴聚集;(开花,穿云重新命名)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -240,6 +236,74 @@
   </si>
   <si>
     <t>弹窗功能重做不会再出现此问题</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>待验证</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>游戏配置</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>敌人配置，波次配置数值重做</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>26.4.12</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>26.4.14</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Boss2 图片</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>26.4.13</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>26.4.13</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>26.4.14</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Boss2 设计</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>26.4.17</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AI, 配置，预制件</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>波次设计11-15</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>26.4.18</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>26.4.19</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -319,7 +383,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -364,16 +428,19 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -677,7 +744,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G46"/>
+  <dimension ref="A1:G50"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="22.625" style="3" customWidth="1"/>
@@ -690,33 +757,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A2" s="16"/>
-      <c r="B2" s="16"/>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="16"/>
-      <c r="G2" s="16"/>
+      <c r="A2" s="18"/>
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
+      <c r="G2" s="18"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A3" s="16"/>
-      <c r="B3" s="16"/>
-      <c r="C3" s="16"/>
-      <c r="D3" s="16"/>
-      <c r="E3" s="16"/>
-      <c r="F3" s="16"/>
-      <c r="G3" s="16"/>
+      <c r="A3" s="18"/>
+      <c r="B3" s="18"/>
+      <c r="C3" s="18"/>
+      <c r="D3" s="18"/>
+      <c r="E3" s="18"/>
+      <c r="F3" s="18"/>
+      <c r="G3" s="18"/>
     </row>
     <row r="4" spans="1:7" s="2" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="4" t="s">
@@ -740,7 +807,7 @@
       <c r="G4" s="5"/>
     </row>
     <row r="5" spans="1:7" s="2" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="17" t="s">
+      <c r="A5" s="19" t="s">
         <v>2</v>
       </c>
       <c r="B5" s="9" t="s">
@@ -761,18 +828,18 @@
       <c r="G5" s="7"/>
     </row>
     <row r="6" spans="1:7" ht="30.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="17"/>
+      <c r="A6" s="19"/>
     </row>
     <row r="7" spans="1:7" ht="29.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="16" t="s">
+      <c r="A7" s="18" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="27" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="16"/>
+      <c r="A8" s="18"/>
     </row>
     <row r="9" spans="1:7" ht="38.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="16" t="s">
+      <c r="A9" s="18" t="s">
         <v>27</v>
       </c>
       <c r="B9" s="13" t="s">
@@ -790,7 +857,7 @@
       <c r="F9" s="15"/>
     </row>
     <row r="10" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="16"/>
+      <c r="A10" s="18"/>
       <c r="B10" s="3" t="s">
         <v>29</v>
       </c>
@@ -822,7 +889,7 @@
       <c r="G11" s="7"/>
     </row>
     <row r="12" spans="1:7" s="2" customFormat="1" ht="47.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A12" s="17" t="s">
+      <c r="A12" s="19" t="s">
         <v>10</v>
       </c>
       <c r="B12" s="6" t="s">
@@ -834,12 +901,16 @@
       <c r="D12" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="E12" s="6"/>
-      <c r="F12" s="6"/>
+      <c r="E12" s="20">
+        <v>0.8</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>52</v>
+      </c>
       <c r="G12" s="7"/>
     </row>
     <row r="13" spans="1:7" s="2" customFormat="1" ht="47.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A13" s="17"/>
+      <c r="A13" s="19"/>
       <c r="B13" s="9" t="s">
         <v>30</v>
       </c>
@@ -853,12 +924,12 @@
         <v>1</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G13" s="7"/>
     </row>
     <row r="14" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A14" s="17" t="s">
+      <c r="A14" s="19" t="s">
         <v>8</v>
       </c>
       <c r="B14" s="6" t="s">
@@ -871,7 +942,7 @@
       <c r="G14" s="7"/>
     </row>
     <row r="15" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A15" s="17"/>
+      <c r="A15" s="19"/>
       <c r="B15" s="9" t="s">
         <v>25</v>
       </c>
@@ -890,7 +961,7 @@
       <c r="G15" s="7"/>
     </row>
     <row r="16" spans="1:7" s="2" customFormat="1" ht="48.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A16" s="17"/>
+      <c r="A16" s="19"/>
       <c r="B16" s="9" t="s">
         <v>34</v>
       </c>
@@ -909,7 +980,7 @@
       <c r="G16" s="7"/>
     </row>
     <row r="17" spans="1:7" s="2" customFormat="1" ht="48.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A17" s="17"/>
+      <c r="A17" s="19"/>
       <c r="B17" s="9" t="s">
         <v>39</v>
       </c>
@@ -928,7 +999,7 @@
       <c r="G17" s="7"/>
     </row>
     <row r="18" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A18" s="17"/>
+      <c r="A18" s="19"/>
       <c r="B18" s="9" t="s">
         <v>9</v>
       </c>
@@ -947,7 +1018,7 @@
       <c r="G18" s="7"/>
     </row>
     <row r="19" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A19" s="17"/>
+      <c r="A19" s="19"/>
       <c r="B19" s="9" t="s">
         <v>32</v>
       </c>
@@ -966,73 +1037,105 @@
       <c r="G19" s="7"/>
     </row>
     <row r="20" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A20" s="17"/>
-      <c r="B20" s="18" t="s">
+      <c r="A20" s="19"/>
+      <c r="B20" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="C20" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="C20" s="18" t="s">
-        <v>51</v>
-      </c>
-      <c r="D20" s="18" t="s">
-        <v>51</v>
-      </c>
-      <c r="E20" s="19"/>
-      <c r="F20" s="18"/>
+      <c r="D20" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="E20" s="12">
+        <v>1</v>
+      </c>
+      <c r="F20" s="9" t="s">
+        <v>53</v>
+      </c>
       <c r="G20" s="7"/>
     </row>
-    <row r="21" spans="1:7" s="2" customFormat="1" ht="33.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A21" s="6" t="s">
+    <row r="21" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A21" s="19"/>
+      <c r="B21" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C21" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="D21" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="E21" s="17"/>
+      <c r="F21" s="16"/>
+      <c r="G21" s="7"/>
+    </row>
+    <row r="22" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A22" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="B22" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="C22" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="D22" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="E22" s="17"/>
+      <c r="F22" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="G22" s="7"/>
+    </row>
+    <row r="23" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A23" s="19"/>
+      <c r="B23" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="C23" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="D23" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="E23" s="12">
+        <v>1</v>
+      </c>
+      <c r="F23" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G23" s="7"/>
+    </row>
+    <row r="24" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A24" s="19"/>
+      <c r="B24" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="C24" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="D24" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="E24" s="17"/>
+      <c r="F24" s="16"/>
+      <c r="G24" s="7"/>
+    </row>
+    <row r="25" spans="1:7" s="2" customFormat="1" ht="33.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A25" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B21" s="6" t="s">
+      <c r="B25" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="C21" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="D21" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="E21" s="6"/>
-      <c r="F21" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="G21" s="7"/>
-    </row>
-    <row r="22" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A22" s="6"/>
-      <c r="B22" s="6"/>
-      <c r="C22" s="6"/>
-      <c r="D22" s="6"/>
-      <c r="E22" s="6"/>
-      <c r="F22" s="6"/>
-      <c r="G22" s="7"/>
-    </row>
-    <row r="23" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A23" s="6"/>
-      <c r="B23" s="6"/>
-      <c r="C23" s="6"/>
-      <c r="D23" s="6"/>
-      <c r="E23" s="6"/>
-      <c r="F23" s="6"/>
-      <c r="G23" s="7"/>
-    </row>
-    <row r="24" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A24" s="6"/>
-      <c r="B24" s="6"/>
-      <c r="C24" s="6"/>
-      <c r="D24" s="6"/>
-      <c r="E24" s="6"/>
-      <c r="F24" s="6"/>
-      <c r="G24" s="7"/>
-    </row>
-    <row r="25" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A25" s="6"/>
-      <c r="B25" s="6"/>
       <c r="C25" s="6"/>
       <c r="D25" s="6"/>
       <c r="E25" s="6"/>
-      <c r="F25" s="6"/>
+      <c r="F25" s="6" t="s">
+        <v>48</v>
+      </c>
       <c r="G25" s="7"/>
     </row>
     <row r="26" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.15">
@@ -1189,30 +1292,67 @@
       <c r="G42" s="7"/>
     </row>
     <row r="43" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A43" s="3"/>
-      <c r="B43" s="3"/>
-      <c r="C43" s="3"/>
-      <c r="D43" s="3"/>
-      <c r="E43" s="3"/>
-      <c r="F43" s="3"/>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="F44" s="1"/>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="F45" s="1"/>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="F46" s="1"/>
+      <c r="A43" s="6"/>
+      <c r="B43" s="6"/>
+      <c r="C43" s="6"/>
+      <c r="D43" s="6"/>
+      <c r="E43" s="6"/>
+      <c r="F43" s="6"/>
+      <c r="G43" s="7"/>
+    </row>
+    <row r="44" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A44" s="6"/>
+      <c r="B44" s="6"/>
+      <c r="C44" s="6"/>
+      <c r="D44" s="6"/>
+      <c r="E44" s="6"/>
+      <c r="F44" s="6"/>
+      <c r="G44" s="7"/>
+    </row>
+    <row r="45" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A45" s="6"/>
+      <c r="B45" s="6"/>
+      <c r="C45" s="6"/>
+      <c r="D45" s="6"/>
+      <c r="E45" s="6"/>
+      <c r="F45" s="6"/>
+      <c r="G45" s="7"/>
+    </row>
+    <row r="46" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A46" s="6"/>
+      <c r="B46" s="6"/>
+      <c r="C46" s="6"/>
+      <c r="D46" s="6"/>
+      <c r="E46" s="6"/>
+      <c r="F46" s="6"/>
+      <c r="G46" s="7"/>
+    </row>
+    <row r="47" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A47" s="3"/>
+      <c r="B47" s="3"/>
+      <c r="C47" s="3"/>
+      <c r="D47" s="3"/>
+      <c r="E47" s="3"/>
+      <c r="F47" s="3"/>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="F48" s="1"/>
+    </row>
+    <row r="49" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F49" s="1"/>
+    </row>
+    <row r="50" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F50" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="7">
+    <mergeCell ref="A22:A24"/>
     <mergeCell ref="A1:G3"/>
     <mergeCell ref="A9:A10"/>
     <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A14:A20"/>
     <mergeCell ref="A5:A6"/>
     <mergeCell ref="A7:A8"/>
+    <mergeCell ref="A14:A21"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/1.xlsx
+++ b/1.xlsx
@@ -434,14 +434,14 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -757,33 +757,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A2" s="18"/>
-      <c r="B2" s="18"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
+      <c r="A2" s="20"/>
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A3" s="18"/>
-      <c r="B3" s="18"/>
-      <c r="C3" s="18"/>
-      <c r="D3" s="18"/>
-      <c r="E3" s="18"/>
-      <c r="F3" s="18"/>
-      <c r="G3" s="18"/>
+      <c r="A3" s="20"/>
+      <c r="B3" s="20"/>
+      <c r="C3" s="20"/>
+      <c r="D3" s="20"/>
+      <c r="E3" s="20"/>
+      <c r="F3" s="20"/>
+      <c r="G3" s="20"/>
     </row>
     <row r="4" spans="1:7" s="2" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="4" t="s">
@@ -831,15 +831,15 @@
       <c r="A6" s="19"/>
     </row>
     <row r="7" spans="1:7" ht="29.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="18" t="s">
+      <c r="A7" s="20" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="27" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="18"/>
+      <c r="A8" s="20"/>
     </row>
     <row r="9" spans="1:7" ht="38.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="18" t="s">
+      <c r="A9" s="20" t="s">
         <v>27</v>
       </c>
       <c r="B9" s="13" t="s">
@@ -857,7 +857,7 @@
       <c r="F9" s="15"/>
     </row>
     <row r="10" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="18"/>
+      <c r="A10" s="20"/>
       <c r="B10" s="3" t="s">
         <v>29</v>
       </c>
@@ -901,7 +901,7 @@
       <c r="D12" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="E12" s="20">
+      <c r="E12" s="18">
         <v>0.8</v>
       </c>
       <c r="F12" s="6" t="s">

--- a/1.xlsx
+++ b/1.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="70">
   <si>
     <t>模块</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -300,6 +300,10 @@
   </si>
   <si>
     <t>26.4.19</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1057,17 +1061,21 @@
     </row>
     <row r="21" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="19"/>
-      <c r="B21" s="16" t="s">
+      <c r="B21" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="C21" s="16" t="s">
+      <c r="C21" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="D21" s="16" t="s">
+      <c r="D21" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="E21" s="17"/>
-      <c r="F21" s="16"/>
+      <c r="E21" s="12">
+        <v>1</v>
+      </c>
+      <c r="F21" s="9" t="s">
+        <v>69</v>
+      </c>
       <c r="G21" s="7"/>
     </row>
     <row r="22" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">

--- a/1.xlsx
+++ b/1.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="74">
   <si>
     <t>模块</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -287,27 +287,43 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>波次设计11-15</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>26.4.18</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>26.4.19</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>AI, 配置，预制件</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>波次设计11-15</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>26.4.18</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>26.4.19</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>-</t>
+    <t>26.4.16</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>26.4.16</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>子弹类型2生成</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>生成的子弹可控制在任意节点上，并且子弹有休眠模式，在休眠模式下子弹不做运动。为之后BOSS环绕子弹做铺垫</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -748,7 +764,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G50"/>
+  <dimension ref="A1:G51"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="22.625" style="3" customWidth="1"/>
@@ -1074,7 +1090,7 @@
         <v>1</v>
       </c>
       <c r="F21" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G21" s="7"/>
     </row>
@@ -1083,76 +1099,84 @@
         <v>54</v>
       </c>
       <c r="B22" s="16" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="C22" s="16" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="D22" s="16" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="E22" s="17"/>
       <c r="F22" s="16" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="G22" s="7"/>
     </row>
     <row r="23" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="19"/>
-      <c r="B23" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="C23" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="D23" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="E23" s="12">
-        <v>1</v>
-      </c>
-      <c r="F23" s="9" t="s">
-        <v>68</v>
+      <c r="B23" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="C23" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="D23" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="E23" s="17"/>
+      <c r="F23" s="16" t="s">
+        <v>69</v>
       </c>
       <c r="G23" s="7"/>
     </row>
     <row r="24" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="19"/>
-      <c r="B24" s="16" t="s">
-        <v>65</v>
-      </c>
-      <c r="C24" s="16" t="s">
-        <v>66</v>
-      </c>
-      <c r="D24" s="16" t="s">
+      <c r="B24" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="D24" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="E24" s="12">
+        <v>1</v>
+      </c>
+      <c r="F24" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="E24" s="17"/>
-      <c r="F24" s="16"/>
       <c r="G24" s="7"/>
     </row>
     <row r="25" spans="1:7" s="2" customFormat="1" ht="33.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B25" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="C25" s="6"/>
-      <c r="D25" s="6"/>
-      <c r="E25" s="6"/>
-      <c r="F25" s="6" t="s">
-        <v>48</v>
-      </c>
+      <c r="B25" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="C25" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="D25" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="E25" s="17"/>
+      <c r="F25" s="16"/>
       <c r="G25" s="7"/>
     </row>
     <row r="26" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A26" s="6"/>
-      <c r="B26" s="6"/>
+      <c r="B26" s="6" t="s">
+        <v>47</v>
+      </c>
       <c r="C26" s="6"/>
       <c r="D26" s="6"/>
       <c r="E26" s="6"/>
-      <c r="F26" s="6"/>
+      <c r="F26" s="6" t="s">
+        <v>48</v>
+      </c>
       <c r="G26" s="7"/>
     </row>
     <row r="27" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.15">
@@ -1337,20 +1361,23 @@
     </row>
     <row r="47" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A47" s="3"/>
-      <c r="B47" s="3"/>
-      <c r="C47" s="3"/>
-      <c r="D47" s="3"/>
-      <c r="E47" s="3"/>
-      <c r="F47" s="3"/>
+      <c r="B47" s="6"/>
+      <c r="C47" s="6"/>
+      <c r="D47" s="6"/>
+      <c r="E47" s="6"/>
+      <c r="F47" s="6"/>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="F48" s="1"/>
+      <c r="F48" s="3"/>
     </row>
     <row r="49" spans="6:6" x14ac:dyDescent="0.15">
       <c r="F49" s="1"/>
     </row>
     <row r="50" spans="6:6" x14ac:dyDescent="0.15">
       <c r="F50" s="1"/>
+    </row>
+    <row r="51" spans="6:6" x14ac:dyDescent="0.15">
+      <c r="F51" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="7">

--- a/1.xlsx
+++ b/1.xlsx
@@ -1098,17 +1098,19 @@
       <c r="A22" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="B22" s="16" t="s">
+      <c r="B22" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="C22" s="16" t="s">
+      <c r="C22" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="D22" s="16" t="s">
+      <c r="D22" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="E22" s="17"/>
-      <c r="F22" s="16" t="s">
+      <c r="E22" s="12">
+        <v>1</v>
+      </c>
+      <c r="F22" s="9" t="s">
         <v>73</v>
       </c>
       <c r="G22" s="7"/>

--- a/1.xlsx
+++ b/1.xlsx
@@ -239,10 +239,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>待验证</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>-</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -324,6 +320,10 @@
   </si>
   <si>
     <t>生成的子弹可控制在任意节点上，并且子弹有休眠模式，在休眠模式下子弹不做运动。为之后BOSS环绕子弹做铺垫</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>敌人出生后马上消失，波次结束时又出现</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -922,10 +922,10 @@
         <v>46</v>
       </c>
       <c r="E12" s="18">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>52</v>
+        <v>73</v>
       </c>
       <c r="G12" s="7"/>
     </row>
@@ -1071,105 +1071,107 @@
         <v>1</v>
       </c>
       <c r="F20" s="9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G20" s="7"/>
     </row>
     <row r="21" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="19"/>
       <c r="B21" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="C21" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="C21" s="9" t="s">
+      <c r="D21" s="9" t="s">
         <v>59</v>
-      </c>
-      <c r="D21" s="9" t="s">
-        <v>60</v>
       </c>
       <c r="E21" s="12">
         <v>1</v>
       </c>
       <c r="F21" s="9" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G21" s="7"/>
     </row>
     <row r="22" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="19" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C22" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="D22" s="9" t="s">
         <v>70</v>
-      </c>
-      <c r="D22" s="9" t="s">
-        <v>71</v>
       </c>
       <c r="E22" s="12">
         <v>1</v>
       </c>
       <c r="F22" s="9" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G22" s="7"/>
     </row>
     <row r="23" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="19"/>
-      <c r="B23" s="16" t="s">
+      <c r="B23" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="C23" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="D23" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="C23" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="D23" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="E23" s="17"/>
-      <c r="F23" s="16" t="s">
-        <v>69</v>
+      <c r="E23" s="12">
+        <v>1</v>
+      </c>
+      <c r="F23" s="9" t="s">
+        <v>68</v>
       </c>
       <c r="G23" s="7"/>
     </row>
     <row r="24" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="19"/>
       <c r="B24" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="C24" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="C24" s="9" t="s">
+      <c r="D24" s="9" t="s">
         <v>56</v>
-      </c>
-      <c r="D24" s="9" t="s">
-        <v>57</v>
       </c>
       <c r="E24" s="12">
         <v>1</v>
       </c>
       <c r="F24" s="9" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G24" s="7"/>
     </row>
     <row r="25" spans="1:7" s="2" customFormat="1" ht="33.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A25" s="6" t="s">
+      <c r="A25" s="19" t="s">
         <v>15</v>
       </c>
       <c r="B25" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="C25" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="C25" s="16" t="s">
+      <c r="D25" s="16" t="s">
         <v>65</v>
-      </c>
-      <c r="D25" s="16" t="s">
-        <v>66</v>
       </c>
       <c r="E25" s="17"/>
       <c r="F25" s="16"/>
       <c r="G25" s="7"/>
     </row>
     <row r="26" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A26" s="6"/>
+      <c r="A26" s="19"/>
       <c r="B26" s="6" t="s">
         <v>47</v>
       </c>
@@ -1382,7 +1384,8 @@
       <c r="F51" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="8">
+    <mergeCell ref="A25:A26"/>
     <mergeCell ref="A22:A24"/>
     <mergeCell ref="A1:G3"/>
     <mergeCell ref="A9:A10"/>

--- a/1.xlsx
+++ b/1.xlsx
@@ -11,12 +11,12 @@
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="122211"/>
+  <calcPr calcId="145621"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="81">
   <si>
     <t>模块</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -283,18 +283,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>波次设计11-15</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>26.4.18</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>26.4.19</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>-</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -324,6 +316,42 @@
   </si>
   <si>
     <t>敌人出生后马上消失，波次结束时又出现</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在升级核心后，伤害计算有误</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>26.4.22</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>已有波次优化11-15</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>26.4.23</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>敌人数值填充</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>26.4.23</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>属性存在小数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>26.4.24</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -764,7 +792,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G51"/>
+  <dimension ref="A1:G54"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="22.625" style="3" customWidth="1"/>
@@ -925,7 +953,7 @@
         <v>0</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G12" s="7"/>
     </row>
@@ -948,266 +976,288 @@
       </c>
       <c r="G13" s="7"/>
     </row>
-    <row r="14" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A14" s="19" t="s">
+    <row r="14" spans="1:7" s="2" customFormat="1" ht="47.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A14" s="19"/>
+      <c r="B14" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="C14" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="D14" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="E14" s="17">
+        <v>1</v>
+      </c>
+      <c r="F14" s="16" t="s">
+        <v>80</v>
+      </c>
+      <c r="G14" s="7"/>
+    </row>
+    <row r="15" spans="1:7" s="2" customFormat="1" ht="47.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A15" s="19"/>
+      <c r="B15" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="C15" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="D15" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="E15" s="17"/>
+      <c r="F15" s="16"/>
+      <c r="G15" s="7"/>
+    </row>
+    <row r="16" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A16" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="B16" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="C14" s="8"/>
-      <c r="D14" s="8"/>
-      <c r="E14" s="6"/>
-      <c r="F14" s="6"/>
-      <c r="G14" s="7"/>
-    </row>
-    <row r="15" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A15" s="19"/>
-      <c r="B15" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="C15" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="D15" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="E15" s="12">
-        <v>1</v>
-      </c>
-      <c r="F15" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G15" s="7"/>
-    </row>
-    <row r="16" spans="1:7" s="2" customFormat="1" ht="48.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A16" s="19"/>
-      <c r="B16" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C16" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="D16" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="E16" s="12">
-        <v>1</v>
-      </c>
-      <c r="F16" s="9" t="s">
-        <v>40</v>
-      </c>
+      <c r="C16" s="8"/>
+      <c r="D16" s="8"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="6"/>
       <c r="G16" s="7"/>
     </row>
-    <row r="17" spans="1:7" s="2" customFormat="1" ht="48.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="19"/>
       <c r="B17" s="9" t="s">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="D17" s="9" t="s">
-        <v>43</v>
+        <v>24</v>
+      </c>
+      <c r="D17" s="11" t="s">
+        <v>24</v>
       </c>
       <c r="E17" s="12">
         <v>1</v>
       </c>
       <c r="F17" s="9" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="G17" s="7"/>
     </row>
-    <row r="18" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:7" s="2" customFormat="1" ht="48.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="19"/>
       <c r="B18" s="9" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="E18" s="12">
         <v>1</v>
       </c>
       <c r="F18" s="9" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="G18" s="7"/>
     </row>
-    <row r="19" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:7" s="2" customFormat="1" ht="48.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="19"/>
       <c r="B19" s="9" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="E19" s="12">
         <v>1</v>
       </c>
       <c r="F19" s="9" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="G19" s="7"/>
     </row>
     <row r="20" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="19"/>
       <c r="B20" s="9" t="s">
-        <v>49</v>
+        <v>9</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>50</v>
+        <v>21</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>50</v>
+        <v>21</v>
       </c>
       <c r="E20" s="12">
         <v>1</v>
       </c>
       <c r="F20" s="9" t="s">
-        <v>52</v>
+        <v>23</v>
       </c>
       <c r="G20" s="7"/>
     </row>
     <row r="21" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="19"/>
       <c r="B21" s="9" t="s">
-        <v>57</v>
+        <v>32</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>58</v>
+        <v>33</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>59</v>
+        <v>37</v>
       </c>
       <c r="E21" s="12">
         <v>1</v>
       </c>
       <c r="F21" s="9" t="s">
-        <v>67</v>
+        <v>38</v>
       </c>
       <c r="G21" s="7"/>
     </row>
     <row r="22" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A22" s="19" t="s">
-        <v>53</v>
-      </c>
+      <c r="A22" s="19"/>
       <c r="B22" s="9" t="s">
-        <v>71</v>
+        <v>49</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>69</v>
+        <v>50</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="E22" s="12">
         <v>1</v>
       </c>
       <c r="F22" s="9" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="G22" s="7"/>
     </row>
     <row r="23" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="19"/>
       <c r="B23" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="C23" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="D23" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="E23" s="12">
+        <v>1</v>
+      </c>
+      <c r="F23" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="G23" s="7"/>
+    </row>
+    <row r="24" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A24" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="B24" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="D24" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="E24" s="12">
+        <v>1</v>
+      </c>
+      <c r="F24" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="G24" s="7"/>
+    </row>
+    <row r="25" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A25" s="19"/>
+      <c r="B25" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="C23" s="9" t="s">
+      <c r="C25" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="D23" s="9" t="s">
+      <c r="D25" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="E23" s="12">
-        <v>1</v>
-      </c>
-      <c r="F23" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="G23" s="7"/>
-    </row>
-    <row r="24" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A24" s="19"/>
-      <c r="B24" s="9" t="s">
+      <c r="E25" s="12">
+        <v>1</v>
+      </c>
+      <c r="F25" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="G25" s="7"/>
+    </row>
+    <row r="26" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A26" s="19"/>
+      <c r="B26" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="C24" s="9" t="s">
+      <c r="C26" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="D24" s="9" t="s">
+      <c r="D26" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="E24" s="12">
-        <v>1</v>
-      </c>
-      <c r="F24" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="G24" s="7"/>
-    </row>
-    <row r="25" spans="1:7" s="2" customFormat="1" ht="33.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A25" s="19" t="s">
+      <c r="E26" s="12">
+        <v>1</v>
+      </c>
+      <c r="F26" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="G26" s="7"/>
+    </row>
+    <row r="27" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A27" s="19"/>
+      <c r="B27" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="C27" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="D27" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="E27" s="17"/>
+      <c r="F27" s="16"/>
+      <c r="G27" s="7"/>
+    </row>
+    <row r="28" spans="1:7" s="2" customFormat="1" ht="33.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A28" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="B25" s="16" t="s">
+      <c r="B28" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="C28" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="C25" s="16" t="s">
-        <v>64</v>
-      </c>
-      <c r="D25" s="16" t="s">
-        <v>65</v>
-      </c>
-      <c r="E25" s="17"/>
-      <c r="F25" s="16"/>
-      <c r="G25" s="7"/>
-    </row>
-    <row r="26" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A26" s="19"/>
-      <c r="B26" s="6" t="s">
+      <c r="D28" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="E28" s="17"/>
+      <c r="F28" s="16"/>
+      <c r="G28" s="7"/>
+    </row>
+    <row r="29" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A29" s="19"/>
+      <c r="B29" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="C26" s="6"/>
-      <c r="D26" s="6"/>
-      <c r="E26" s="6"/>
-      <c r="F26" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="G26" s="7"/>
-    </row>
-    <row r="27" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A27" s="6"/>
-      <c r="B27" s="6"/>
-      <c r="C27" s="6"/>
-      <c r="D27" s="6"/>
-      <c r="E27" s="6"/>
-      <c r="F27" s="6"/>
-      <c r="G27" s="7"/>
-    </row>
-    <row r="28" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A28" s="6"/>
-      <c r="B28" s="6"/>
-      <c r="C28" s="6"/>
-      <c r="D28" s="6"/>
-      <c r="E28" s="6"/>
-      <c r="F28" s="6"/>
-      <c r="G28" s="7"/>
-    </row>
-    <row r="29" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A29" s="6"/>
-      <c r="B29" s="6"/>
       <c r="C29" s="6"/>
       <c r="D29" s="6"/>
       <c r="E29" s="6"/>
-      <c r="F29" s="6"/>
+      <c r="F29" s="6" t="s">
+        <v>48</v>
+      </c>
       <c r="G29" s="7"/>
     </row>
     <row r="30" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.15">
@@ -1364,35 +1414,62 @@
       <c r="G46" s="7"/>
     </row>
     <row r="47" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A47" s="3"/>
+      <c r="A47" s="6"/>
       <c r="B47" s="6"/>
       <c r="C47" s="6"/>
       <c r="D47" s="6"/>
       <c r="E47" s="6"/>
       <c r="F47" s="6"/>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="F48" s="3"/>
-    </row>
-    <row r="49" spans="6:6" x14ac:dyDescent="0.15">
-      <c r="F49" s="1"/>
-    </row>
-    <row r="50" spans="6:6" x14ac:dyDescent="0.15">
-      <c r="F50" s="1"/>
-    </row>
-    <row r="51" spans="6:6" x14ac:dyDescent="0.15">
-      <c r="F51" s="1"/>
+      <c r="G47" s="7"/>
+    </row>
+    <row r="48" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A48" s="6"/>
+      <c r="B48" s="6"/>
+      <c r="C48" s="6"/>
+      <c r="D48" s="6"/>
+      <c r="E48" s="6"/>
+      <c r="F48" s="6"/>
+      <c r="G48" s="7"/>
+    </row>
+    <row r="49" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A49" s="6"/>
+      <c r="B49" s="6"/>
+      <c r="C49" s="6"/>
+      <c r="D49" s="6"/>
+      <c r="E49" s="6"/>
+      <c r="F49" s="6"/>
+      <c r="G49" s="7"/>
+    </row>
+    <row r="50" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A50" s="3"/>
+      <c r="B50" s="6"/>
+      <c r="C50" s="6"/>
+      <c r="D50" s="6"/>
+      <c r="E50" s="6"/>
+      <c r="F50" s="6"/>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="F51" s="3"/>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="F52" s="1"/>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="F53" s="1"/>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="F54" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A25:A26"/>
-    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A28:A29"/>
     <mergeCell ref="A1:G3"/>
     <mergeCell ref="A9:A10"/>
-    <mergeCell ref="A12:A13"/>
     <mergeCell ref="A5:A6"/>
     <mergeCell ref="A7:A8"/>
-    <mergeCell ref="A14:A21"/>
+    <mergeCell ref="A16:A23"/>
+    <mergeCell ref="A24:A27"/>
+    <mergeCell ref="A12:A15"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/1.xlsx
+++ b/1.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="83">
   <si>
     <t>模块</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -331,18 +331,14 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>敌人数值填充</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>26.4.23</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>敌人数值填充</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>26.4.23</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>属性存在小数</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -352,6 +348,18 @@
   </si>
   <si>
     <t>-</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在波次结束后仍可以受到远程伤害</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>26.4.27</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -792,7 +800,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G54"/>
+  <dimension ref="A1:G55"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="22.625" style="3" customWidth="1"/>
@@ -991,282 +999,288 @@
         <v>1</v>
       </c>
       <c r="F14" s="16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G14" s="7"/>
     </row>
     <row r="15" spans="1:7" s="2" customFormat="1" ht="47.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="19"/>
       <c r="B15" s="16" t="s">
-        <v>78</v>
-      </c>
-      <c r="C15" s="16" t="s">
-        <v>79</v>
-      </c>
-      <c r="D15" s="16" t="s">
-        <v>79</v>
-      </c>
+        <v>81</v>
+      </c>
+      <c r="C15" s="16"/>
+      <c r="D15" s="16"/>
       <c r="E15" s="17"/>
       <c r="F15" s="16"/>
       <c r="G15" s="7"/>
     </row>
-    <row r="16" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A16" s="19" t="s">
+    <row r="16" spans="1:7" s="2" customFormat="1" ht="47.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A16" s="19"/>
+      <c r="B16" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="C16" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="D16" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="E16" s="17"/>
+      <c r="F16" s="16"/>
+      <c r="G16" s="7"/>
+    </row>
+    <row r="17" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A17" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="B17" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="C16" s="8"/>
-      <c r="D16" s="8"/>
-      <c r="E16" s="6"/>
-      <c r="F16" s="6"/>
-      <c r="G16" s="7"/>
-    </row>
-    <row r="17" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A17" s="19"/>
-      <c r="B17" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="C17" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="D17" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="E17" s="12">
-        <v>1</v>
-      </c>
-      <c r="F17" s="9" t="s">
-        <v>26</v>
-      </c>
+      <c r="C17" s="8"/>
+      <c r="D17" s="8"/>
+      <c r="E17" s="6"/>
+      <c r="F17" s="6"/>
       <c r="G17" s="7"/>
     </row>
-    <row r="18" spans="1:7" s="2" customFormat="1" ht="48.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="19"/>
       <c r="B18" s="9" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="D18" s="9" t="s">
-        <v>45</v>
+        <v>24</v>
+      </c>
+      <c r="D18" s="11" t="s">
+        <v>24</v>
       </c>
       <c r="E18" s="12">
         <v>1</v>
       </c>
       <c r="F18" s="9" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="G18" s="7"/>
     </row>
     <row r="19" spans="1:7" s="2" customFormat="1" ht="48.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="19"/>
       <c r="B19" s="9" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E19" s="12">
         <v>1</v>
       </c>
       <c r="F19" s="9" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G19" s="7"/>
     </row>
-    <row r="20" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:7" s="2" customFormat="1" ht="48.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="19"/>
       <c r="B20" s="9" t="s">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="E20" s="12">
         <v>1</v>
       </c>
       <c r="F20" s="9" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="G20" s="7"/>
     </row>
     <row r="21" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="19"/>
       <c r="B21" s="9" t="s">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="E21" s="12">
         <v>1</v>
       </c>
       <c r="F21" s="9" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="G21" s="7"/>
     </row>
     <row r="22" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="19"/>
       <c r="B22" s="9" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="E22" s="12">
         <v>1</v>
       </c>
       <c r="F22" s="9" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="G22" s="7"/>
     </row>
     <row r="23" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="19"/>
       <c r="B23" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="C23" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D23" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="E23" s="12">
+        <v>1</v>
+      </c>
+      <c r="F23" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="G23" s="7"/>
+    </row>
+    <row r="24" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A24" s="19"/>
+      <c r="B24" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="C23" s="9" t="s">
+      <c r="C24" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="D23" s="9" t="s">
+      <c r="D24" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="E23" s="12">
-        <v>1</v>
-      </c>
-      <c r="F23" s="9" t="s">
+      <c r="E24" s="12">
+        <v>1</v>
+      </c>
+      <c r="F24" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="G23" s="7"/>
-    </row>
-    <row r="24" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A24" s="19" t="s">
+      <c r="G24" s="7"/>
+    </row>
+    <row r="25" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A25" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="B24" s="9" t="s">
+      <c r="B25" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="C24" s="9" t="s">
+      <c r="C25" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="D24" s="9" t="s">
+      <c r="D25" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="E24" s="12">
-        <v>1</v>
-      </c>
-      <c r="F24" s="9" t="s">
+      <c r="E25" s="12">
+        <v>1</v>
+      </c>
+      <c r="F25" s="9" t="s">
         <v>70</v>
-      </c>
-      <c r="G24" s="7"/>
-    </row>
-    <row r="25" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A25" s="19"/>
-      <c r="B25" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="C25" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="D25" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="E25" s="12">
-        <v>1</v>
-      </c>
-      <c r="F25" s="9" t="s">
-        <v>66</v>
       </c>
       <c r="G25" s="7"/>
     </row>
     <row r="26" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="19"/>
       <c r="B26" s="9" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="E26" s="12">
         <v>1</v>
       </c>
       <c r="F26" s="9" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G26" s="7"/>
     </row>
     <row r="27" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="19"/>
-      <c r="B27" s="16" t="s">
+      <c r="B27" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="C27" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="D27" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="E27" s="12">
+        <v>1</v>
+      </c>
+      <c r="F27" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="G27" s="7"/>
+    </row>
+    <row r="28" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A28" s="19"/>
+      <c r="B28" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="C28" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="C27" s="16" t="s">
-        <v>77</v>
-      </c>
-      <c r="D27" s="16" t="s">
-        <v>77</v>
-      </c>
-      <c r="E27" s="17"/>
-      <c r="F27" s="16"/>
-      <c r="G27" s="7"/>
-    </row>
-    <row r="28" spans="1:7" s="2" customFormat="1" ht="33.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A28" s="19" t="s">
+      <c r="D28" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="E28" s="17">
+        <v>1</v>
+      </c>
+      <c r="F28" s="16" t="s">
+        <v>80</v>
+      </c>
+      <c r="G28" s="7"/>
+    </row>
+    <row r="29" spans="1:7" s="2" customFormat="1" ht="33.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A29" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="B28" s="16" t="s">
+      <c r="B29" s="16" t="s">
         <v>74</v>
       </c>
-      <c r="C28" s="16" t="s">
+      <c r="C29" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="D28" s="16" t="s">
-        <v>75</v>
-      </c>
-      <c r="E28" s="17"/>
-      <c r="F28" s="16"/>
-      <c r="G28" s="7"/>
-    </row>
-    <row r="29" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A29" s="19"/>
-      <c r="B29" s="6" t="s">
+      <c r="D29" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="E29" s="17"/>
+      <c r="F29" s="16"/>
+      <c r="G29" s="7"/>
+    </row>
+    <row r="30" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A30" s="19"/>
+      <c r="B30" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="C29" s="6"/>
-      <c r="D29" s="6"/>
-      <c r="E29" s="6"/>
-      <c r="F29" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="G29" s="7"/>
-    </row>
-    <row r="30" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A30" s="6"/>
-      <c r="B30" s="6"/>
       <c r="C30" s="6"/>
       <c r="D30" s="6"/>
       <c r="E30" s="6"/>
-      <c r="F30" s="6"/>
+      <c r="F30" s="6" t="s">
+        <v>48</v>
+      </c>
       <c r="G30" s="7"/>
     </row>
     <row r="31" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.15">
@@ -1441,18 +1455,24 @@
       <c r="G49" s="7"/>
     </row>
     <row r="50" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A50" s="3"/>
+      <c r="A50" s="6"/>
       <c r="B50" s="6"/>
       <c r="C50" s="6"/>
       <c r="D50" s="6"/>
       <c r="E50" s="6"/>
       <c r="F50" s="6"/>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="F51" s="3"/>
+      <c r="G50" s="7"/>
+    </row>
+    <row r="51" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A51" s="3"/>
+      <c r="B51" s="6"/>
+      <c r="C51" s="6"/>
+      <c r="D51" s="6"/>
+      <c r="E51" s="6"/>
+      <c r="F51" s="6"/>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="F52" s="1"/>
+      <c r="F52" s="3"/>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.15">
       <c r="F53" s="1"/>
@@ -1460,16 +1480,19 @@
     <row r="54" spans="1:7" x14ac:dyDescent="0.15">
       <c r="F54" s="1"/>
     </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="F55" s="1"/>
+    </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="A29:A30"/>
     <mergeCell ref="A1:G3"/>
     <mergeCell ref="A9:A10"/>
     <mergeCell ref="A5:A6"/>
     <mergeCell ref="A7:A8"/>
-    <mergeCell ref="A16:A23"/>
-    <mergeCell ref="A24:A27"/>
-    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A17:A24"/>
+    <mergeCell ref="A25:A28"/>
+    <mergeCell ref="A12:A16"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/1.xlsx
+++ b/1.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="84">
   <si>
     <t>模块</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -360,6 +360,10 @@
   </si>
   <si>
     <t>26.4.27</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>26.4.28</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1023,7 +1027,7 @@
         <v>78</v>
       </c>
       <c r="D16" s="16" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E16" s="17"/>
       <c r="F16" s="16"/>
@@ -1266,7 +1270,9 @@
       <c r="D29" s="16" t="s">
         <v>82</v>
       </c>
-      <c r="E29" s="17"/>
+      <c r="E29" s="17">
+        <v>0.2</v>
+      </c>
       <c r="F29" s="16"/>
       <c r="G29" s="7"/>
     </row>

--- a/1.xlsx
+++ b/1.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="100">
   <si>
     <t>模块</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -91,279 +91,343 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>道具</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>26.3.24</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>26.3.22</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>26.3.23</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>备注</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>26.3.26</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>26.3.27</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>核心强化界面调整,准备界面核心强化图标改进</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>属性</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>角色防御属性设计</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>角色幸运属性设计</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>属性面板点击事件被其他遮罩盖住</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>26.3.26</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>属性弹窗说明优化</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>26.3.29</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>界面弹窗功能重做</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>26.4.1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>26.4.2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>26.4.6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>提示管理功能</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>拆分成传统弹窗和Tooltips。侧边属性. 传统弹窗同时只能存在一个</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>26.4.7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>角色属性预览, 道具预览, 核心预览, 核心强化预览, 可用, 后续轻提示同样可用, Tooltips同时只能存在一个</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>26.4.8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>26.4.10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>26.4.9</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>部分核心强化包图标</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>左右开弓,饱和散射,急速散射,风暴聚集;(开花,穿云重新命名)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>备战界面核心经验进度条</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>26.4.10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>弹窗功能重做不会再出现此问题</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>游戏配置</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>敌人配置，波次配置数值重做</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>26.4.12</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>26.4.14</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Boss2 图片</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>26.4.13</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>26.4.13</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>26.4.14</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Boss2 设计</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>26.4.17</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>26.4.18</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AI, 配置，预制件</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>26.4.16</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>26.4.16</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>子弹类型2生成</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>生成的子弹可控制在任意节点上，并且子弹有休眠模式，在休眠模式下子弹不做运动。为之后BOSS环绕子弹做铺垫</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在升级核心后，伤害计算有误</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>26.4.22</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>已有波次优化11-15</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>敌人数值填充</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>26.4.23</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>属性存在小数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>26.4.24</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>26.4.28</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>26.4.28</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>敌人回收前将动画停止即可</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>UI设计</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>道具</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>26.3.24</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>26.3.22</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>26.3.23</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>备注</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>26.3.26</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>26.3.27</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>核心强化界面调整,准备界面核心强化图标改进</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>属性</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>角色防御属性设计</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>角色幸运属性设计</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>属性面板点击事件被其他遮罩盖住</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>26.3.26</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>属性弹窗说明优化</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>26.3.29</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>界面弹窗功能重做</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>26.4.1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>26.4.2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>26.4.6</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>提示管理功能</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>拆分成传统弹窗和Tooltips。侧边属性. 传统弹窗同时只能存在一个</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>26.4.7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>角色属性预览, 道具预览, 核心预览, 核心强化预览, 可用, 后续轻提示同样可用, Tooltips同时只能存在一个</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>26.4.8</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>26.4.10</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>26.4.9</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>26.4.10</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>部分核心强化包图标</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>左右开弓,饱和散射,急速散射,风暴聚集;(开花,穿云重新命名)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>备战界面核心经验进度条</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>26.4.10</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>弹窗功能重做不会再出现此问题</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>游戏配置</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>敌人配置，波次配置数值重做</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>26.4.12</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>26.4.14</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Boss2 图片</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>26.4.13</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>26.4.13</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>26.4.14</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Boss2 设计</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>26.4.17</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>26.4.18</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>AI, 配置，预制件</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>26.4.16</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>26.4.16</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>子弹类型2生成</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>生成的子弹可控制在任意节点上，并且子弹有休眠模式，在休眠模式下子弹不做运动。为之后BOSS环绕子弹做铺垫</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>敌人出生后马上消失，波次结束时又出现</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>在升级核心后，伤害计算有误</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>26.4.22</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>已有波次优化11-15</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>敌人数值填充</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>26.4.23</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>属性存在小数</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>26.4.24</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>在波次结束后仍可以受到远程伤害</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>26.4.27</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>26.4.28</t>
+    <t>波次16-20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>26.5.3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>26.5.4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>伤害结算错误(高核心等级时)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>26.5.5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>待测试，第5波怪太多</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>公共子弹属性被污染</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>道具价格控制</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>宝箱图标</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>26.5.6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>26.5.6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>26.5.7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>26.5.7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>宝箱生成逻辑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>开宝箱界面</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>26.5.8</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -443,7 +507,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -495,6 +559,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -804,7 +871,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G55"/>
+  <dimension ref="A1:G57"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="22.625" style="3" customWidth="1"/>
@@ -817,33 +884,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
+      <c r="G1" s="21"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A2" s="20"/>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
-      <c r="G2" s="20"/>
+      <c r="A2" s="21"/>
+      <c r="B2" s="21"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="21"/>
+      <c r="F2" s="21"/>
+      <c r="G2" s="21"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A3" s="20"/>
-      <c r="B3" s="20"/>
-      <c r="C3" s="20"/>
-      <c r="D3" s="20"/>
-      <c r="E3" s="20"/>
-      <c r="F3" s="20"/>
-      <c r="G3" s="20"/>
+      <c r="A3" s="21"/>
+      <c r="B3" s="21"/>
+      <c r="C3" s="21"/>
+      <c r="D3" s="21"/>
+      <c r="E3" s="21"/>
+      <c r="F3" s="21"/>
+      <c r="G3" s="21"/>
     </row>
     <row r="4" spans="1:7" s="2" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="4" t="s">
@@ -862,179 +929,199 @@
         <v>14</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G4" s="5"/>
     </row>
     <row r="5" spans="1:7" s="2" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="19" t="s">
+      <c r="A5" s="20" t="s">
         <v>2</v>
       </c>
       <c r="B5" s="9" t="s">
         <v>3</v>
       </c>
       <c r="C5" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="D5" s="10" t="s">
-        <v>19</v>
-      </c>
       <c r="E5" s="12">
         <v>1</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G5" s="7"/>
     </row>
     <row r="6" spans="1:7" ht="30.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="19"/>
+      <c r="A6" s="20"/>
     </row>
     <row r="7" spans="1:7" ht="29.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="20" t="s">
-        <v>16</v>
+      <c r="A7" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="27" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="20"/>
+      <c r="A8" s="21"/>
+      <c r="B8" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="9" spans="1:7" ht="38.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="20" t="s">
+      <c r="A9" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="B9" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="B9" s="13" t="s">
+      <c r="C9" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="D9" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="E9" s="14">
+        <v>1</v>
+      </c>
+      <c r="F9" s="15"/>
+    </row>
+    <row r="10" spans="1:7" ht="38.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A10" s="21"/>
+      <c r="B10" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C9" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="D9" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="E9" s="14">
-        <v>1</v>
-      </c>
-      <c r="F9" s="15"/>
-    </row>
-    <row r="10" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="20"/>
-      <c r="B10" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
       <c r="F10" s="6"/>
-      <c r="G10" s="7"/>
-    </row>
-    <row r="11" spans="1:7" s="2" customFormat="1" ht="69.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A11" s="6" t="s">
-        <v>5</v>
-      </c>
+    </row>
+    <row r="11" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A11" s="21"/>
       <c r="B11" s="9" t="s">
         <v>6</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E11" s="12">
         <v>1</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G11" s="7"/>
     </row>
-    <row r="12" spans="1:7" s="2" customFormat="1" ht="47.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A12" s="19" t="s">
-        <v>10</v>
+    <row r="12" spans="1:7" s="2" customFormat="1" ht="69.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A12" s="6" t="s">
+        <v>5</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>46</v>
+        <v>80</v>
       </c>
       <c r="E12" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="G12" s="7"/>
     </row>
     <row r="13" spans="1:7" s="2" customFormat="1" ht="47.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A13" s="19"/>
+      <c r="A13" s="20" t="s">
+        <v>10</v>
+      </c>
       <c r="B13" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E13" s="12">
         <v>1</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G13" s="7"/>
     </row>
     <row r="14" spans="1:7" s="2" customFormat="1" ht="47.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A14" s="19"/>
+      <c r="A14" s="20"/>
       <c r="B14" s="16" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C14" s="16" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D14" s="16" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="E14" s="17">
         <v>1</v>
       </c>
       <c r="F14" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="G14" s="7"/>
+    </row>
+    <row r="15" spans="1:7" s="2" customFormat="1" ht="47.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A15" s="20"/>
+      <c r="B15" s="16" t="s">
+        <v>87</v>
+      </c>
+      <c r="C15" s="16" t="s">
+        <v>88</v>
+      </c>
+      <c r="D15" s="16" t="s">
+        <v>88</v>
+      </c>
+      <c r="E15" s="17">
+        <v>1</v>
+      </c>
+      <c r="F15" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="G15" s="7"/>
+    </row>
+    <row r="16" spans="1:7" s="2" customFormat="1" ht="47.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A16" s="20"/>
+      <c r="B16" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="C16" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="D16" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="E16" s="17">
+        <v>1</v>
+      </c>
+      <c r="F16" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="G14" s="7"/>
-    </row>
-    <row r="15" spans="1:7" s="2" customFormat="1" ht="47.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A15" s="19"/>
-      <c r="B15" s="16" t="s">
-        <v>81</v>
-      </c>
-      <c r="C15" s="16"/>
-      <c r="D15" s="16"/>
-      <c r="E15" s="17"/>
-      <c r="F15" s="16"/>
-      <c r="G15" s="7"/>
-    </row>
-    <row r="16" spans="1:7" s="2" customFormat="1" ht="47.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A16" s="19"/>
-      <c r="B16" s="16" t="s">
-        <v>77</v>
-      </c>
-      <c r="C16" s="16" t="s">
-        <v>78</v>
-      </c>
-      <c r="D16" s="16" t="s">
-        <v>83</v>
-      </c>
-      <c r="E16" s="17"/>
-      <c r="F16" s="16"/>
       <c r="G16" s="7"/>
     </row>
-    <row r="17" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A17" s="19" t="s">
+    <row r="17" spans="1:7" s="2" customFormat="1" ht="47.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A17" s="20" t="s">
         <v>8</v>
       </c>
       <c r="B17" s="6" t="s">
@@ -1046,189 +1133,185 @@
       <c r="F17" s="6"/>
       <c r="G17" s="7"/>
     </row>
-    <row r="18" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A18" s="19"/>
-      <c r="B18" s="9" t="s">
+    <row r="18" spans="1:7" s="2" customFormat="1" ht="47.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A18" s="20"/>
+      <c r="B18" s="19" t="s">
+        <v>98</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="E18" s="19"/>
+      <c r="F18" s="19"/>
+      <c r="G18" s="7"/>
+    </row>
+    <row r="19" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A19" s="20"/>
+      <c r="B19" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D19" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E19" s="12">
+        <v>1</v>
+      </c>
+      <c r="F19" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="D18" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="E18" s="12">
-        <v>1</v>
-      </c>
-      <c r="F18" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G18" s="7"/>
-    </row>
-    <row r="19" spans="1:7" s="2" customFormat="1" ht="48.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A19" s="19"/>
-      <c r="B19" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C19" s="9" t="s">
+      <c r="G19" s="7"/>
+    </row>
+    <row r="20" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A20" s="20"/>
+      <c r="B20" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="D19" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="E19" s="12">
-        <v>1</v>
-      </c>
-      <c r="F19" s="9" t="s">
+      <c r="C20" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="D20" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="E20" s="12">
+        <v>1</v>
+      </c>
+      <c r="F20" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="G20" s="7"/>
+    </row>
+    <row r="21" spans="1:7" s="2" customFormat="1" ht="48.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A21" s="20"/>
+      <c r="B21" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="C21" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="G19" s="7"/>
-    </row>
-    <row r="20" spans="1:7" s="2" customFormat="1" ht="48.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A20" s="19"/>
-      <c r="B20" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="C20" s="9" t="s">
+      <c r="D21" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="E21" s="12">
+        <v>1</v>
+      </c>
+      <c r="F21" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="D20" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="E20" s="12">
-        <v>1</v>
-      </c>
-      <c r="F20" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="G20" s="7"/>
-    </row>
-    <row r="21" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A21" s="19"/>
-      <c r="B21" s="9" t="s">
+      <c r="G21" s="7"/>
+    </row>
+    <row r="22" spans="1:7" s="2" customFormat="1" ht="48.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A22" s="20"/>
+      <c r="B22" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="C21" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="D21" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="E21" s="12">
-        <v>1</v>
-      </c>
-      <c r="F21" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="G21" s="7"/>
-    </row>
-    <row r="22" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A22" s="19"/>
-      <c r="B22" s="9" t="s">
+      <c r="C22" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="D22" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="12">
+        <v>1</v>
+      </c>
+      <c r="F22" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="G22" s="7"/>
+    </row>
+    <row r="23" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A23" s="20"/>
+      <c r="B23" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C23" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="C22" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="D22" s="9" t="s">
+      <c r="D23" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="E23" s="12">
+        <v>1</v>
+      </c>
+      <c r="F23" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="E22" s="12">
-        <v>1</v>
-      </c>
-      <c r="F22" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="G22" s="7"/>
-    </row>
-    <row r="23" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A23" s="19"/>
-      <c r="B23" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="C23" s="9" t="s">
+      <c r="G23" s="7"/>
+    </row>
+    <row r="24" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A24" s="20"/>
+      <c r="B24" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="D24" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="E24" s="12">
+        <v>1</v>
+      </c>
+      <c r="F24" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="D23" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="E23" s="12">
-        <v>1</v>
-      </c>
-      <c r="F23" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="G23" s="7"/>
-    </row>
-    <row r="24" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A24" s="19"/>
-      <c r="B24" s="9" t="s">
+      <c r="G24" s="7"/>
+    </row>
+    <row r="25" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A25" s="20"/>
+      <c r="B25" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="C25" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="D25" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="C24" s="9" t="s">
+      <c r="E25" s="12">
+        <v>1</v>
+      </c>
+      <c r="F25" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="G25" s="7"/>
+    </row>
+    <row r="26" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A26" s="20"/>
+      <c r="B26" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="C26" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="D26" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="E26" s="12">
+        <v>1</v>
+      </c>
+      <c r="F26" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G26" s="7"/>
+    </row>
+    <row r="27" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A27" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="B27" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="C27" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="D24" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="E24" s="12">
-        <v>1</v>
-      </c>
-      <c r="F24" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="G24" s="7"/>
-    </row>
-    <row r="25" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A25" s="19" t="s">
-        <v>53</v>
-      </c>
-      <c r="B25" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="C25" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="D25" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="E25" s="12">
-        <v>1</v>
-      </c>
-      <c r="F25" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="G25" s="7"/>
-    </row>
-    <row r="26" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A26" s="19"/>
-      <c r="B26" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="C26" s="9" t="s">
+      <c r="D27" s="9" t="s">
         <v>60</v>
-      </c>
-      <c r="D26" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="E26" s="12">
-        <v>1</v>
-      </c>
-      <c r="F26" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="G26" s="7"/>
-    </row>
-    <row r="27" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A27" s="19"/>
-      <c r="B27" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="C27" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="D27" s="9" t="s">
-        <v>56</v>
       </c>
       <c r="E27" s="12">
         <v>1</v>
@@ -1239,81 +1322,109 @@
       <c r="G27" s="7"/>
     </row>
     <row r="28" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A28" s="19"/>
-      <c r="B28" s="16" t="s">
-        <v>75</v>
-      </c>
-      <c r="C28" s="16" t="s">
-        <v>76</v>
-      </c>
-      <c r="D28" s="16" t="s">
-        <v>76</v>
-      </c>
-      <c r="E28" s="17">
-        <v>1</v>
-      </c>
-      <c r="F28" s="16" t="s">
-        <v>80</v>
+      <c r="A28" s="20"/>
+      <c r="B28" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="C28" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="D28" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="E28" s="12">
+        <v>1</v>
+      </c>
+      <c r="F28" s="9" t="s">
+        <v>62</v>
       </c>
       <c r="G28" s="7"/>
     </row>
-    <row r="29" spans="1:7" s="2" customFormat="1" ht="33.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A29" s="19" t="s">
-        <v>15</v>
-      </c>
+    <row r="29" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A29" s="20"/>
       <c r="B29" s="16" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C29" s="16" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="D29" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="E29" s="17">
+        <v>1</v>
+      </c>
+      <c r="F29" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="G29" s="7"/>
+    </row>
+    <row r="30" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A30" s="20"/>
+      <c r="B30" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="C30" s="16" t="s">
+        <v>86</v>
+      </c>
+      <c r="D30" s="16" t="s">
+        <v>86</v>
+      </c>
+      <c r="E30" s="17">
+        <v>1</v>
+      </c>
+      <c r="F30" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="G30" s="7"/>
+    </row>
+    <row r="31" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A31" s="20"/>
+      <c r="B31" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="C31" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="D31" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="E31" s="12">
+        <v>1</v>
+      </c>
+      <c r="F31" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="E29" s="17">
-        <v>0.2</v>
-      </c>
-      <c r="F29" s="16"/>
-      <c r="G29" s="7"/>
-    </row>
-    <row r="30" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A30" s="19"/>
-      <c r="B30" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="C30" s="6"/>
-      <c r="D30" s="6"/>
-      <c r="E30" s="6"/>
-      <c r="F30" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="G30" s="7"/>
-    </row>
-    <row r="31" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A31" s="6"/>
-      <c r="B31" s="6"/>
-      <c r="C31" s="6"/>
-      <c r="D31" s="6"/>
-      <c r="E31" s="6"/>
-      <c r="F31" s="6"/>
       <c r="G31" s="7"/>
     </row>
-    <row r="32" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A32" s="6"/>
-      <c r="B32" s="6"/>
+    <row r="32" spans="1:7" s="2" customFormat="1" ht="33.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A32" s="20"/>
+      <c r="B32" s="6" t="s">
+        <v>45</v>
+      </c>
       <c r="C32" s="6"/>
       <c r="D32" s="6"/>
       <c r="E32" s="6"/>
-      <c r="F32" s="6"/>
+      <c r="F32" s="6" t="s">
+        <v>46</v>
+      </c>
       <c r="G32" s="7"/>
     </row>
-    <row r="33" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A33" s="6"/>
-      <c r="B33" s="6"/>
-      <c r="C33" s="6"/>
-      <c r="D33" s="6"/>
-      <c r="E33" s="6"/>
-      <c r="F33" s="6"/>
+    <row r="33" spans="1:7" s="2" customFormat="1" ht="33.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A33" s="19" t="s">
+        <v>83</v>
+      </c>
+      <c r="B33" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="C33" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="D33" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="E33" s="17"/>
+      <c r="F33" s="16"/>
       <c r="G33" s="7"/>
     </row>
     <row r="34" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.15">
@@ -1470,35 +1581,58 @@
       <c r="G50" s="7"/>
     </row>
     <row r="51" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A51" s="3"/>
+      <c r="A51" s="6"/>
       <c r="B51" s="6"/>
       <c r="C51" s="6"/>
       <c r="D51" s="6"/>
       <c r="E51" s="6"/>
       <c r="F51" s="6"/>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="F52" s="3"/>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="F53" s="1"/>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="F54" s="1"/>
+      <c r="G51" s="7"/>
+    </row>
+    <row r="52" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A52" s="6"/>
+      <c r="B52" s="6"/>
+      <c r="C52" s="6"/>
+      <c r="D52" s="6"/>
+      <c r="E52" s="6"/>
+      <c r="F52" s="6"/>
+      <c r="G52" s="7"/>
+    </row>
+    <row r="53" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A53" s="6"/>
+      <c r="B53" s="6"/>
+      <c r="C53" s="6"/>
+      <c r="D53" s="6"/>
+      <c r="E53" s="6"/>
+      <c r="F53" s="6"/>
+      <c r="G53" s="7"/>
+    </row>
+    <row r="54" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A54" s="3"/>
+      <c r="B54" s="3"/>
+      <c r="C54" s="3"/>
+      <c r="D54" s="3"/>
+      <c r="E54" s="3"/>
+      <c r="F54" s="3"/>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.15">
       <c r="F55" s="1"/>
     </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="F56" s="1"/>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="F57" s="1"/>
+    </row>
   </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="A29:A30"/>
+  <mergeCells count="7">
     <mergeCell ref="A1:G3"/>
-    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="A9:A11"/>
     <mergeCell ref="A5:A6"/>
     <mergeCell ref="A7:A8"/>
-    <mergeCell ref="A17:A24"/>
-    <mergeCell ref="A25:A28"/>
-    <mergeCell ref="A12:A16"/>
+    <mergeCell ref="A27:A32"/>
+    <mergeCell ref="A17:A26"/>
+    <mergeCell ref="A13:A16"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/1.xlsx
+++ b/1.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="103">
   <si>
     <t>模块</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -428,6 +428,18 @@
   </si>
   <si>
     <t>26.5.8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>图标也许会优化</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>开箱逻辑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>26.5.9</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -507,7 +519,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -551,7 +563,6 @@
     <xf numFmtId="9" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -568,6 +579,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -871,7 +891,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G57"/>
+  <dimension ref="A1:G58"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="22.625" style="3" customWidth="1"/>
@@ -934,7 +954,7 @@
       <c r="G4" s="5"/>
     </row>
     <row r="5" spans="1:7" s="2" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="20" t="s">
+      <c r="A5" s="22" t="s">
         <v>2</v>
       </c>
       <c r="B5" s="9" t="s">
@@ -955,7 +975,8 @@
       <c r="G5" s="7"/>
     </row>
     <row r="6" spans="1:7" ht="30.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="20"/>
+      <c r="A6" s="22"/>
+      <c r="F6" s="20"/>
     </row>
     <row r="7" spans="1:7" ht="29.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="21" t="s">
@@ -964,6 +985,7 @@
       <c r="B7" s="3" t="s">
         <v>91</v>
       </c>
+      <c r="F7" s="20"/>
     </row>
     <row r="8" spans="1:7" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="21"/>
@@ -976,464 +998,477 @@
       <c r="D8" s="3" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" ht="38.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="21" t="s">
+      <c r="E8" s="23">
+        <v>0.6</v>
+      </c>
+      <c r="F8" s="20"/>
+    </row>
+    <row r="9" spans="1:7" ht="27" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A9" s="21"/>
+      <c r="B9" s="20" t="s">
+        <v>101</v>
+      </c>
+      <c r="C9" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="D9" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="E9" s="20"/>
+      <c r="F9" s="20"/>
+    </row>
+    <row r="10" spans="1:7" ht="38.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A10" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="B9" s="13" t="s">
+      <c r="B10" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C9" s="13" t="s">
+      <c r="C10" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="D9" s="13" t="s">
+      <c r="D10" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="E9" s="14">
-        <v>1</v>
-      </c>
-      <c r="F9" s="15"/>
-    </row>
-    <row r="10" spans="1:7" ht="38.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="21"/>
-      <c r="B10" s="3" t="s">
+      <c r="E10" s="14">
+        <v>1</v>
+      </c>
+      <c r="F10" s="13"/>
+    </row>
+    <row r="11" spans="1:7" ht="38.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A11" s="21"/>
+      <c r="B11" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F10" s="6"/>
-    </row>
-    <row r="11" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A11" s="21"/>
-      <c r="B11" s="9" t="s">
+      <c r="F11" s="19"/>
+    </row>
+    <row r="12" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A12" s="21"/>
+      <c r="B12" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="C11" s="10" t="s">
+      <c r="C12" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="D11" s="11" t="s">
+      <c r="D12" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="E11" s="12">
-        <v>1</v>
-      </c>
-      <c r="F11" s="9" t="s">
+      <c r="E12" s="12">
+        <v>1</v>
+      </c>
+      <c r="F12" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="G11" s="7"/>
-    </row>
-    <row r="12" spans="1:7" s="2" customFormat="1" ht="69.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A12" s="6" t="s">
+      <c r="G12" s="7"/>
+    </row>
+    <row r="13" spans="1:7" s="2" customFormat="1" ht="69.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A13" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B13" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C13" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="D12" s="6" t="s">
+      <c r="D13" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="E12" s="18">
-        <v>1</v>
-      </c>
-      <c r="F12" s="6" t="s">
+      <c r="E13" s="17">
+        <v>1</v>
+      </c>
+      <c r="F13" s="19" t="s">
         <v>81</v>
       </c>
-      <c r="G12" s="7"/>
-    </row>
-    <row r="13" spans="1:7" s="2" customFormat="1" ht="47.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A13" s="20" t="s">
+      <c r="G13" s="7"/>
+    </row>
+    <row r="14" spans="1:7" s="2" customFormat="1" ht="47.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A14" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="B13" s="9" t="s">
+      <c r="B14" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="C13" s="9" t="s">
+      <c r="C14" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="D13" s="9" t="s">
+      <c r="D14" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="E13" s="12">
-        <v>1</v>
-      </c>
-      <c r="F13" s="9" t="s">
+      <c r="E14" s="12">
+        <v>1</v>
+      </c>
+      <c r="F14" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="G13" s="7"/>
-    </row>
-    <row r="14" spans="1:7" s="2" customFormat="1" ht="47.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A14" s="20"/>
-      <c r="B14" s="16" t="s">
+      <c r="G14" s="7"/>
+    </row>
+    <row r="15" spans="1:7" s="2" customFormat="1" ht="47.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A15" s="22"/>
+      <c r="B15" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="C14" s="16" t="s">
+      <c r="C15" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="D14" s="16" t="s">
+      <c r="D15" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="E14" s="17">
-        <v>1</v>
-      </c>
-      <c r="F14" s="16" t="s">
+      <c r="E15" s="16">
+        <v>1</v>
+      </c>
+      <c r="F15" s="15" t="s">
         <v>76</v>
       </c>
-      <c r="G14" s="7"/>
-    </row>
-    <row r="15" spans="1:7" s="2" customFormat="1" ht="47.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A15" s="20"/>
-      <c r="B15" s="16" t="s">
+      <c r="G15" s="7"/>
+    </row>
+    <row r="16" spans="1:7" s="2" customFormat="1" ht="47.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A16" s="22"/>
+      <c r="B16" s="15" t="s">
         <v>87</v>
       </c>
-      <c r="C15" s="16" t="s">
+      <c r="C16" s="15" t="s">
         <v>88</v>
       </c>
-      <c r="D15" s="16" t="s">
+      <c r="D16" s="15" t="s">
         <v>88</v>
       </c>
-      <c r="E15" s="17">
-        <v>1</v>
-      </c>
-      <c r="F15" s="16" t="s">
+      <c r="E16" s="16">
+        <v>1</v>
+      </c>
+      <c r="F16" s="15" t="s">
         <v>90</v>
       </c>
-      <c r="G15" s="7"/>
-    </row>
-    <row r="16" spans="1:7" s="2" customFormat="1" ht="47.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A16" s="20"/>
-      <c r="B16" s="16" t="s">
+      <c r="G16" s="7"/>
+    </row>
+    <row r="17" spans="1:7" s="2" customFormat="1" ht="47.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A17" s="22"/>
+      <c r="B17" s="15" t="s">
         <v>74</v>
       </c>
-      <c r="C16" s="16" t="s">
+      <c r="C17" s="15" t="s">
         <v>75</v>
       </c>
-      <c r="D16" s="16" t="s">
+      <c r="D17" s="15" t="s">
         <v>78</v>
       </c>
-      <c r="E16" s="17">
-        <v>1</v>
-      </c>
-      <c r="F16" s="16" t="s">
+      <c r="E17" s="16">
+        <v>1</v>
+      </c>
+      <c r="F17" s="15" t="s">
         <v>79</v>
       </c>
-      <c r="G16" s="7"/>
-    </row>
-    <row r="17" spans="1:7" s="2" customFormat="1" ht="47.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A17" s="20" t="s">
+      <c r="G17" s="7"/>
+    </row>
+    <row r="18" spans="1:7" s="2" customFormat="1" ht="47.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A18" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="B18" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="C17" s="8"/>
-      <c r="D17" s="8"/>
-      <c r="E17" s="6"/>
-      <c r="F17" s="6"/>
-      <c r="G17" s="7"/>
-    </row>
-    <row r="18" spans="1:7" s="2" customFormat="1" ht="47.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A18" s="20"/>
-      <c r="B18" s="19" t="s">
-        <v>98</v>
-      </c>
-      <c r="C18" s="8" t="s">
-        <v>99</v>
-      </c>
-      <c r="D18" s="8" t="s">
-        <v>99</v>
-      </c>
-      <c r="E18" s="19"/>
+      <c r="C18" s="8"/>
+      <c r="D18" s="8"/>
+      <c r="E18" s="6"/>
       <c r="F18" s="19"/>
       <c r="G18" s="7"/>
     </row>
-    <row r="19" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A19" s="20"/>
-      <c r="B19" s="9" t="s">
+    <row r="19" spans="1:7" s="2" customFormat="1" ht="47.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A19" s="22"/>
+      <c r="B19" s="18" t="s">
+        <v>98</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="D19" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="E19" s="18"/>
+      <c r="F19" s="19"/>
+      <c r="G19" s="7"/>
+    </row>
+    <row r="20" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A20" s="22"/>
+      <c r="B20" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="C19" s="9" t="s">
+      <c r="C20" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="D19" s="11" t="s">
+      <c r="D20" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="E19" s="12">
-        <v>1</v>
-      </c>
-      <c r="F19" s="9" t="s">
+      <c r="E20" s="12">
+        <v>1</v>
+      </c>
+      <c r="F20" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="G19" s="7"/>
-    </row>
-    <row r="20" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A20" s="20"/>
-      <c r="B20" s="9" t="s">
+      <c r="G20" s="7"/>
+    </row>
+    <row r="21" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A21" s="22"/>
+      <c r="B21" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="C20" s="9" t="s">
+      <c r="C21" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="D20" s="9" t="s">
+      <c r="D21" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="E20" s="12">
-        <v>1</v>
-      </c>
-      <c r="F20" s="9" t="s">
+      <c r="E21" s="12">
+        <v>1</v>
+      </c>
+      <c r="F21" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="G20" s="7"/>
-    </row>
-    <row r="21" spans="1:7" s="2" customFormat="1" ht="48.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A21" s="20"/>
-      <c r="B21" s="9" t="s">
+      <c r="G21" s="7"/>
+    </row>
+    <row r="22" spans="1:7" s="2" customFormat="1" ht="48.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A22" s="22"/>
+      <c r="B22" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="C21" s="9" t="s">
+      <c r="C22" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="D21" s="9" t="s">
+      <c r="D22" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="E21" s="12">
-        <v>1</v>
-      </c>
-      <c r="F21" s="9" t="s">
+      <c r="E22" s="12">
+        <v>1</v>
+      </c>
+      <c r="F22" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="G21" s="7"/>
-    </row>
-    <row r="22" spans="1:7" s="2" customFormat="1" ht="48.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A22" s="20"/>
-      <c r="B22" s="9" t="s">
+      <c r="G22" s="7"/>
+    </row>
+    <row r="23" spans="1:7" s="2" customFormat="1" ht="48.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A23" s="22"/>
+      <c r="B23" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="C22" s="9" t="s">
+      <c r="C23" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="9" t="s">
+      <c r="D23" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="E22" s="12">
-        <v>1</v>
-      </c>
-      <c r="F22" s="9" t="s">
+      <c r="E23" s="12">
+        <v>1</v>
+      </c>
+      <c r="F23" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="G22" s="7"/>
-    </row>
-    <row r="23" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A23" s="20"/>
-      <c r="B23" s="9" t="s">
+      <c r="G23" s="7"/>
+    </row>
+    <row r="24" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A24" s="22"/>
+      <c r="B24" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="C23" s="9" t="s">
+      <c r="C24" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="D23" s="9" t="s">
+      <c r="D24" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="E23" s="12">
-        <v>1</v>
-      </c>
-      <c r="F23" s="9" t="s">
+      <c r="E24" s="12">
+        <v>1</v>
+      </c>
+      <c r="F24" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="G23" s="7"/>
-    </row>
-    <row r="24" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A24" s="20"/>
-      <c r="B24" s="9" t="s">
+      <c r="G24" s="7"/>
+    </row>
+    <row r="25" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A25" s="22"/>
+      <c r="B25" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="C24" s="9" t="s">
+      <c r="C25" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="D24" s="9" t="s">
+      <c r="D25" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="E24" s="12">
-        <v>1</v>
-      </c>
-      <c r="F24" s="9" t="s">
+      <c r="E25" s="12">
+        <v>1</v>
+      </c>
+      <c r="F25" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="G24" s="7"/>
-    </row>
-    <row r="25" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A25" s="20"/>
-      <c r="B25" s="9" t="s">
+      <c r="G25" s="7"/>
+    </row>
+    <row r="26" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A26" s="22"/>
+      <c r="B26" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="C25" s="9" t="s">
+      <c r="C26" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="D25" s="9" t="s">
+      <c r="D26" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="E25" s="12">
-        <v>1</v>
-      </c>
-      <c r="F25" s="9" t="s">
+      <c r="E26" s="12">
+        <v>1</v>
+      </c>
+      <c r="F26" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="G25" s="7"/>
-    </row>
-    <row r="26" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A26" s="20"/>
-      <c r="B26" s="9" t="s">
+      <c r="G26" s="7"/>
+    </row>
+    <row r="27" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A27" s="22"/>
+      <c r="B27" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="C26" s="9" t="s">
+      <c r="C27" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="D26" s="9" t="s">
+      <c r="D27" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="E26" s="12">
-        <v>1</v>
-      </c>
-      <c r="F26" s="9" t="s">
+      <c r="E27" s="12">
+        <v>1</v>
+      </c>
+      <c r="F27" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="G26" s="7"/>
-    </row>
-    <row r="27" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A27" s="20" t="s">
+      <c r="G27" s="7"/>
+    </row>
+    <row r="28" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A28" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="B27" s="9" t="s">
+      <c r="B28" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="C27" s="9" t="s">
+      <c r="C28" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="D27" s="9" t="s">
+      <c r="D28" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="E27" s="12">
-        <v>1</v>
-      </c>
-      <c r="F27" s="9" t="s">
+      <c r="E28" s="12">
+        <v>1</v>
+      </c>
+      <c r="F28" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="G27" s="7"/>
-    </row>
-    <row r="28" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A28" s="20"/>
-      <c r="B28" s="9" t="s">
+      <c r="G28" s="7"/>
+    </row>
+    <row r="29" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A29" s="22"/>
+      <c r="B29" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="C28" s="9" t="s">
+      <c r="C29" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="D28" s="9" t="s">
+      <c r="D29" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="E28" s="12">
-        <v>1</v>
-      </c>
-      <c r="F28" s="9" t="s">
+      <c r="E29" s="12">
+        <v>1</v>
+      </c>
+      <c r="F29" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="G28" s="7"/>
-    </row>
-    <row r="29" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A29" s="20"/>
-      <c r="B29" s="16" t="s">
+      <c r="G29" s="7"/>
+    </row>
+    <row r="30" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A30" s="22"/>
+      <c r="B30" s="15" t="s">
         <v>72</v>
       </c>
-      <c r="C29" s="16" t="s">
+      <c r="C30" s="15" t="s">
         <v>73</v>
       </c>
-      <c r="D29" s="16" t="s">
+      <c r="D30" s="15" t="s">
         <v>73</v>
       </c>
-      <c r="E29" s="17">
-        <v>1</v>
-      </c>
-      <c r="F29" s="16" t="s">
+      <c r="E30" s="16">
+        <v>1</v>
+      </c>
+      <c r="F30" s="15" t="s">
         <v>77</v>
       </c>
-      <c r="G29" s="7"/>
-    </row>
-    <row r="30" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A30" s="20"/>
-      <c r="B30" s="16" t="s">
+      <c r="G30" s="7"/>
+    </row>
+    <row r="31" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A31" s="22"/>
+      <c r="B31" s="15" t="s">
         <v>84</v>
       </c>
-      <c r="C30" s="16" t="s">
+      <c r="C31" s="15" t="s">
         <v>86</v>
       </c>
-      <c r="D30" s="16" t="s">
+      <c r="D31" s="15" t="s">
         <v>86</v>
       </c>
-      <c r="E30" s="17">
-        <v>1</v>
-      </c>
-      <c r="F30" s="16" t="s">
+      <c r="E31" s="16">
+        <v>1</v>
+      </c>
+      <c r="F31" s="15" t="s">
         <v>89</v>
       </c>
-      <c r="G30" s="7"/>
-    </row>
-    <row r="31" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A31" s="20"/>
-      <c r="B31" s="9" t="s">
+      <c r="G31" s="7"/>
+    </row>
+    <row r="32" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A32" s="22"/>
+      <c r="B32" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="C31" s="9" t="s">
+      <c r="C32" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="D31" s="9" t="s">
+      <c r="D32" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="E31" s="12">
-        <v>1</v>
-      </c>
-      <c r="F31" s="9" t="s">
+      <c r="E32" s="12">
+        <v>1</v>
+      </c>
+      <c r="F32" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="G31" s="7"/>
-    </row>
-    <row r="32" spans="1:7" s="2" customFormat="1" ht="33.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A32" s="20"/>
-      <c r="B32" s="6" t="s">
+      <c r="G32" s="7"/>
+    </row>
+    <row r="33" spans="1:7" s="2" customFormat="1" ht="33.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A33" s="22"/>
+      <c r="B33" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="C32" s="6"/>
-      <c r="D32" s="6"/>
-      <c r="E32" s="6"/>
-      <c r="F32" s="6" t="s">
+      <c r="C33" s="6"/>
+      <c r="D33" s="6"/>
+      <c r="E33" s="6"/>
+      <c r="F33" s="19" t="s">
         <v>46</v>
       </c>
-      <c r="G32" s="7"/>
-    </row>
-    <row r="33" spans="1:7" s="2" customFormat="1" ht="33.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A33" s="19" t="s">
+      <c r="G33" s="7"/>
+    </row>
+    <row r="34" spans="1:7" s="2" customFormat="1" ht="33.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A34" s="18" t="s">
         <v>83</v>
       </c>
-      <c r="B33" s="16" t="s">
+      <c r="B34" s="15" t="s">
         <v>92</v>
       </c>
-      <c r="C33" s="16" t="s">
+      <c r="C34" s="15" t="s">
         <v>93</v>
       </c>
-      <c r="D33" s="16" t="s">
+      <c r="D34" s="15" t="s">
         <v>94</v>
       </c>
-      <c r="E33" s="17"/>
-      <c r="F33" s="16"/>
-      <c r="G33" s="7"/>
-    </row>
-    <row r="34" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A34" s="6"/>
-      <c r="B34" s="6"/>
-      <c r="C34" s="6"/>
-      <c r="D34" s="6"/>
-      <c r="E34" s="6"/>
-      <c r="F34" s="6"/>
+      <c r="E34" s="16">
+        <v>1</v>
+      </c>
+      <c r="F34" s="15" t="s">
+        <v>100</v>
+      </c>
       <c r="G34" s="7"/>
     </row>
     <row r="35" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.15">
@@ -1608,31 +1643,40 @@
       <c r="G53" s="7"/>
     </row>
     <row r="54" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A54" s="3"/>
-      <c r="B54" s="3"/>
-      <c r="C54" s="3"/>
-      <c r="D54" s="3"/>
-      <c r="E54" s="3"/>
-      <c r="F54" s="3"/>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="F55" s="1"/>
+      <c r="A54" s="6"/>
+      <c r="B54" s="6"/>
+      <c r="C54" s="6"/>
+      <c r="D54" s="6"/>
+      <c r="E54" s="6"/>
+      <c r="F54" s="6"/>
+      <c r="G54" s="7"/>
+    </row>
+    <row r="55" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A55" s="3"/>
+      <c r="B55" s="3"/>
+      <c r="C55" s="3"/>
+      <c r="D55" s="3"/>
+      <c r="E55" s="3"/>
+      <c r="F55" s="3"/>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.15">
       <c r="F56" s="1"/>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.15">
       <c r="F57" s="1"/>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="F58" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="7">
     <mergeCell ref="A1:G3"/>
-    <mergeCell ref="A9:A11"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="A5:A6"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="A27:A32"/>
-    <mergeCell ref="A17:A26"/>
-    <mergeCell ref="A13:A16"/>
+    <mergeCell ref="A28:A33"/>
+    <mergeCell ref="A18:A27"/>
+    <mergeCell ref="A14:A17"/>
+    <mergeCell ref="A7:A9"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/1.xlsx
+++ b/1.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="104">
   <si>
     <t>模块</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -440,6 +440,10 @@
   </si>
   <si>
     <t>26.5.9</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -581,14 +585,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -904,33 +908,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
-      <c r="G1" s="21"/>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A2" s="21"/>
-      <c r="B2" s="21"/>
-      <c r="C2" s="21"/>
-      <c r="D2" s="21"/>
-      <c r="E2" s="21"/>
-      <c r="F2" s="21"/>
-      <c r="G2" s="21"/>
+      <c r="A2" s="22"/>
+      <c r="B2" s="22"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="22"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A3" s="21"/>
-      <c r="B3" s="21"/>
-      <c r="C3" s="21"/>
-      <c r="D3" s="21"/>
-      <c r="E3" s="21"/>
-      <c r="F3" s="21"/>
-      <c r="G3" s="21"/>
+      <c r="A3" s="22"/>
+      <c r="B3" s="22"/>
+      <c r="C3" s="22"/>
+      <c r="D3" s="22"/>
+      <c r="E3" s="22"/>
+      <c r="F3" s="22"/>
+      <c r="G3" s="22"/>
     </row>
     <row r="4" spans="1:7" s="2" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="4" t="s">
@@ -954,7 +958,7 @@
       <c r="G4" s="5"/>
     </row>
     <row r="5" spans="1:7" s="2" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="22" t="s">
+      <c r="A5" s="23" t="s">
         <v>2</v>
       </c>
       <c r="B5" s="9" t="s">
@@ -975,11 +979,11 @@
       <c r="G5" s="7"/>
     </row>
     <row r="6" spans="1:7" ht="30.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="22"/>
+      <c r="A6" s="23"/>
       <c r="F6" s="20"/>
     </row>
     <row r="7" spans="1:7" ht="29.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="21" t="s">
+      <c r="A7" s="22" t="s">
         <v>15</v>
       </c>
       <c r="B7" s="3" t="s">
@@ -988,7 +992,7 @@
       <c r="F7" s="20"/>
     </row>
     <row r="8" spans="1:7" ht="27" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="21"/>
+      <c r="A8" s="22"/>
       <c r="B8" s="3" t="s">
         <v>97</v>
       </c>
@@ -998,13 +1002,15 @@
       <c r="D8" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="E8" s="23">
-        <v>0.6</v>
-      </c>
-      <c r="F8" s="20"/>
+      <c r="E8" s="21">
+        <v>1</v>
+      </c>
+      <c r="F8" s="20" t="s">
+        <v>103</v>
+      </c>
     </row>
     <row r="9" spans="1:7" ht="27" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="21"/>
+      <c r="A9" s="22"/>
       <c r="B9" s="20" t="s">
         <v>101</v>
       </c>
@@ -1018,7 +1024,7 @@
       <c r="F9" s="20"/>
     </row>
     <row r="10" spans="1:7" ht="38.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="21" t="s">
+      <c r="A10" s="22" t="s">
         <v>26</v>
       </c>
       <c r="B10" s="13" t="s">
@@ -1036,14 +1042,14 @@
       <c r="F10" s="13"/>
     </row>
     <row r="11" spans="1:7" ht="38.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A11" s="21"/>
+      <c r="A11" s="22"/>
       <c r="B11" s="3" t="s">
         <v>28</v>
       </c>
       <c r="F11" s="19"/>
     </row>
     <row r="12" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A12" s="21"/>
+      <c r="A12" s="22"/>
       <c r="B12" s="9" t="s">
         <v>6</v>
       </c>
@@ -1083,7 +1089,7 @@
       <c r="G13" s="7"/>
     </row>
     <row r="14" spans="1:7" s="2" customFormat="1" ht="47.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A14" s="22" t="s">
+      <c r="A14" s="23" t="s">
         <v>10</v>
       </c>
       <c r="B14" s="9" t="s">
@@ -1104,7 +1110,7 @@
       <c r="G14" s="7"/>
     </row>
     <row r="15" spans="1:7" s="2" customFormat="1" ht="47.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A15" s="22"/>
+      <c r="A15" s="23"/>
       <c r="B15" s="15" t="s">
         <v>69</v>
       </c>
@@ -1123,7 +1129,7 @@
       <c r="G15" s="7"/>
     </row>
     <row r="16" spans="1:7" s="2" customFormat="1" ht="47.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A16" s="22"/>
+      <c r="A16" s="23"/>
       <c r="B16" s="15" t="s">
         <v>87</v>
       </c>
@@ -1142,7 +1148,7 @@
       <c r="G16" s="7"/>
     </row>
     <row r="17" spans="1:7" s="2" customFormat="1" ht="47.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A17" s="22"/>
+      <c r="A17" s="23"/>
       <c r="B17" s="15" t="s">
         <v>74</v>
       </c>
@@ -1161,7 +1167,7 @@
       <c r="G17" s="7"/>
     </row>
     <row r="18" spans="1:7" s="2" customFormat="1" ht="47.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A18" s="22" t="s">
+      <c r="A18" s="23" t="s">
         <v>8</v>
       </c>
       <c r="B18" s="6" t="s">
@@ -1174,7 +1180,7 @@
       <c r="G18" s="7"/>
     </row>
     <row r="19" spans="1:7" s="2" customFormat="1" ht="47.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A19" s="22"/>
+      <c r="A19" s="23"/>
       <c r="B19" s="18" t="s">
         <v>98</v>
       </c>
@@ -1189,7 +1195,7 @@
       <c r="G19" s="7"/>
     </row>
     <row r="20" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A20" s="22"/>
+      <c r="A20" s="23"/>
       <c r="B20" s="9" t="s">
         <v>24</v>
       </c>
@@ -1208,7 +1214,7 @@
       <c r="G20" s="7"/>
     </row>
     <row r="21" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A21" s="22"/>
+      <c r="A21" s="23"/>
       <c r="B21" s="9" t="s">
         <v>33</v>
       </c>
@@ -1227,7 +1233,7 @@
       <c r="G21" s="7"/>
     </row>
     <row r="22" spans="1:7" s="2" customFormat="1" ht="48.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A22" s="22"/>
+      <c r="A22" s="23"/>
       <c r="B22" s="9" t="s">
         <v>38</v>
       </c>
@@ -1246,7 +1252,7 @@
       <c r="G22" s="7"/>
     </row>
     <row r="23" spans="1:7" s="2" customFormat="1" ht="48.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A23" s="22"/>
+      <c r="A23" s="23"/>
       <c r="B23" s="9" t="s">
         <v>9</v>
       </c>
@@ -1265,7 +1271,7 @@
       <c r="G23" s="7"/>
     </row>
     <row r="24" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A24" s="22"/>
+      <c r="A24" s="23"/>
       <c r="B24" s="9" t="s">
         <v>31</v>
       </c>
@@ -1284,7 +1290,7 @@
       <c r="G24" s="7"/>
     </row>
     <row r="25" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A25" s="22"/>
+      <c r="A25" s="23"/>
       <c r="B25" s="9" t="s">
         <v>47</v>
       </c>
@@ -1303,7 +1309,7 @@
       <c r="G25" s="7"/>
     </row>
     <row r="26" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A26" s="22"/>
+      <c r="A26" s="23"/>
       <c r="B26" s="9" t="s">
         <v>55</v>
       </c>
@@ -1322,7 +1328,7 @@
       <c r="G26" s="7"/>
     </row>
     <row r="27" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A27" s="22"/>
+      <c r="A27" s="23"/>
       <c r="B27" s="9" t="s">
         <v>67</v>
       </c>
@@ -1341,7 +1347,7 @@
       <c r="G27" s="7"/>
     </row>
     <row r="28" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A28" s="22" t="s">
+      <c r="A28" s="23" t="s">
         <v>51</v>
       </c>
       <c r="B28" s="9" t="s">
@@ -1362,7 +1368,7 @@
       <c r="G28" s="7"/>
     </row>
     <row r="29" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A29" s="22"/>
+      <c r="A29" s="23"/>
       <c r="B29" s="9" t="s">
         <v>52</v>
       </c>
@@ -1381,7 +1387,7 @@
       <c r="G29" s="7"/>
     </row>
     <row r="30" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A30" s="22"/>
+      <c r="A30" s="23"/>
       <c r="B30" s="15" t="s">
         <v>72</v>
       </c>
@@ -1400,7 +1406,7 @@
       <c r="G30" s="7"/>
     </row>
     <row r="31" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A31" s="22"/>
+      <c r="A31" s="23"/>
       <c r="B31" s="15" t="s">
         <v>84</v>
       </c>
@@ -1419,7 +1425,7 @@
       <c r="G31" s="7"/>
     </row>
     <row r="32" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A32" s="22"/>
+      <c r="A32" s="23"/>
       <c r="B32" s="9" t="s">
         <v>71</v>
       </c>
@@ -1438,7 +1444,7 @@
       <c r="G32" s="7"/>
     </row>
     <row r="33" spans="1:7" s="2" customFormat="1" ht="33.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A33" s="22"/>
+      <c r="A33" s="23"/>
       <c r="B33" s="6" t="s">
         <v>45</v>
       </c>

--- a/1.xlsx
+++ b/1.xlsx
@@ -1190,7 +1190,9 @@
       <c r="D19" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="E19" s="18"/>
+      <c r="E19" s="17">
+        <v>0.5</v>
+      </c>
       <c r="F19" s="19"/>
       <c r="G19" s="7"/>
     </row>

--- a/1.xlsx
+++ b/1.xlsx
@@ -4,19 +4,20 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9303"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="2"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="轨道核心" sheetId="4" r:id="rId2"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId3"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId4"/>
   </sheets>
   <calcPr calcId="145621"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="139">
   <si>
     <t>模块</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -569,6 +570,48 @@
   </si>
   <si>
     <t>《轨道》核心，角色周围有固定数量的几何刀片（如3个）持续环绕旋转刀片接触到敌人时造成伤害，并小幅击退</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>核心线速度与攻速、范围的关系</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>26.6.14</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>26.6.15</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>敌人的碰撞击退根据核心线速度修正</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>26.6.16</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>26.6.16</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>《几何竞技场》开发规划</t>
+    </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -664,7 +707,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -740,6 +783,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1065,33 +1114,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="28" t="s">
         <v>117</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26"/>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A2" s="26"/>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
-      <c r="G2" s="26"/>
+      <c r="A2" s="28"/>
+      <c r="B2" s="28"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
+      <c r="F2" s="28"/>
+      <c r="G2" s="28"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A3" s="26"/>
-      <c r="B3" s="26"/>
-      <c r="C3" s="26"/>
-      <c r="D3" s="26"/>
-      <c r="E3" s="26"/>
-      <c r="F3" s="26"/>
-      <c r="G3" s="26"/>
+      <c r="A3" s="28"/>
+      <c r="B3" s="28"/>
+      <c r="C3" s="28"/>
+      <c r="D3" s="28"/>
+      <c r="E3" s="28"/>
+      <c r="F3" s="28"/>
+      <c r="G3" s="28"/>
     </row>
     <row r="4" spans="1:7" s="2" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="4" t="s">
@@ -1115,7 +1164,7 @@
       <c r="G4" s="5"/>
     </row>
     <row r="5" spans="1:7" s="2" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="27" t="s">
+      <c r="A5" s="29" t="s">
         <v>2</v>
       </c>
       <c r="B5" s="9" t="s">
@@ -1136,7 +1185,7 @@
       <c r="G5" s="7"/>
     </row>
     <row r="6" spans="1:7" ht="30.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="27"/>
+      <c r="A6" s="29"/>
       <c r="B6" s="3" t="s">
         <v>113</v>
       </c>
@@ -1154,7 +1203,7 @@
       </c>
     </row>
     <row r="7" spans="1:7" ht="48" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="26" t="s">
+      <c r="A7" s="28" t="s">
         <v>11</v>
       </c>
       <c r="B7" s="13" t="s">
@@ -1174,7 +1223,7 @@
       </c>
     </row>
     <row r="8" spans="1:7" ht="27" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="26"/>
+      <c r="A8" s="28"/>
       <c r="B8" s="3" t="s">
         <v>93</v>
       </c>
@@ -1192,7 +1241,7 @@
       </c>
     </row>
     <row r="9" spans="1:7" ht="27" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="26"/>
+      <c r="A9" s="28"/>
       <c r="B9" s="24" t="s">
         <v>122</v>
       </c>
@@ -1208,7 +1257,7 @@
       </c>
     </row>
     <row r="10" spans="1:7" ht="27" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="26"/>
+      <c r="A10" s="28"/>
       <c r="B10" s="20" t="s">
         <v>97</v>
       </c>
@@ -1226,7 +1275,7 @@
       </c>
     </row>
     <row r="11" spans="1:7" ht="38.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A11" s="26" t="s">
+      <c r="A11" s="28" t="s">
         <v>22</v>
       </c>
       <c r="B11" s="13" t="s">
@@ -1244,14 +1293,14 @@
       <c r="F11" s="13"/>
     </row>
     <row r="12" spans="1:7" ht="38.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A12" s="26"/>
+      <c r="A12" s="28"/>
       <c r="B12" s="3" t="s">
         <v>24</v>
       </c>
       <c r="F12" s="19"/>
     </row>
     <row r="13" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A13" s="26"/>
+      <c r="A13" s="28"/>
       <c r="B13" s="9" t="s">
         <v>5</v>
       </c>
@@ -1270,7 +1319,7 @@
       <c r="G13" s="7"/>
     </row>
     <row r="14" spans="1:7" s="2" customFormat="1" ht="69.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A14" s="27" t="s">
+      <c r="A14" s="29" t="s">
         <v>105</v>
       </c>
       <c r="B14" s="6" t="s">
@@ -1291,7 +1340,7 @@
       <c r="G14" s="7"/>
     </row>
     <row r="15" spans="1:7" s="2" customFormat="1" ht="47.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A15" s="27"/>
+      <c r="A15" s="29"/>
       <c r="B15" s="9" t="s">
         <v>25</v>
       </c>
@@ -1310,7 +1359,7 @@
       <c r="G15" s="7"/>
     </row>
     <row r="16" spans="1:7" s="2" customFormat="1" ht="47.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A16" s="27"/>
+      <c r="A16" s="29"/>
       <c r="B16" s="15" t="s">
         <v>65</v>
       </c>
@@ -1329,7 +1378,7 @@
       <c r="G16" s="7"/>
     </row>
     <row r="17" spans="1:7" s="2" customFormat="1" ht="47.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A17" s="27"/>
+      <c r="A17" s="29"/>
       <c r="B17" s="15" t="s">
         <v>83</v>
       </c>
@@ -1348,7 +1397,7 @@
       <c r="G17" s="7"/>
     </row>
     <row r="18" spans="1:7" s="2" customFormat="1" ht="47.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A18" s="27"/>
+      <c r="A18" s="29"/>
       <c r="B18" s="15" t="s">
         <v>70</v>
       </c>
@@ -1367,7 +1416,7 @@
       <c r="G18" s="7"/>
     </row>
     <row r="19" spans="1:7" s="2" customFormat="1" ht="47.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A19" s="27" t="s">
+      <c r="A19" s="29" t="s">
         <v>104</v>
       </c>
       <c r="B19" s="6" t="s">
@@ -1380,7 +1429,7 @@
       <c r="G19" s="7"/>
     </row>
     <row r="20" spans="1:7" s="2" customFormat="1" ht="47.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A20" s="27"/>
+      <c r="A20" s="29"/>
       <c r="B20" s="22" t="s">
         <v>100</v>
       </c>
@@ -1399,7 +1448,7 @@
       <c r="G20" s="7"/>
     </row>
     <row r="21" spans="1:7" s="2" customFormat="1" ht="47.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A21" s="27"/>
+      <c r="A21" s="29"/>
       <c r="B21" s="18" t="s">
         <v>94</v>
       </c>
@@ -1418,7 +1467,7 @@
       <c r="G21" s="7"/>
     </row>
     <row r="22" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A22" s="27"/>
+      <c r="A22" s="29"/>
       <c r="B22" s="9" t="s">
         <v>20</v>
       </c>
@@ -1437,7 +1486,7 @@
       <c r="G22" s="7"/>
     </row>
     <row r="23" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A23" s="27"/>
+      <c r="A23" s="29"/>
       <c r="B23" s="9" t="s">
         <v>29</v>
       </c>
@@ -1456,7 +1505,7 @@
       <c r="G23" s="7"/>
     </row>
     <row r="24" spans="1:7" s="2" customFormat="1" ht="48.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A24" s="27"/>
+      <c r="A24" s="29"/>
       <c r="B24" s="9" t="s">
         <v>34</v>
       </c>
@@ -1475,7 +1524,7 @@
       <c r="G24" s="7"/>
     </row>
     <row r="25" spans="1:7" s="2" customFormat="1" ht="48.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A25" s="27"/>
+      <c r="A25" s="29"/>
       <c r="B25" s="9" t="s">
         <v>6</v>
       </c>
@@ -1494,7 +1543,7 @@
       <c r="G25" s="7"/>
     </row>
     <row r="26" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A26" s="27"/>
+      <c r="A26" s="29"/>
       <c r="B26" s="9" t="s">
         <v>27</v>
       </c>
@@ -1513,7 +1562,7 @@
       <c r="G26" s="7"/>
     </row>
     <row r="27" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A27" s="27"/>
+      <c r="A27" s="29"/>
       <c r="B27" s="9" t="s">
         <v>43</v>
       </c>
@@ -1532,7 +1581,7 @@
       <c r="G27" s="7"/>
     </row>
     <row r="28" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A28" s="27"/>
+      <c r="A28" s="29"/>
       <c r="B28" s="9" t="s">
         <v>51</v>
       </c>
@@ -1551,7 +1600,7 @@
       <c r="G28" s="7"/>
     </row>
     <row r="29" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A29" s="27"/>
+      <c r="A29" s="29"/>
       <c r="B29" s="9" t="s">
         <v>63</v>
       </c>
@@ -1570,7 +1619,7 @@
       <c r="G29" s="7"/>
     </row>
     <row r="30" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A30" s="27" t="s">
+      <c r="A30" s="29" t="s">
         <v>47</v>
       </c>
       <c r="B30" s="9" t="s">
@@ -1591,7 +1640,7 @@
       <c r="G30" s="7"/>
     </row>
     <row r="31" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A31" s="27"/>
+      <c r="A31" s="29"/>
       <c r="B31" s="9" t="s">
         <v>48</v>
       </c>
@@ -1610,7 +1659,7 @@
       <c r="G31" s="7"/>
     </row>
     <row r="32" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A32" s="27"/>
+      <c r="A32" s="29"/>
       <c r="B32" s="15" t="s">
         <v>68</v>
       </c>
@@ -1629,7 +1678,7 @@
       <c r="G32" s="7"/>
     </row>
     <row r="33" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A33" s="27"/>
+      <c r="A33" s="29"/>
       <c r="B33" s="15" t="s">
         <v>80</v>
       </c>
@@ -1648,7 +1697,7 @@
       <c r="G33" s="7"/>
     </row>
     <row r="34" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A34" s="27"/>
+      <c r="A34" s="29"/>
       <c r="B34" s="9" t="s">
         <v>67</v>
       </c>
@@ -1667,7 +1716,7 @@
       <c r="G34" s="7"/>
     </row>
     <row r="35" spans="1:7" s="2" customFormat="1" ht="33.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A35" s="27"/>
+      <c r="A35" s="29"/>
       <c r="B35" s="6" t="s">
         <v>41</v>
       </c>
@@ -1915,322 +1964,709 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G36"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <cols>
+    <col min="1" max="1" width="15.375" customWidth="1"/>
+    <col min="2" max="2" width="38.625" customWidth="1"/>
+    <col min="3" max="3" width="14.875" customWidth="1"/>
+    <col min="4" max="4" width="18.5" customWidth="1"/>
+    <col min="5" max="5" width="18.875" customWidth="1"/>
+    <col min="6" max="6" width="60.875" customWidth="1"/>
+    <col min="7" max="7" width="9.875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A1" s="28" t="s">
+        <v>138</v>
+      </c>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A2" s="28"/>
+      <c r="B2" s="28"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
+      <c r="F2" s="28"/>
+      <c r="G2" s="28"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A3" s="28"/>
+      <c r="B3" s="28"/>
+      <c r="C3" s="28"/>
+      <c r="D3" s="28"/>
+      <c r="E3" s="28"/>
+      <c r="F3" s="28"/>
+      <c r="G3" s="28"/>
+    </row>
+    <row r="4" spans="1:7" ht="18.75" x14ac:dyDescent="0.15">
+      <c r="A4" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4" s="5"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A5" s="29" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5" s="9"/>
+      <c r="C5" s="11"/>
+      <c r="D5" s="10"/>
+      <c r="E5" s="12"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="7"/>
+    </row>
+    <row r="6" spans="1:7" ht="33.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A6" s="29"/>
+      <c r="B6" s="26"/>
+      <c r="C6" s="26"/>
+      <c r="D6" s="26"/>
+      <c r="E6" s="21"/>
+      <c r="F6" s="26"/>
+    </row>
+    <row r="7" spans="1:7" ht="34.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A7" s="28" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="C7" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="D7" s="13" t="s">
+        <v>134</v>
+      </c>
+      <c r="E7" s="14"/>
+      <c r="F7" s="9"/>
+    </row>
+    <row r="8" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A8" s="28"/>
+      <c r="B8" s="26" t="s">
+        <v>135</v>
+      </c>
+      <c r="C8" s="26" t="s">
+        <v>137</v>
+      </c>
+      <c r="D8" s="26" t="s">
+        <v>136</v>
+      </c>
+      <c r="E8" s="21"/>
+      <c r="F8" s="26"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A9" s="28"/>
+      <c r="B9" s="26"/>
+      <c r="C9" s="26"/>
+      <c r="D9" s="26"/>
+      <c r="E9" s="21"/>
+      <c r="F9" s="26"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A10" s="28"/>
+      <c r="B10" s="26"/>
+      <c r="C10" s="26"/>
+      <c r="D10" s="26"/>
+      <c r="E10" s="21"/>
+      <c r="F10" s="26"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A11" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" s="13"/>
+      <c r="C11" s="13"/>
+      <c r="D11" s="13"/>
+      <c r="E11" s="14"/>
+      <c r="F11" s="13"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A12" s="28"/>
+      <c r="B12" s="26"/>
+      <c r="C12" s="26"/>
+      <c r="D12" s="26"/>
+      <c r="E12" s="26"/>
+      <c r="F12" s="27"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A13" s="28"/>
+      <c r="B13" s="9"/>
+      <c r="C13" s="10"/>
+      <c r="D13" s="11"/>
+      <c r="E13" s="12"/>
+      <c r="F13" s="9"/>
+      <c r="G13" s="7"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A14" s="29" t="s">
+        <v>105</v>
+      </c>
+      <c r="B14" s="27"/>
+      <c r="C14" s="27"/>
+      <c r="D14" s="27"/>
+      <c r="E14" s="17"/>
+      <c r="F14" s="27"/>
+      <c r="G14" s="7"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A15" s="29"/>
+      <c r="B15" s="9"/>
+      <c r="C15" s="9"/>
+      <c r="D15" s="9"/>
+      <c r="E15" s="12"/>
+      <c r="F15" s="9"/>
+      <c r="G15" s="7"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A16" s="29"/>
+      <c r="B16" s="15"/>
+      <c r="C16" s="15"/>
+      <c r="D16" s="15"/>
+      <c r="E16" s="16"/>
+      <c r="F16" s="15"/>
+      <c r="G16" s="7"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A17" s="29"/>
+      <c r="B17" s="15"/>
+      <c r="C17" s="15"/>
+      <c r="D17" s="15"/>
+      <c r="E17" s="16"/>
+      <c r="F17" s="15"/>
+      <c r="G17" s="7"/>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A18" s="29"/>
+      <c r="B18" s="15"/>
+      <c r="C18" s="15"/>
+      <c r="D18" s="15"/>
+      <c r="E18" s="16"/>
+      <c r="F18" s="15"/>
+      <c r="G18" s="7"/>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A19" s="29" t="s">
+        <v>104</v>
+      </c>
+      <c r="B19" s="27"/>
+      <c r="C19" s="8"/>
+      <c r="D19" s="8"/>
+      <c r="E19" s="27"/>
+      <c r="F19" s="27"/>
+      <c r="G19" s="7"/>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A20" s="29"/>
+      <c r="B20" s="27"/>
+      <c r="C20" s="8"/>
+      <c r="D20" s="8"/>
+      <c r="E20" s="17"/>
+      <c r="F20" s="27"/>
+      <c r="G20" s="7"/>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A21" s="29"/>
+      <c r="B21" s="27"/>
+      <c r="C21" s="8"/>
+      <c r="D21" s="8"/>
+      <c r="E21" s="17"/>
+      <c r="F21" s="27"/>
+      <c r="G21" s="7"/>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A22" s="29"/>
+      <c r="B22" s="9"/>
+      <c r="C22" s="9"/>
+      <c r="D22" s="11"/>
+      <c r="E22" s="12"/>
+      <c r="F22" s="9"/>
+      <c r="G22" s="7"/>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A23" s="29"/>
+      <c r="B23" s="9"/>
+      <c r="C23" s="9"/>
+      <c r="D23" s="9"/>
+      <c r="E23" s="12"/>
+      <c r="F23" s="9"/>
+      <c r="G23" s="7"/>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A24" s="29"/>
+      <c r="B24" s="9"/>
+      <c r="C24" s="9"/>
+      <c r="D24" s="9"/>
+      <c r="E24" s="12"/>
+      <c r="F24" s="9"/>
+      <c r="G24" s="7"/>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A25" s="29"/>
+      <c r="B25" s="9"/>
+      <c r="C25" s="9"/>
+      <c r="D25" s="9"/>
+      <c r="E25" s="12"/>
+      <c r="F25" s="9"/>
+      <c r="G25" s="7"/>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A26" s="29"/>
+      <c r="B26" s="9"/>
+      <c r="C26" s="9"/>
+      <c r="D26" s="9"/>
+      <c r="E26" s="12"/>
+      <c r="F26" s="9"/>
+      <c r="G26" s="7"/>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A27" s="29"/>
+      <c r="B27" s="9"/>
+      <c r="C27" s="9"/>
+      <c r="D27" s="9"/>
+      <c r="E27" s="12"/>
+      <c r="F27" s="9"/>
+      <c r="G27" s="7"/>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A28" s="29"/>
+      <c r="B28" s="9"/>
+      <c r="C28" s="9"/>
+      <c r="D28" s="9"/>
+      <c r="E28" s="12"/>
+      <c r="F28" s="9"/>
+      <c r="G28" s="7"/>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A29" s="29"/>
+      <c r="B29" s="9"/>
+      <c r="C29" s="9"/>
+      <c r="D29" s="9"/>
+      <c r="E29" s="12"/>
+      <c r="F29" s="9"/>
+      <c r="G29" s="7"/>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A30" s="29" t="s">
+        <v>47</v>
+      </c>
+      <c r="B30" s="9"/>
+      <c r="C30" s="9"/>
+      <c r="D30" s="9"/>
+      <c r="E30" s="12"/>
+      <c r="F30" s="9"/>
+      <c r="G30" s="7"/>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A31" s="29"/>
+      <c r="B31" s="9"/>
+      <c r="C31" s="9"/>
+      <c r="D31" s="9"/>
+      <c r="E31" s="12"/>
+      <c r="F31" s="9"/>
+      <c r="G31" s="7"/>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A32" s="29"/>
+      <c r="B32" s="15"/>
+      <c r="C32" s="15"/>
+      <c r="D32" s="15"/>
+      <c r="E32" s="16"/>
+      <c r="F32" s="15"/>
+      <c r="G32" s="7"/>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A33" s="29"/>
+      <c r="B33" s="15"/>
+      <c r="C33" s="15"/>
+      <c r="D33" s="15"/>
+      <c r="E33" s="16"/>
+      <c r="F33" s="15"/>
+      <c r="G33" s="7"/>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A34" s="29"/>
+      <c r="B34" s="9"/>
+      <c r="C34" s="9"/>
+      <c r="D34" s="9"/>
+      <c r="E34" s="12"/>
+      <c r="F34" s="9"/>
+      <c r="G34" s="7"/>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A35" s="29"/>
+      <c r="B35" s="27"/>
+      <c r="C35" s="27"/>
+      <c r="D35" s="27"/>
+      <c r="E35" s="27"/>
+      <c r="F35" s="27"/>
+      <c r="G35" s="7"/>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A36" s="27" t="s">
+        <v>79</v>
+      </c>
+      <c r="B36" s="15"/>
+      <c r="C36" s="15"/>
+      <c r="D36" s="15"/>
+      <c r="E36" s="16"/>
+      <c r="F36" s="15"/>
+      <c r="G36" s="7"/>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="A30:A35"/>
+    <mergeCell ref="A1:G3"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="A7:A10"/>
+    <mergeCell ref="A11:A13"/>
+    <mergeCell ref="A14:A18"/>
+    <mergeCell ref="A19:A29"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:R62"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="30" t="s">
         <v>126</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26"/>
-      <c r="H1" s="26"/>
-      <c r="I1" s="26"/>
-      <c r="J1" s="26"/>
-      <c r="K1" s="26"/>
-      <c r="L1" s="26"/>
-      <c r="M1" s="26"/>
-      <c r="N1" s="26"/>
-      <c r="O1" s="26"/>
-      <c r="P1" s="26"/>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="28"/>
+      <c r="I1" s="28"/>
+      <c r="J1" s="28"/>
+      <c r="K1" s="28"/>
+      <c r="L1" s="28"/>
+      <c r="M1" s="28"/>
+      <c r="N1" s="28"/>
+      <c r="O1" s="28"/>
+      <c r="P1" s="28"/>
       <c r="Q1" s="23"/>
       <c r="R1" s="23"/>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="A2" s="26"/>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
-      <c r="G2" s="26"/>
-      <c r="H2" s="26"/>
-      <c r="I2" s="26"/>
-      <c r="J2" s="26"/>
-      <c r="K2" s="26"/>
-      <c r="L2" s="26"/>
-      <c r="M2" s="26"/>
-      <c r="N2" s="26"/>
-      <c r="O2" s="26"/>
-      <c r="P2" s="26"/>
+      <c r="A2" s="28"/>
+      <c r="B2" s="28"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
+      <c r="F2" s="28"/>
+      <c r="G2" s="28"/>
+      <c r="H2" s="28"/>
+      <c r="I2" s="28"/>
+      <c r="J2" s="28"/>
+      <c r="K2" s="28"/>
+      <c r="L2" s="28"/>
+      <c r="M2" s="28"/>
+      <c r="N2" s="28"/>
+      <c r="O2" s="28"/>
+      <c r="P2" s="28"/>
       <c r="Q2" s="23"/>
       <c r="R2" s="23"/>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="A3" s="26"/>
-      <c r="B3" s="26"/>
-      <c r="C3" s="26"/>
-      <c r="D3" s="26"/>
-      <c r="E3" s="26"/>
-      <c r="F3" s="26"/>
-      <c r="G3" s="26"/>
-      <c r="H3" s="26"/>
-      <c r="I3" s="26"/>
-      <c r="J3" s="26"/>
-      <c r="K3" s="26"/>
-      <c r="L3" s="26"/>
-      <c r="M3" s="26"/>
-      <c r="N3" s="26"/>
-      <c r="O3" s="26"/>
-      <c r="P3" s="26"/>
+      <c r="A3" s="28"/>
+      <c r="B3" s="28"/>
+      <c r="C3" s="28"/>
+      <c r="D3" s="28"/>
+      <c r="E3" s="28"/>
+      <c r="F3" s="28"/>
+      <c r="G3" s="28"/>
+      <c r="H3" s="28"/>
+      <c r="I3" s="28"/>
+      <c r="J3" s="28"/>
+      <c r="K3" s="28"/>
+      <c r="L3" s="28"/>
+      <c r="M3" s="28"/>
+      <c r="N3" s="28"/>
+      <c r="O3" s="28"/>
+      <c r="P3" s="28"/>
       <c r="Q3" s="23"/>
       <c r="R3" s="23"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="A4" s="26" t="s">
+      <c r="A4" s="28" t="s">
         <v>118</v>
       </c>
-      <c r="B4" s="26"/>
-      <c r="C4" s="26" t="s">
+      <c r="B4" s="28"/>
+      <c r="C4" s="28" t="s">
         <v>120</v>
       </c>
-      <c r="D4" s="26"/>
-      <c r="E4" s="26"/>
-      <c r="F4" s="26"/>
-      <c r="G4" s="26"/>
-      <c r="H4" s="26"/>
-      <c r="I4" s="26"/>
-      <c r="J4" s="26"/>
-      <c r="K4" s="26"/>
-      <c r="L4" s="26"/>
-      <c r="M4" s="26"/>
-      <c r="N4" s="26"/>
-      <c r="O4" s="26"/>
-      <c r="P4" s="26"/>
+      <c r="D4" s="28"/>
+      <c r="E4" s="28"/>
+      <c r="F4" s="28"/>
+      <c r="G4" s="28"/>
+      <c r="H4" s="28"/>
+      <c r="I4" s="28"/>
+      <c r="J4" s="28"/>
+      <c r="K4" s="28"/>
+      <c r="L4" s="28"/>
+      <c r="M4" s="28"/>
+      <c r="N4" s="28"/>
+      <c r="O4" s="28"/>
+      <c r="P4" s="28"/>
       <c r="Q4" s="23"/>
       <c r="R4" s="23"/>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="A5" s="26"/>
-      <c r="B5" s="26"/>
-      <c r="C5" s="26"/>
-      <c r="D5" s="26"/>
-      <c r="E5" s="26"/>
-      <c r="F5" s="26"/>
-      <c r="G5" s="26"/>
-      <c r="H5" s="26"/>
-      <c r="I5" s="26"/>
-      <c r="J5" s="26"/>
-      <c r="K5" s="26"/>
-      <c r="L5" s="26"/>
-      <c r="M5" s="26"/>
-      <c r="N5" s="26"/>
-      <c r="O5" s="26"/>
-      <c r="P5" s="26"/>
+      <c r="A5" s="28"/>
+      <c r="B5" s="28"/>
+      <c r="C5" s="28"/>
+      <c r="D5" s="28"/>
+      <c r="E5" s="28"/>
+      <c r="F5" s="28"/>
+      <c r="G5" s="28"/>
+      <c r="H5" s="28"/>
+      <c r="I5" s="28"/>
+      <c r="J5" s="28"/>
+      <c r="K5" s="28"/>
+      <c r="L5" s="28"/>
+      <c r="M5" s="28"/>
+      <c r="N5" s="28"/>
+      <c r="O5" s="28"/>
+      <c r="P5" s="28"/>
       <c r="Q5" s="23"/>
       <c r="R5" s="23"/>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="A6" s="26" t="s">
+      <c r="A6" s="28" t="s">
         <v>119</v>
       </c>
-      <c r="B6" s="26"/>
-      <c r="C6" s="26" t="s">
+      <c r="B6" s="28"/>
+      <c r="C6" s="28" t="s">
         <v>121</v>
       </c>
-      <c r="D6" s="26"/>
-      <c r="E6" s="26"/>
-      <c r="F6" s="26"/>
-      <c r="G6" s="26"/>
-      <c r="H6" s="26"/>
-      <c r="I6" s="26"/>
-      <c r="J6" s="26"/>
-      <c r="K6" s="26"/>
-      <c r="L6" s="26"/>
-      <c r="M6" s="26"/>
-      <c r="N6" s="26"/>
-      <c r="O6" s="26"/>
-      <c r="P6" s="26"/>
+      <c r="D6" s="28"/>
+      <c r="E6" s="28"/>
+      <c r="F6" s="28"/>
+      <c r="G6" s="28"/>
+      <c r="H6" s="28"/>
+      <c r="I6" s="28"/>
+      <c r="J6" s="28"/>
+      <c r="K6" s="28"/>
+      <c r="L6" s="28"/>
+      <c r="M6" s="28"/>
+      <c r="N6" s="28"/>
+      <c r="O6" s="28"/>
+      <c r="P6" s="28"/>
       <c r="Q6" s="23"/>
       <c r="R6" s="23"/>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="A7" s="26"/>
-      <c r="B7" s="26"/>
-      <c r="C7" s="26"/>
-      <c r="D7" s="26"/>
-      <c r="E7" s="26"/>
-      <c r="F7" s="26"/>
-      <c r="G7" s="26"/>
-      <c r="H7" s="26"/>
-      <c r="I7" s="26"/>
-      <c r="J7" s="26"/>
-      <c r="K7" s="26"/>
-      <c r="L7" s="26"/>
-      <c r="M7" s="26"/>
-      <c r="N7" s="26"/>
-      <c r="O7" s="26"/>
-      <c r="P7" s="26"/>
+      <c r="A7" s="28"/>
+      <c r="B7" s="28"/>
+      <c r="C7" s="28"/>
+      <c r="D7" s="28"/>
+      <c r="E7" s="28"/>
+      <c r="F7" s="28"/>
+      <c r="G7" s="28"/>
+      <c r="H7" s="28"/>
+      <c r="I7" s="28"/>
+      <c r="J7" s="28"/>
+      <c r="K7" s="28"/>
+      <c r="L7" s="28"/>
+      <c r="M7" s="28"/>
+      <c r="N7" s="28"/>
+      <c r="O7" s="28"/>
+      <c r="P7" s="28"/>
       <c r="Q7" s="23"/>
       <c r="R7" s="23"/>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="A8" s="26"/>
-      <c r="B8" s="26"/>
-      <c r="C8" s="26"/>
-      <c r="D8" s="26"/>
-      <c r="E8" s="26"/>
-      <c r="F8" s="26"/>
-      <c r="G8" s="26"/>
-      <c r="H8" s="26"/>
-      <c r="I8" s="26"/>
-      <c r="J8" s="26"/>
-      <c r="K8" s="26"/>
-      <c r="L8" s="26"/>
-      <c r="M8" s="26"/>
-      <c r="N8" s="26"/>
-      <c r="O8" s="26"/>
-      <c r="P8" s="26"/>
+      <c r="A8" s="28"/>
+      <c r="B8" s="28"/>
+      <c r="C8" s="28"/>
+      <c r="D8" s="28"/>
+      <c r="E8" s="28"/>
+      <c r="F8" s="28"/>
+      <c r="G8" s="28"/>
+      <c r="H8" s="28"/>
+      <c r="I8" s="28"/>
+      <c r="J8" s="28"/>
+      <c r="K8" s="28"/>
+      <c r="L8" s="28"/>
+      <c r="M8" s="28"/>
+      <c r="N8" s="28"/>
+      <c r="O8" s="28"/>
+      <c r="P8" s="28"/>
       <c r="Q8" s="23"/>
       <c r="R8" s="23"/>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="A9" s="26"/>
-      <c r="B9" s="26"/>
-      <c r="C9" s="26"/>
-      <c r="D9" s="26"/>
-      <c r="E9" s="26"/>
-      <c r="F9" s="26"/>
-      <c r="G9" s="26"/>
-      <c r="H9" s="26"/>
-      <c r="I9" s="26"/>
-      <c r="J9" s="26"/>
-      <c r="K9" s="26"/>
-      <c r="L9" s="26"/>
-      <c r="M9" s="26"/>
-      <c r="N9" s="26"/>
-      <c r="O9" s="26"/>
-      <c r="P9" s="26"/>
+      <c r="A9" s="28"/>
+      <c r="B9" s="28"/>
+      <c r="C9" s="28"/>
+      <c r="D9" s="28"/>
+      <c r="E9" s="28"/>
+      <c r="F9" s="28"/>
+      <c r="G9" s="28"/>
+      <c r="H9" s="28"/>
+      <c r="I9" s="28"/>
+      <c r="J9" s="28"/>
+      <c r="K9" s="28"/>
+      <c r="L9" s="28"/>
+      <c r="M9" s="28"/>
+      <c r="N9" s="28"/>
+      <c r="O9" s="28"/>
+      <c r="P9" s="28"/>
       <c r="Q9" s="23"/>
       <c r="R9" s="23"/>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="A10" s="26"/>
-      <c r="B10" s="26"/>
-      <c r="C10" s="26"/>
-      <c r="D10" s="26"/>
-      <c r="E10" s="26"/>
-      <c r="F10" s="26"/>
-      <c r="G10" s="26"/>
-      <c r="H10" s="26"/>
-      <c r="I10" s="26"/>
-      <c r="J10" s="26"/>
-      <c r="K10" s="26"/>
-      <c r="L10" s="26"/>
-      <c r="M10" s="26"/>
-      <c r="N10" s="26"/>
-      <c r="O10" s="26"/>
-      <c r="P10" s="26"/>
+      <c r="A10" s="28"/>
+      <c r="B10" s="28"/>
+      <c r="C10" s="28"/>
+      <c r="D10" s="28"/>
+      <c r="E10" s="28"/>
+      <c r="F10" s="28"/>
+      <c r="G10" s="28"/>
+      <c r="H10" s="28"/>
+      <c r="I10" s="28"/>
+      <c r="J10" s="28"/>
+      <c r="K10" s="28"/>
+      <c r="L10" s="28"/>
+      <c r="M10" s="28"/>
+      <c r="N10" s="28"/>
+      <c r="O10" s="28"/>
+      <c r="P10" s="28"/>
       <c r="Q10" s="23"/>
       <c r="R10" s="23"/>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="A11" s="26"/>
-      <c r="B11" s="26"/>
-      <c r="C11" s="26"/>
-      <c r="D11" s="26"/>
-      <c r="E11" s="26"/>
-      <c r="F11" s="26"/>
-      <c r="G11" s="26"/>
-      <c r="H11" s="26"/>
-      <c r="I11" s="26"/>
-      <c r="J11" s="26"/>
-      <c r="K11" s="26"/>
-      <c r="L11" s="26"/>
-      <c r="M11" s="26"/>
-      <c r="N11" s="26"/>
-      <c r="O11" s="26"/>
-      <c r="P11" s="26"/>
+      <c r="A11" s="28"/>
+      <c r="B11" s="28"/>
+      <c r="C11" s="28"/>
+      <c r="D11" s="28"/>
+      <c r="E11" s="28"/>
+      <c r="F11" s="28"/>
+      <c r="G11" s="28"/>
+      <c r="H11" s="28"/>
+      <c r="I11" s="28"/>
+      <c r="J11" s="28"/>
+      <c r="K11" s="28"/>
+      <c r="L11" s="28"/>
+      <c r="M11" s="28"/>
+      <c r="N11" s="28"/>
+      <c r="O11" s="28"/>
+      <c r="P11" s="28"/>
       <c r="Q11" s="23"/>
       <c r="R11" s="23"/>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="A12" s="26"/>
-      <c r="B12" s="26"/>
-      <c r="C12" s="26"/>
-      <c r="D12" s="26"/>
-      <c r="E12" s="26"/>
-      <c r="F12" s="26"/>
-      <c r="G12" s="26"/>
-      <c r="H12" s="26"/>
-      <c r="I12" s="26"/>
-      <c r="J12" s="26"/>
-      <c r="K12" s="26"/>
-      <c r="L12" s="26"/>
-      <c r="M12" s="26"/>
-      <c r="N12" s="26"/>
-      <c r="O12" s="26"/>
-      <c r="P12" s="26"/>
+      <c r="A12" s="28"/>
+      <c r="B12" s="28"/>
+      <c r="C12" s="28"/>
+      <c r="D12" s="28"/>
+      <c r="E12" s="28"/>
+      <c r="F12" s="28"/>
+      <c r="G12" s="28"/>
+      <c r="H12" s="28"/>
+      <c r="I12" s="28"/>
+      <c r="J12" s="28"/>
+      <c r="K12" s="28"/>
+      <c r="L12" s="28"/>
+      <c r="M12" s="28"/>
+      <c r="N12" s="28"/>
+      <c r="O12" s="28"/>
+      <c r="P12" s="28"/>
       <c r="Q12" s="23"/>
       <c r="R12" s="23"/>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="A13" s="26"/>
-      <c r="B13" s="26"/>
-      <c r="C13" s="26"/>
-      <c r="D13" s="26"/>
-      <c r="E13" s="26"/>
-      <c r="F13" s="26"/>
-      <c r="G13" s="26"/>
-      <c r="H13" s="26"/>
-      <c r="I13" s="26"/>
-      <c r="J13" s="26"/>
-      <c r="K13" s="26"/>
-      <c r="L13" s="26"/>
-      <c r="M13" s="26"/>
-      <c r="N13" s="26"/>
-      <c r="O13" s="26"/>
-      <c r="P13" s="26"/>
+      <c r="A13" s="28"/>
+      <c r="B13" s="28"/>
+      <c r="C13" s="28"/>
+      <c r="D13" s="28"/>
+      <c r="E13" s="28"/>
+      <c r="F13" s="28"/>
+      <c r="G13" s="28"/>
+      <c r="H13" s="28"/>
+      <c r="I13" s="28"/>
+      <c r="J13" s="28"/>
+      <c r="K13" s="28"/>
+      <c r="L13" s="28"/>
+      <c r="M13" s="28"/>
+      <c r="N13" s="28"/>
+      <c r="O13" s="28"/>
+      <c r="P13" s="28"/>
       <c r="Q13" s="23"/>
       <c r="R13" s="23"/>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="A14" s="26"/>
-      <c r="B14" s="26"/>
-      <c r="C14" s="26"/>
-      <c r="D14" s="26"/>
-      <c r="E14" s="26"/>
-      <c r="F14" s="26"/>
-      <c r="G14" s="26"/>
-      <c r="H14" s="26"/>
-      <c r="I14" s="26"/>
-      <c r="J14" s="26"/>
-      <c r="K14" s="26"/>
-      <c r="L14" s="26"/>
-      <c r="M14" s="26"/>
-      <c r="N14" s="26"/>
-      <c r="O14" s="26"/>
-      <c r="P14" s="26"/>
+      <c r="A14" s="28"/>
+      <c r="B14" s="28"/>
+      <c r="C14" s="28"/>
+      <c r="D14" s="28"/>
+      <c r="E14" s="28"/>
+      <c r="F14" s="28"/>
+      <c r="G14" s="28"/>
+      <c r="H14" s="28"/>
+      <c r="I14" s="28"/>
+      <c r="J14" s="28"/>
+      <c r="K14" s="28"/>
+      <c r="L14" s="28"/>
+      <c r="M14" s="28"/>
+      <c r="N14" s="28"/>
+      <c r="O14" s="28"/>
+      <c r="P14" s="28"/>
       <c r="Q14" s="23"/>
       <c r="R14" s="23"/>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="A15" s="26"/>
-      <c r="B15" s="26"/>
-      <c r="C15" s="26"/>
-      <c r="D15" s="26"/>
-      <c r="E15" s="26"/>
-      <c r="F15" s="26"/>
-      <c r="G15" s="26"/>
-      <c r="H15" s="26"/>
-      <c r="I15" s="26"/>
-      <c r="J15" s="26"/>
-      <c r="K15" s="26"/>
-      <c r="L15" s="26"/>
-      <c r="M15" s="26"/>
-      <c r="N15" s="26"/>
-      <c r="O15" s="26"/>
-      <c r="P15" s="26"/>
+      <c r="A15" s="28"/>
+      <c r="B15" s="28"/>
+      <c r="C15" s="28"/>
+      <c r="D15" s="28"/>
+      <c r="E15" s="28"/>
+      <c r="F15" s="28"/>
+      <c r="G15" s="28"/>
+      <c r="H15" s="28"/>
+      <c r="I15" s="28"/>
+      <c r="J15" s="28"/>
+      <c r="K15" s="28"/>
+      <c r="L15" s="28"/>
+      <c r="M15" s="28"/>
+      <c r="N15" s="28"/>
+      <c r="O15" s="28"/>
+      <c r="P15" s="28"/>
       <c r="Q15" s="23"/>
       <c r="R15" s="23"/>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="A16" s="26"/>
-      <c r="B16" s="26"/>
+      <c r="A16" s="28"/>
+      <c r="B16" s="28"/>
       <c r="C16" s="23"/>
       <c r="D16" s="23"/>
       <c r="E16" s="23"/>
@@ -2249,8 +2685,8 @@
       <c r="R16" s="23"/>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="A17" s="26"/>
-      <c r="B17" s="26"/>
+      <c r="A17" s="28"/>
+      <c r="B17" s="28"/>
       <c r="C17" s="23"/>
       <c r="D17" s="23"/>
       <c r="E17" s="23"/>
@@ -2269,8 +2705,8 @@
       <c r="R17" s="23"/>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="A18" s="26"/>
-      <c r="B18" s="26"/>
+      <c r="A18" s="28"/>
+      <c r="B18" s="28"/>
       <c r="C18" s="23"/>
       <c r="D18" s="23"/>
       <c r="E18" s="23"/>
@@ -2289,8 +2725,8 @@
       <c r="R18" s="23"/>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="A19" s="26"/>
-      <c r="B19" s="26"/>
+      <c r="A19" s="28"/>
+      <c r="B19" s="28"/>
       <c r="C19" s="23"/>
       <c r="D19" s="23"/>
       <c r="E19" s="23"/>
@@ -2309,8 +2745,8 @@
       <c r="R19" s="23"/>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="A20" s="26"/>
-      <c r="B20" s="26"/>
+      <c r="A20" s="28"/>
+      <c r="B20" s="28"/>
       <c r="C20" s="23"/>
       <c r="D20" s="23"/>
       <c r="E20" s="23"/>
@@ -3186,298 +3622,298 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:P20"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="30" t="s">
         <v>127</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26"/>
-      <c r="H1" s="26"/>
-      <c r="I1" s="26"/>
-      <c r="J1" s="26"/>
-      <c r="K1" s="26"/>
-      <c r="L1" s="26"/>
-      <c r="M1" s="26"/>
-      <c r="N1" s="26"/>
-      <c r="O1" s="26"/>
-      <c r="P1" s="26"/>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="28"/>
+      <c r="I1" s="28"/>
+      <c r="J1" s="28"/>
+      <c r="K1" s="28"/>
+      <c r="L1" s="28"/>
+      <c r="M1" s="28"/>
+      <c r="N1" s="28"/>
+      <c r="O1" s="28"/>
+      <c r="P1" s="28"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A2" s="26"/>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
-      <c r="G2" s="26"/>
-      <c r="H2" s="26"/>
-      <c r="I2" s="26"/>
-      <c r="J2" s="26"/>
-      <c r="K2" s="26"/>
-      <c r="L2" s="26"/>
-      <c r="M2" s="26"/>
-      <c r="N2" s="26"/>
-      <c r="O2" s="26"/>
-      <c r="P2" s="26"/>
+      <c r="A2" s="28"/>
+      <c r="B2" s="28"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
+      <c r="F2" s="28"/>
+      <c r="G2" s="28"/>
+      <c r="H2" s="28"/>
+      <c r="I2" s="28"/>
+      <c r="J2" s="28"/>
+      <c r="K2" s="28"/>
+      <c r="L2" s="28"/>
+      <c r="M2" s="28"/>
+      <c r="N2" s="28"/>
+      <c r="O2" s="28"/>
+      <c r="P2" s="28"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A3" s="26"/>
-      <c r="B3" s="26"/>
-      <c r="C3" s="26"/>
-      <c r="D3" s="26"/>
-      <c r="E3" s="26"/>
-      <c r="F3" s="26"/>
-      <c r="G3" s="26"/>
-      <c r="H3" s="26"/>
-      <c r="I3" s="26"/>
-      <c r="J3" s="26"/>
-      <c r="K3" s="26"/>
-      <c r="L3" s="26"/>
-      <c r="M3" s="26"/>
-      <c r="N3" s="26"/>
-      <c r="O3" s="26"/>
-      <c r="P3" s="26"/>
+      <c r="A3" s="28"/>
+      <c r="B3" s="28"/>
+      <c r="C3" s="28"/>
+      <c r="D3" s="28"/>
+      <c r="E3" s="28"/>
+      <c r="F3" s="28"/>
+      <c r="G3" s="28"/>
+      <c r="H3" s="28"/>
+      <c r="I3" s="28"/>
+      <c r="J3" s="28"/>
+      <c r="K3" s="28"/>
+      <c r="L3" s="28"/>
+      <c r="M3" s="28"/>
+      <c r="N3" s="28"/>
+      <c r="O3" s="28"/>
+      <c r="P3" s="28"/>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A4" s="26" t="s">
+      <c r="A4" s="28" t="s">
         <v>118</v>
       </c>
-      <c r="B4" s="26"/>
-      <c r="C4" s="27" t="s">
+      <c r="B4" s="28"/>
+      <c r="C4" s="29" t="s">
         <v>131</v>
       </c>
-      <c r="D4" s="26"/>
-      <c r="E4" s="26"/>
-      <c r="F4" s="26"/>
-      <c r="G4" s="26"/>
-      <c r="H4" s="26"/>
-      <c r="I4" s="26"/>
-      <c r="J4" s="26"/>
-      <c r="K4" s="26"/>
-      <c r="L4" s="26"/>
-      <c r="M4" s="26"/>
-      <c r="N4" s="26"/>
-      <c r="O4" s="26"/>
-      <c r="P4" s="26"/>
+      <c r="D4" s="28"/>
+      <c r="E4" s="28"/>
+      <c r="F4" s="28"/>
+      <c r="G4" s="28"/>
+      <c r="H4" s="28"/>
+      <c r="I4" s="28"/>
+      <c r="J4" s="28"/>
+      <c r="K4" s="28"/>
+      <c r="L4" s="28"/>
+      <c r="M4" s="28"/>
+      <c r="N4" s="28"/>
+      <c r="O4" s="28"/>
+      <c r="P4" s="28"/>
     </row>
     <row r="5" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="26"/>
-      <c r="B5" s="26"/>
-      <c r="C5" s="26"/>
-      <c r="D5" s="26"/>
-      <c r="E5" s="26"/>
-      <c r="F5" s="26"/>
-      <c r="G5" s="26"/>
-      <c r="H5" s="26"/>
-      <c r="I5" s="26"/>
-      <c r="J5" s="26"/>
-      <c r="K5" s="26"/>
-      <c r="L5" s="26"/>
-      <c r="M5" s="26"/>
-      <c r="N5" s="26"/>
-      <c r="O5" s="26"/>
-      <c r="P5" s="26"/>
+      <c r="A5" s="28"/>
+      <c r="B5" s="28"/>
+      <c r="C5" s="28"/>
+      <c r="D5" s="28"/>
+      <c r="E5" s="28"/>
+      <c r="F5" s="28"/>
+      <c r="G5" s="28"/>
+      <c r="H5" s="28"/>
+      <c r="I5" s="28"/>
+      <c r="J5" s="28"/>
+      <c r="K5" s="28"/>
+      <c r="L5" s="28"/>
+      <c r="M5" s="28"/>
+      <c r="N5" s="28"/>
+      <c r="O5" s="28"/>
+      <c r="P5" s="28"/>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A6" s="26" t="s">
+      <c r="A6" s="28" t="s">
         <v>119</v>
       </c>
-      <c r="B6" s="26"/>
-      <c r="C6" s="27" t="s">
+      <c r="B6" s="28"/>
+      <c r="C6" s="29" t="s">
         <v>130</v>
       </c>
-      <c r="D6" s="26"/>
-      <c r="E6" s="26"/>
-      <c r="F6" s="26"/>
-      <c r="G6" s="26"/>
-      <c r="H6" s="26"/>
-      <c r="I6" s="26"/>
-      <c r="J6" s="26"/>
-      <c r="K6" s="26"/>
-      <c r="L6" s="26"/>
-      <c r="M6" s="26"/>
-      <c r="N6" s="26"/>
-      <c r="O6" s="26"/>
-      <c r="P6" s="26"/>
+      <c r="D6" s="28"/>
+      <c r="E6" s="28"/>
+      <c r="F6" s="28"/>
+      <c r="G6" s="28"/>
+      <c r="H6" s="28"/>
+      <c r="I6" s="28"/>
+      <c r="J6" s="28"/>
+      <c r="K6" s="28"/>
+      <c r="L6" s="28"/>
+      <c r="M6" s="28"/>
+      <c r="N6" s="28"/>
+      <c r="O6" s="28"/>
+      <c r="P6" s="28"/>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A7" s="26"/>
-      <c r="B7" s="26"/>
-      <c r="C7" s="26"/>
-      <c r="D7" s="26"/>
-      <c r="E7" s="26"/>
-      <c r="F7" s="26"/>
-      <c r="G7" s="26"/>
-      <c r="H7" s="26"/>
-      <c r="I7" s="26"/>
-      <c r="J7" s="26"/>
-      <c r="K7" s="26"/>
-      <c r="L7" s="26"/>
-      <c r="M7" s="26"/>
-      <c r="N7" s="26"/>
-      <c r="O7" s="26"/>
-      <c r="P7" s="26"/>
+      <c r="A7" s="28"/>
+      <c r="B7" s="28"/>
+      <c r="C7" s="28"/>
+      <c r="D7" s="28"/>
+      <c r="E7" s="28"/>
+      <c r="F7" s="28"/>
+      <c r="G7" s="28"/>
+      <c r="H7" s="28"/>
+      <c r="I7" s="28"/>
+      <c r="J7" s="28"/>
+      <c r="K7" s="28"/>
+      <c r="L7" s="28"/>
+      <c r="M7" s="28"/>
+      <c r="N7" s="28"/>
+      <c r="O7" s="28"/>
+      <c r="P7" s="28"/>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A8" s="26"/>
-      <c r="B8" s="26"/>
-      <c r="C8" s="26" t="s">
+      <c r="A8" s="28"/>
+      <c r="B8" s="28"/>
+      <c r="C8" s="28" t="s">
         <v>128</v>
       </c>
-      <c r="D8" s="26"/>
-      <c r="E8" s="26"/>
-      <c r="F8" s="26"/>
-      <c r="G8" s="26"/>
-      <c r="H8" s="26"/>
-      <c r="I8" s="26"/>
-      <c r="J8" s="26"/>
-      <c r="K8" s="26"/>
-      <c r="L8" s="26"/>
-      <c r="M8" s="26"/>
-      <c r="N8" s="26"/>
-      <c r="O8" s="26"/>
-      <c r="P8" s="26"/>
+      <c r="D8" s="28"/>
+      <c r="E8" s="28"/>
+      <c r="F8" s="28"/>
+      <c r="G8" s="28"/>
+      <c r="H8" s="28"/>
+      <c r="I8" s="28"/>
+      <c r="J8" s="28"/>
+      <c r="K8" s="28"/>
+      <c r="L8" s="28"/>
+      <c r="M8" s="28"/>
+      <c r="N8" s="28"/>
+      <c r="O8" s="28"/>
+      <c r="P8" s="28"/>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A9" s="26"/>
-      <c r="B9" s="26"/>
-      <c r="C9" s="26"/>
-      <c r="D9" s="26"/>
-      <c r="E9" s="26"/>
-      <c r="F9" s="26"/>
-      <c r="G9" s="26"/>
-      <c r="H9" s="26"/>
-      <c r="I9" s="26"/>
-      <c r="J9" s="26"/>
-      <c r="K9" s="26"/>
-      <c r="L9" s="26"/>
-      <c r="M9" s="26"/>
-      <c r="N9" s="26"/>
-      <c r="O9" s="26"/>
-      <c r="P9" s="26"/>
+      <c r="A9" s="28"/>
+      <c r="B9" s="28"/>
+      <c r="C9" s="28"/>
+      <c r="D9" s="28"/>
+      <c r="E9" s="28"/>
+      <c r="F9" s="28"/>
+      <c r="G9" s="28"/>
+      <c r="H9" s="28"/>
+      <c r="I9" s="28"/>
+      <c r="J9" s="28"/>
+      <c r="K9" s="28"/>
+      <c r="L9" s="28"/>
+      <c r="M9" s="28"/>
+      <c r="N9" s="28"/>
+      <c r="O9" s="28"/>
+      <c r="P9" s="28"/>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A10" s="26"/>
-      <c r="B10" s="26"/>
-      <c r="C10" s="26" t="s">
+      <c r="A10" s="28"/>
+      <c r="B10" s="28"/>
+      <c r="C10" s="28" t="s">
         <v>129</v>
       </c>
-      <c r="D10" s="26"/>
-      <c r="E10" s="26"/>
-      <c r="F10" s="26"/>
-      <c r="G10" s="26"/>
-      <c r="H10" s="26"/>
-      <c r="I10" s="26"/>
-      <c r="J10" s="26"/>
-      <c r="K10" s="26"/>
-      <c r="L10" s="26"/>
-      <c r="M10" s="26"/>
-      <c r="N10" s="26"/>
-      <c r="O10" s="26"/>
-      <c r="P10" s="26"/>
+      <c r="D10" s="28"/>
+      <c r="E10" s="28"/>
+      <c r="F10" s="28"/>
+      <c r="G10" s="28"/>
+      <c r="H10" s="28"/>
+      <c r="I10" s="28"/>
+      <c r="J10" s="28"/>
+      <c r="K10" s="28"/>
+      <c r="L10" s="28"/>
+      <c r="M10" s="28"/>
+      <c r="N10" s="28"/>
+      <c r="O10" s="28"/>
+      <c r="P10" s="28"/>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A11" s="26"/>
-      <c r="B11" s="26"/>
-      <c r="C11" s="26"/>
-      <c r="D11" s="26"/>
-      <c r="E11" s="26"/>
-      <c r="F11" s="26"/>
-      <c r="G11" s="26"/>
-      <c r="H11" s="26"/>
-      <c r="I11" s="26"/>
-      <c r="J11" s="26"/>
-      <c r="K11" s="26"/>
-      <c r="L11" s="26"/>
-      <c r="M11" s="26"/>
-      <c r="N11" s="26"/>
-      <c r="O11" s="26"/>
-      <c r="P11" s="26"/>
+      <c r="A11" s="28"/>
+      <c r="B11" s="28"/>
+      <c r="C11" s="28"/>
+      <c r="D11" s="28"/>
+      <c r="E11" s="28"/>
+      <c r="F11" s="28"/>
+      <c r="G11" s="28"/>
+      <c r="H11" s="28"/>
+      <c r="I11" s="28"/>
+      <c r="J11" s="28"/>
+      <c r="K11" s="28"/>
+      <c r="L11" s="28"/>
+      <c r="M11" s="28"/>
+      <c r="N11" s="28"/>
+      <c r="O11" s="28"/>
+      <c r="P11" s="28"/>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A12" s="26"/>
-      <c r="B12" s="26"/>
-      <c r="C12" s="26"/>
-      <c r="D12" s="26"/>
-      <c r="E12" s="26"/>
-      <c r="F12" s="26"/>
-      <c r="G12" s="26"/>
-      <c r="H12" s="26"/>
-      <c r="I12" s="26"/>
-      <c r="J12" s="26"/>
-      <c r="K12" s="26"/>
-      <c r="L12" s="26"/>
-      <c r="M12" s="26"/>
-      <c r="N12" s="26"/>
-      <c r="O12" s="26"/>
-      <c r="P12" s="26"/>
+      <c r="A12" s="28"/>
+      <c r="B12" s="28"/>
+      <c r="C12" s="28"/>
+      <c r="D12" s="28"/>
+      <c r="E12" s="28"/>
+      <c r="F12" s="28"/>
+      <c r="G12" s="28"/>
+      <c r="H12" s="28"/>
+      <c r="I12" s="28"/>
+      <c r="J12" s="28"/>
+      <c r="K12" s="28"/>
+      <c r="L12" s="28"/>
+      <c r="M12" s="28"/>
+      <c r="N12" s="28"/>
+      <c r="O12" s="28"/>
+      <c r="P12" s="28"/>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A13" s="26"/>
-      <c r="B13" s="26"/>
-      <c r="C13" s="26"/>
-      <c r="D13" s="26"/>
-      <c r="E13" s="26"/>
-      <c r="F13" s="26"/>
-      <c r="G13" s="26"/>
-      <c r="H13" s="26"/>
-      <c r="I13" s="26"/>
-      <c r="J13" s="26"/>
-      <c r="K13" s="26"/>
-      <c r="L13" s="26"/>
-      <c r="M13" s="26"/>
-      <c r="N13" s="26"/>
-      <c r="O13" s="26"/>
-      <c r="P13" s="26"/>
+      <c r="A13" s="28"/>
+      <c r="B13" s="28"/>
+      <c r="C13" s="28"/>
+      <c r="D13" s="28"/>
+      <c r="E13" s="28"/>
+      <c r="F13" s="28"/>
+      <c r="G13" s="28"/>
+      <c r="H13" s="28"/>
+      <c r="I13" s="28"/>
+      <c r="J13" s="28"/>
+      <c r="K13" s="28"/>
+      <c r="L13" s="28"/>
+      <c r="M13" s="28"/>
+      <c r="N13" s="28"/>
+      <c r="O13" s="28"/>
+      <c r="P13" s="28"/>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A14" s="26"/>
-      <c r="B14" s="26"/>
-      <c r="C14" s="26"/>
-      <c r="D14" s="26"/>
-      <c r="E14" s="26"/>
-      <c r="F14" s="26"/>
-      <c r="G14" s="26"/>
-      <c r="H14" s="26"/>
-      <c r="I14" s="26"/>
-      <c r="J14" s="26"/>
-      <c r="K14" s="26"/>
-      <c r="L14" s="26"/>
-      <c r="M14" s="26"/>
-      <c r="N14" s="26"/>
-      <c r="O14" s="26"/>
-      <c r="P14" s="26"/>
+      <c r="A14" s="28"/>
+      <c r="B14" s="28"/>
+      <c r="C14" s="28"/>
+      <c r="D14" s="28"/>
+      <c r="E14" s="28"/>
+      <c r="F14" s="28"/>
+      <c r="G14" s="28"/>
+      <c r="H14" s="28"/>
+      <c r="I14" s="28"/>
+      <c r="J14" s="28"/>
+      <c r="K14" s="28"/>
+      <c r="L14" s="28"/>
+      <c r="M14" s="28"/>
+      <c r="N14" s="28"/>
+      <c r="O14" s="28"/>
+      <c r="P14" s="28"/>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A15" s="26"/>
-      <c r="B15" s="26"/>
-      <c r="C15" s="26"/>
-      <c r="D15" s="26"/>
-      <c r="E15" s="26"/>
-      <c r="F15" s="26"/>
-      <c r="G15" s="26"/>
-      <c r="H15" s="26"/>
-      <c r="I15" s="26"/>
-      <c r="J15" s="26"/>
-      <c r="K15" s="26"/>
-      <c r="L15" s="26"/>
-      <c r="M15" s="26"/>
-      <c r="N15" s="26"/>
-      <c r="O15" s="26"/>
-      <c r="P15" s="26"/>
+      <c r="A15" s="28"/>
+      <c r="B15" s="28"/>
+      <c r="C15" s="28"/>
+      <c r="D15" s="28"/>
+      <c r="E15" s="28"/>
+      <c r="F15" s="28"/>
+      <c r="G15" s="28"/>
+      <c r="H15" s="28"/>
+      <c r="I15" s="28"/>
+      <c r="J15" s="28"/>
+      <c r="K15" s="28"/>
+      <c r="L15" s="28"/>
+      <c r="M15" s="28"/>
+      <c r="N15" s="28"/>
+      <c r="O15" s="28"/>
+      <c r="P15" s="28"/>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A16" s="26"/>
-      <c r="B16" s="26"/>
+      <c r="A16" s="28"/>
+      <c r="B16" s="28"/>
       <c r="C16" s="25"/>
       <c r="D16" s="25"/>
       <c r="E16" s="25"/>
@@ -3494,8 +3930,8 @@
       <c r="P16" s="25"/>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A17" s="26"/>
-      <c r="B17" s="26"/>
+      <c r="A17" s="28"/>
+      <c r="B17" s="28"/>
       <c r="C17" s="25"/>
       <c r="D17" s="25"/>
       <c r="E17" s="25"/>
@@ -3512,8 +3948,8 @@
       <c r="P17" s="25"/>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A18" s="26"/>
-      <c r="B18" s="26"/>
+      <c r="A18" s="28"/>
+      <c r="B18" s="28"/>
       <c r="C18" s="25"/>
       <c r="D18" s="25"/>
       <c r="E18" s="25"/>
@@ -3530,8 +3966,8 @@
       <c r="P18" s="25"/>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A19" s="26"/>
-      <c r="B19" s="26"/>
+      <c r="A19" s="28"/>
+      <c r="B19" s="28"/>
       <c r="C19" s="25"/>
       <c r="D19" s="25"/>
       <c r="E19" s="25"/>
@@ -3548,8 +3984,8 @@
       <c r="P19" s="25"/>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A20" s="26"/>
-      <c r="B20" s="26"/>
+      <c r="A20" s="28"/>
+      <c r="B20" s="28"/>
       <c r="C20" s="25"/>
       <c r="D20" s="25"/>
       <c r="E20" s="25"/>

--- a/1.xlsx
+++ b/1.xlsx
@@ -581,10 +581,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>26.6.15</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>敌人的碰撞击退根据核心线速度修正</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -612,6 +608,10 @@
       </rPr>
       <t>《几何竞技场》开发规划</t>
     </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>26.6.22</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1978,7 +1978,7 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A1" s="28" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B1" s="28"/>
       <c r="C1" s="28"/>
@@ -2056,21 +2056,23 @@
         <v>133</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>134</v>
-      </c>
-      <c r="E7" s="14"/>
+        <v>138</v>
+      </c>
+      <c r="E7" s="14">
+        <v>1</v>
+      </c>
       <c r="F7" s="9"/>
     </row>
     <row r="8" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="28"/>
       <c r="B8" s="26" t="s">
+        <v>134</v>
+      </c>
+      <c r="C8" s="26" t="s">
+        <v>136</v>
+      </c>
+      <c r="D8" s="26" t="s">
         <v>135</v>
-      </c>
-      <c r="C8" s="26" t="s">
-        <v>137</v>
-      </c>
-      <c r="D8" s="26" t="s">
-        <v>136</v>
       </c>
       <c r="E8" s="21"/>
       <c r="F8" s="26"/>

--- a/1.xlsx
+++ b/1.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="146">
   <si>
     <t>模块</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -612,6 +612,34 @@
   </si>
   <si>
     <t>26.6.22</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>待定</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"接轨"升级包</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>26.6.24</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>26.6.24</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>26.6.28</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"扩轨"升级包</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2074,23 +2102,43 @@
       <c r="D8" s="26" t="s">
         <v>135</v>
       </c>
-      <c r="E8" s="21"/>
-      <c r="F8" s="26"/>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="E8" s="21" t="s">
+        <v>139</v>
+      </c>
+      <c r="F8" s="26" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="28"/>
-      <c r="B9" s="26"/>
-      <c r="C9" s="26"/>
-      <c r="D9" s="26"/>
-      <c r="E9" s="21"/>
+      <c r="B9" s="26" t="s">
+        <v>141</v>
+      </c>
+      <c r="C9" s="26" t="s">
+        <v>142</v>
+      </c>
+      <c r="D9" s="26" t="s">
+        <v>143</v>
+      </c>
+      <c r="E9" s="21">
+        <v>1</v>
+      </c>
       <c r="F9" s="26"/>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="28"/>
-      <c r="B10" s="26"/>
-      <c r="C10" s="26"/>
-      <c r="D10" s="26"/>
-      <c r="E10" s="21"/>
+      <c r="B10" s="26" t="s">
+        <v>145</v>
+      </c>
+      <c r="C10" s="26" t="s">
+        <v>144</v>
+      </c>
+      <c r="D10" s="26" t="s">
+        <v>144</v>
+      </c>
+      <c r="E10" s="21">
+        <v>1</v>
+      </c>
       <c r="F10" s="26"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.15">

--- a/1.xlsx
+++ b/1.xlsx
@@ -4,20 +4,20 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9303"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="1"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="轨道核心" sheetId="4" r:id="rId2"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId3"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId4"/>
+    <sheet name="棱拳核心" sheetId="3" r:id="rId3"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId4"/>
   </sheets>
   <calcPr calcId="145621"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="145">
   <si>
     <t>模块</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -553,26 +553,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>近战核心构思2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>增大环绕半径（更安全但输出分散）或缩小半径（更危险但输出集中）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>刀片每旋转一周，下一次命中伤害递增（类似充能）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>增加刀片数量（3→4→5）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>《轨道》核心，角色周围有固定数量的几何刀片（如3个）持续环绕旋转刀片接触到敌人时造成伤害，并小幅击退</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>核心线速度与攻速、范围的关系</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -590,6 +570,38 @@
   </si>
   <si>
     <t>26.6.16</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>26.6.22</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>待定</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"接轨"升级包</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>26.6.24</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>26.6.24</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>26.6.28</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"扩轨"升级包</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -608,38 +620,58 @@
       </rPr>
       <t>《几何竞技场》开发规划</t>
     </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>26.6.22</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>待定</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>"接轨"升级包</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>26.6.24</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>26.6.24</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>26.6.28</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>"扩轨"升级包</t>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> —— 轨道核心</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>《几何竞技场》开发规划</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> —— 棱拳核心</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>核心介绍</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>升级包</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>生成拳头在角色身边，射程近、伤害高、攻速中等（0.6秒/次）; 攻击时拳头伸出→命中→收回，整个动作0.3秒; 命中敌人时附带轻微停顿。初始只有一个拳头, 可以拓展多一个拳头凑成一对, 交替出拳。最多同时拥有2对拳头, 每一对拳头使用一个脚本控制。将拳头视为子弹</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -647,7 +679,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -702,8 +734,24 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -722,6 +770,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -735,7 +789,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -813,6 +867,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -825,6 +882,18 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1142,33 +1211,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="29" t="s">
         <v>117</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
+      <c r="E1" s="29"/>
+      <c r="F1" s="29"/>
+      <c r="G1" s="29"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A2" s="28"/>
-      <c r="B2" s="28"/>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
-      <c r="F2" s="28"/>
-      <c r="G2" s="28"/>
+      <c r="A2" s="29"/>
+      <c r="B2" s="29"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="29"/>
+      <c r="F2" s="29"/>
+      <c r="G2" s="29"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A3" s="28"/>
-      <c r="B3" s="28"/>
-      <c r="C3" s="28"/>
-      <c r="D3" s="28"/>
-      <c r="E3" s="28"/>
-      <c r="F3" s="28"/>
-      <c r="G3" s="28"/>
+      <c r="A3" s="29"/>
+      <c r="B3" s="29"/>
+      <c r="C3" s="29"/>
+      <c r="D3" s="29"/>
+      <c r="E3" s="29"/>
+      <c r="F3" s="29"/>
+      <c r="G3" s="29"/>
     </row>
     <row r="4" spans="1:7" s="2" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="4" t="s">
@@ -1192,7 +1261,7 @@
       <c r="G4" s="5"/>
     </row>
     <row r="5" spans="1:7" s="2" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="29" t="s">
+      <c r="A5" s="30" t="s">
         <v>2</v>
       </c>
       <c r="B5" s="9" t="s">
@@ -1213,7 +1282,7 @@
       <c r="G5" s="7"/>
     </row>
     <row r="6" spans="1:7" ht="30.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="29"/>
+      <c r="A6" s="30"/>
       <c r="B6" s="3" t="s">
         <v>113</v>
       </c>
@@ -1231,7 +1300,7 @@
       </c>
     </row>
     <row r="7" spans="1:7" ht="48" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="28" t="s">
+      <c r="A7" s="29" t="s">
         <v>11</v>
       </c>
       <c r="B7" s="13" t="s">
@@ -1251,7 +1320,7 @@
       </c>
     </row>
     <row r="8" spans="1:7" ht="27" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="28"/>
+      <c r="A8" s="29"/>
       <c r="B8" s="3" t="s">
         <v>93</v>
       </c>
@@ -1269,7 +1338,7 @@
       </c>
     </row>
     <row r="9" spans="1:7" ht="27" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="28"/>
+      <c r="A9" s="29"/>
       <c r="B9" s="24" t="s">
         <v>122</v>
       </c>
@@ -1285,7 +1354,7 @@
       </c>
     </row>
     <row r="10" spans="1:7" ht="27" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="28"/>
+      <c r="A10" s="29"/>
       <c r="B10" s="20" t="s">
         <v>97</v>
       </c>
@@ -1303,7 +1372,7 @@
       </c>
     </row>
     <row r="11" spans="1:7" ht="38.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A11" s="28" t="s">
+      <c r="A11" s="29" t="s">
         <v>22</v>
       </c>
       <c r="B11" s="13" t="s">
@@ -1321,14 +1390,14 @@
       <c r="F11" s="13"/>
     </row>
     <row r="12" spans="1:7" ht="38.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A12" s="28"/>
+      <c r="A12" s="29"/>
       <c r="B12" s="3" t="s">
         <v>24</v>
       </c>
       <c r="F12" s="19"/>
     </row>
     <row r="13" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A13" s="28"/>
+      <c r="A13" s="29"/>
       <c r="B13" s="9" t="s">
         <v>5</v>
       </c>
@@ -1347,7 +1416,7 @@
       <c r="G13" s="7"/>
     </row>
     <row r="14" spans="1:7" s="2" customFormat="1" ht="69.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A14" s="29" t="s">
+      <c r="A14" s="30" t="s">
         <v>105</v>
       </c>
       <c r="B14" s="6" t="s">
@@ -1368,7 +1437,7 @@
       <c r="G14" s="7"/>
     </row>
     <row r="15" spans="1:7" s="2" customFormat="1" ht="47.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A15" s="29"/>
+      <c r="A15" s="30"/>
       <c r="B15" s="9" t="s">
         <v>25</v>
       </c>
@@ -1387,7 +1456,7 @@
       <c r="G15" s="7"/>
     </row>
     <row r="16" spans="1:7" s="2" customFormat="1" ht="47.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A16" s="29"/>
+      <c r="A16" s="30"/>
       <c r="B16" s="15" t="s">
         <v>65</v>
       </c>
@@ -1406,7 +1475,7 @@
       <c r="G16" s="7"/>
     </row>
     <row r="17" spans="1:7" s="2" customFormat="1" ht="47.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A17" s="29"/>
+      <c r="A17" s="30"/>
       <c r="B17" s="15" t="s">
         <v>83</v>
       </c>
@@ -1425,7 +1494,7 @@
       <c r="G17" s="7"/>
     </row>
     <row r="18" spans="1:7" s="2" customFormat="1" ht="47.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A18" s="29"/>
+      <c r="A18" s="30"/>
       <c r="B18" s="15" t="s">
         <v>70</v>
       </c>
@@ -1444,7 +1513,7 @@
       <c r="G18" s="7"/>
     </row>
     <row r="19" spans="1:7" s="2" customFormat="1" ht="47.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A19" s="29" t="s">
+      <c r="A19" s="30" t="s">
         <v>104</v>
       </c>
       <c r="B19" s="6" t="s">
@@ -1457,7 +1526,7 @@
       <c r="G19" s="7"/>
     </row>
     <row r="20" spans="1:7" s="2" customFormat="1" ht="47.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A20" s="29"/>
+      <c r="A20" s="30"/>
       <c r="B20" s="22" t="s">
         <v>100</v>
       </c>
@@ -1476,7 +1545,7 @@
       <c r="G20" s="7"/>
     </row>
     <row r="21" spans="1:7" s="2" customFormat="1" ht="47.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A21" s="29"/>
+      <c r="A21" s="30"/>
       <c r="B21" s="18" t="s">
         <v>94</v>
       </c>
@@ -1495,7 +1564,7 @@
       <c r="G21" s="7"/>
     </row>
     <row r="22" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A22" s="29"/>
+      <c r="A22" s="30"/>
       <c r="B22" s="9" t="s">
         <v>20</v>
       </c>
@@ -1514,7 +1583,7 @@
       <c r="G22" s="7"/>
     </row>
     <row r="23" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A23" s="29"/>
+      <c r="A23" s="30"/>
       <c r="B23" s="9" t="s">
         <v>29</v>
       </c>
@@ -1533,7 +1602,7 @@
       <c r="G23" s="7"/>
     </row>
     <row r="24" spans="1:7" s="2" customFormat="1" ht="48.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A24" s="29"/>
+      <c r="A24" s="30"/>
       <c r="B24" s="9" t="s">
         <v>34</v>
       </c>
@@ -1552,7 +1621,7 @@
       <c r="G24" s="7"/>
     </row>
     <row r="25" spans="1:7" s="2" customFormat="1" ht="48.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A25" s="29"/>
+      <c r="A25" s="30"/>
       <c r="B25" s="9" t="s">
         <v>6</v>
       </c>
@@ -1571,7 +1640,7 @@
       <c r="G25" s="7"/>
     </row>
     <row r="26" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A26" s="29"/>
+      <c r="A26" s="30"/>
       <c r="B26" s="9" t="s">
         <v>27</v>
       </c>
@@ -1590,7 +1659,7 @@
       <c r="G26" s="7"/>
     </row>
     <row r="27" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A27" s="29"/>
+      <c r="A27" s="30"/>
       <c r="B27" s="9" t="s">
         <v>43</v>
       </c>
@@ -1609,7 +1678,7 @@
       <c r="G27" s="7"/>
     </row>
     <row r="28" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A28" s="29"/>
+      <c r="A28" s="30"/>
       <c r="B28" s="9" t="s">
         <v>51</v>
       </c>
@@ -1628,7 +1697,7 @@
       <c r="G28" s="7"/>
     </row>
     <row r="29" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A29" s="29"/>
+      <c r="A29" s="30"/>
       <c r="B29" s="9" t="s">
         <v>63</v>
       </c>
@@ -1647,7 +1716,7 @@
       <c r="G29" s="7"/>
     </row>
     <row r="30" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A30" s="29" t="s">
+      <c r="A30" s="30" t="s">
         <v>47</v>
       </c>
       <c r="B30" s="9" t="s">
@@ -1668,7 +1737,7 @@
       <c r="G30" s="7"/>
     </row>
     <row r="31" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A31" s="29"/>
+      <c r="A31" s="30"/>
       <c r="B31" s="9" t="s">
         <v>48</v>
       </c>
@@ -1687,7 +1756,7 @@
       <c r="G31" s="7"/>
     </row>
     <row r="32" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A32" s="29"/>
+      <c r="A32" s="30"/>
       <c r="B32" s="15" t="s">
         <v>68</v>
       </c>
@@ -1706,7 +1775,7 @@
       <c r="G32" s="7"/>
     </row>
     <row r="33" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A33" s="29"/>
+      <c r="A33" s="30"/>
       <c r="B33" s="15" t="s">
         <v>80</v>
       </c>
@@ -1725,7 +1794,7 @@
       <c r="G33" s="7"/>
     </row>
     <row r="34" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A34" s="29"/>
+      <c r="A34" s="30"/>
       <c r="B34" s="9" t="s">
         <v>67</v>
       </c>
@@ -1744,7 +1813,7 @@
       <c r="G34" s="7"/>
     </row>
     <row r="35" spans="1:7" s="2" customFormat="1" ht="33.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A35" s="29"/>
+      <c r="A35" s="30"/>
       <c r="B35" s="6" t="s">
         <v>41</v>
       </c>
@@ -2005,33 +2074,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A1" s="28" t="s">
-        <v>137</v>
-      </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
+      <c r="A1" s="29" t="s">
+        <v>140</v>
+      </c>
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
+      <c r="E1" s="29"/>
+      <c r="F1" s="29"/>
+      <c r="G1" s="29"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A2" s="28"/>
-      <c r="B2" s="28"/>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
-      <c r="F2" s="28"/>
-      <c r="G2" s="28"/>
+      <c r="A2" s="29"/>
+      <c r="B2" s="29"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="29"/>
+      <c r="F2" s="29"/>
+      <c r="G2" s="29"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A3" s="28"/>
-      <c r="B3" s="28"/>
-      <c r="C3" s="28"/>
-      <c r="D3" s="28"/>
-      <c r="E3" s="28"/>
-      <c r="F3" s="28"/>
-      <c r="G3" s="28"/>
+      <c r="A3" s="29"/>
+      <c r="B3" s="29"/>
+      <c r="C3" s="29"/>
+      <c r="D3" s="29"/>
+      <c r="E3" s="29"/>
+      <c r="F3" s="29"/>
+      <c r="G3" s="29"/>
     </row>
     <row r="4" spans="1:7" ht="18.75" x14ac:dyDescent="0.15">
       <c r="A4" s="4" t="s">
@@ -2055,7 +2124,7 @@
       <c r="G4" s="5"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A5" s="29" t="s">
+      <c r="A5" s="30" t="s">
         <v>2</v>
       </c>
       <c r="B5" s="9"/>
@@ -2066,25 +2135,25 @@
       <c r="G5" s="7"/>
     </row>
     <row r="6" spans="1:7" ht="33.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="29"/>
-      <c r="B6" s="26"/>
-      <c r="C6" s="26"/>
-      <c r="D6" s="26"/>
+      <c r="A6" s="30"/>
+      <c r="B6" s="25"/>
+      <c r="C6" s="25"/>
+      <c r="D6" s="25"/>
       <c r="E6" s="21"/>
-      <c r="F6" s="26"/>
+      <c r="F6" s="25"/>
     </row>
     <row r="7" spans="1:7" ht="34.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="28" t="s">
+      <c r="A7" s="29" t="s">
         <v>11</v>
       </c>
       <c r="B7" s="13" t="s">
+        <v>127</v>
+      </c>
+      <c r="C7" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="D7" s="13" t="s">
         <v>132</v>
-      </c>
-      <c r="C7" s="13" t="s">
-        <v>133</v>
-      </c>
-      <c r="D7" s="13" t="s">
-        <v>138</v>
       </c>
       <c r="E7" s="14">
         <v>1</v>
@@ -2092,57 +2161,57 @@
       <c r="F7" s="9"/>
     </row>
     <row r="8" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="28"/>
-      <c r="B8" s="26" t="s">
+      <c r="A8" s="29"/>
+      <c r="B8" s="25" t="s">
+        <v>129</v>
+      </c>
+      <c r="C8" s="25" t="s">
+        <v>131</v>
+      </c>
+      <c r="D8" s="25" t="s">
+        <v>130</v>
+      </c>
+      <c r="E8" s="21" t="s">
+        <v>133</v>
+      </c>
+      <c r="F8" s="25" t="s">
         <v>134</v>
       </c>
-      <c r="C8" s="26" t="s">
+    </row>
+    <row r="9" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A9" s="29"/>
+      <c r="B9" s="25" t="s">
+        <v>135</v>
+      </c>
+      <c r="C9" s="25" t="s">
         <v>136</v>
       </c>
-      <c r="D8" s="26" t="s">
-        <v>135</v>
-      </c>
-      <c r="E8" s="21" t="s">
-        <v>139</v>
-      </c>
-      <c r="F8" s="26" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="28"/>
-      <c r="B9" s="26" t="s">
-        <v>141</v>
-      </c>
-      <c r="C9" s="26" t="s">
-        <v>142</v>
-      </c>
-      <c r="D9" s="26" t="s">
-        <v>143</v>
+      <c r="D9" s="25" t="s">
+        <v>137</v>
       </c>
       <c r="E9" s="21">
         <v>1</v>
       </c>
-      <c r="F9" s="26"/>
+      <c r="F9" s="25"/>
     </row>
     <row r="10" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="28"/>
-      <c r="B10" s="26" t="s">
-        <v>145</v>
-      </c>
-      <c r="C10" s="26" t="s">
-        <v>144</v>
-      </c>
-      <c r="D10" s="26" t="s">
-        <v>144</v>
+      <c r="A10" s="29"/>
+      <c r="B10" s="25" t="s">
+        <v>139</v>
+      </c>
+      <c r="C10" s="25" t="s">
+        <v>138</v>
+      </c>
+      <c r="D10" s="25" t="s">
+        <v>138</v>
       </c>
       <c r="E10" s="21">
         <v>1</v>
       </c>
-      <c r="F10" s="26"/>
+      <c r="F10" s="25"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A11" s="28" t="s">
+      <c r="A11" s="29" t="s">
         <v>22</v>
       </c>
       <c r="B11" s="13"/>
@@ -2152,15 +2221,15 @@
       <c r="F11" s="13"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A12" s="28"/>
-      <c r="B12" s="26"/>
-      <c r="C12" s="26"/>
-      <c r="D12" s="26"/>
-      <c r="E12" s="26"/>
-      <c r="F12" s="27"/>
+      <c r="A12" s="29"/>
+      <c r="B12" s="25"/>
+      <c r="C12" s="25"/>
+      <c r="D12" s="25"/>
+      <c r="E12" s="25"/>
+      <c r="F12" s="26"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A13" s="28"/>
+      <c r="A13" s="29"/>
       <c r="B13" s="9"/>
       <c r="C13" s="10"/>
       <c r="D13" s="11"/>
@@ -2169,18 +2238,18 @@
       <c r="G13" s="7"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A14" s="29" t="s">
+      <c r="A14" s="30" t="s">
         <v>105</v>
       </c>
-      <c r="B14" s="27"/>
-      <c r="C14" s="27"/>
-      <c r="D14" s="27"/>
+      <c r="B14" s="26"/>
+      <c r="C14" s="26"/>
+      <c r="D14" s="26"/>
       <c r="E14" s="17"/>
-      <c r="F14" s="27"/>
+      <c r="F14" s="26"/>
       <c r="G14" s="7"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A15" s="29"/>
+      <c r="A15" s="30"/>
       <c r="B15" s="9"/>
       <c r="C15" s="9"/>
       <c r="D15" s="9"/>
@@ -2189,7 +2258,7 @@
       <c r="G15" s="7"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A16" s="29"/>
+      <c r="A16" s="30"/>
       <c r="B16" s="15"/>
       <c r="C16" s="15"/>
       <c r="D16" s="15"/>
@@ -2198,7 +2267,7 @@
       <c r="G16" s="7"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A17" s="29"/>
+      <c r="A17" s="30"/>
       <c r="B17" s="15"/>
       <c r="C17" s="15"/>
       <c r="D17" s="15"/>
@@ -2207,7 +2276,7 @@
       <c r="G17" s="7"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A18" s="29"/>
+      <c r="A18" s="30"/>
       <c r="B18" s="15"/>
       <c r="C18" s="15"/>
       <c r="D18" s="15"/>
@@ -2216,36 +2285,36 @@
       <c r="G18" s="7"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A19" s="29" t="s">
+      <c r="A19" s="30" t="s">
         <v>104</v>
       </c>
-      <c r="B19" s="27"/>
+      <c r="B19" s="26"/>
       <c r="C19" s="8"/>
       <c r="D19" s="8"/>
-      <c r="E19" s="27"/>
-      <c r="F19" s="27"/>
+      <c r="E19" s="26"/>
+      <c r="F19" s="26"/>
       <c r="G19" s="7"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A20" s="29"/>
-      <c r="B20" s="27"/>
+      <c r="A20" s="30"/>
+      <c r="B20" s="26"/>
       <c r="C20" s="8"/>
       <c r="D20" s="8"/>
       <c r="E20" s="17"/>
-      <c r="F20" s="27"/>
+      <c r="F20" s="26"/>
       <c r="G20" s="7"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A21" s="29"/>
-      <c r="B21" s="27"/>
+      <c r="A21" s="30"/>
+      <c r="B21" s="26"/>
       <c r="C21" s="8"/>
       <c r="D21" s="8"/>
       <c r="E21" s="17"/>
-      <c r="F21" s="27"/>
+      <c r="F21" s="26"/>
       <c r="G21" s="7"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A22" s="29"/>
+      <c r="A22" s="30"/>
       <c r="B22" s="9"/>
       <c r="C22" s="9"/>
       <c r="D22" s="11"/>
@@ -2254,7 +2323,7 @@
       <c r="G22" s="7"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A23" s="29"/>
+      <c r="A23" s="30"/>
       <c r="B23" s="9"/>
       <c r="C23" s="9"/>
       <c r="D23" s="9"/>
@@ -2263,7 +2332,7 @@
       <c r="G23" s="7"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A24" s="29"/>
+      <c r="A24" s="30"/>
       <c r="B24" s="9"/>
       <c r="C24" s="9"/>
       <c r="D24" s="9"/>
@@ -2272,7 +2341,7 @@
       <c r="G24" s="7"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A25" s="29"/>
+      <c r="A25" s="30"/>
       <c r="B25" s="9"/>
       <c r="C25" s="9"/>
       <c r="D25" s="9"/>
@@ -2281,7 +2350,7 @@
       <c r="G25" s="7"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A26" s="29"/>
+      <c r="A26" s="30"/>
       <c r="B26" s="9"/>
       <c r="C26" s="9"/>
       <c r="D26" s="9"/>
@@ -2290,7 +2359,7 @@
       <c r="G26" s="7"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A27" s="29"/>
+      <c r="A27" s="30"/>
       <c r="B27" s="9"/>
       <c r="C27" s="9"/>
       <c r="D27" s="9"/>
@@ -2299,7 +2368,7 @@
       <c r="G27" s="7"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A28" s="29"/>
+      <c r="A28" s="30"/>
       <c r="B28" s="9"/>
       <c r="C28" s="9"/>
       <c r="D28" s="9"/>
@@ -2308,7 +2377,7 @@
       <c r="G28" s="7"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A29" s="29"/>
+      <c r="A29" s="30"/>
       <c r="B29" s="9"/>
       <c r="C29" s="9"/>
       <c r="D29" s="9"/>
@@ -2317,7 +2386,7 @@
       <c r="G29" s="7"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A30" s="29" t="s">
+      <c r="A30" s="30" t="s">
         <v>47</v>
       </c>
       <c r="B30" s="9"/>
@@ -2328,7 +2397,7 @@
       <c r="G30" s="7"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A31" s="29"/>
+      <c r="A31" s="30"/>
       <c r="B31" s="9"/>
       <c r="C31" s="9"/>
       <c r="D31" s="9"/>
@@ -2337,7 +2406,7 @@
       <c r="G31" s="7"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A32" s="29"/>
+      <c r="A32" s="30"/>
       <c r="B32" s="15"/>
       <c r="C32" s="15"/>
       <c r="D32" s="15"/>
@@ -2346,7 +2415,7 @@
       <c r="G32" s="7"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A33" s="29"/>
+      <c r="A33" s="30"/>
       <c r="B33" s="15"/>
       <c r="C33" s="15"/>
       <c r="D33" s="15"/>
@@ -2355,7 +2424,7 @@
       <c r="G33" s="7"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A34" s="29"/>
+      <c r="A34" s="30"/>
       <c r="B34" s="9"/>
       <c r="C34" s="9"/>
       <c r="D34" s="9"/>
@@ -2364,16 +2433,16 @@
       <c r="G34" s="7"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A35" s="29"/>
-      <c r="B35" s="27"/>
-      <c r="C35" s="27"/>
-      <c r="D35" s="27"/>
-      <c r="E35" s="27"/>
-      <c r="F35" s="27"/>
+      <c r="A35" s="30"/>
+      <c r="B35" s="26"/>
+      <c r="C35" s="26"/>
+      <c r="D35" s="26"/>
+      <c r="E35" s="26"/>
+      <c r="F35" s="26"/>
       <c r="G35" s="7"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A36" s="27" t="s">
+      <c r="A36" s="26" t="s">
         <v>79</v>
       </c>
       <c r="B36" s="15"/>
@@ -2401,322 +2470,968 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:P56"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <cols>
+    <col min="1" max="1" width="12.375" customWidth="1"/>
+    <col min="2" max="2" width="39.125" customWidth="1"/>
+    <col min="3" max="3" width="19.625" customWidth="1"/>
+    <col min="4" max="4" width="25.5" customWidth="1"/>
+    <col min="5" max="5" width="20.125" customWidth="1"/>
+    <col min="6" max="6" width="51.125" customWidth="1"/>
+    <col min="7" max="7" width="2" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1" s="29" t="s">
+        <v>141</v>
+      </c>
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
+      <c r="E1" s="29"/>
+      <c r="F1" s="29"/>
+      <c r="G1" s="29"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
+      <c r="O1" s="2"/>
+      <c r="P1" s="2"/>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.15">
+      <c r="A2" s="29"/>
+      <c r="B2" s="29"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="29"/>
+      <c r="F2" s="29"/>
+      <c r="G2" s="29"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
+      <c r="M2" s="2"/>
+      <c r="N2" s="2"/>
+      <c r="O2" s="2"/>
+      <c r="P2" s="2"/>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.15">
+      <c r="A3" s="29"/>
+      <c r="B3" s="29"/>
+      <c r="C3" s="29"/>
+      <c r="D3" s="29"/>
+      <c r="E3" s="29"/>
+      <c r="F3" s="29"/>
+      <c r="G3" s="29"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2"/>
+      <c r="M3" s="2"/>
+      <c r="N3" s="2"/>
+      <c r="O3" s="2"/>
+      <c r="P3" s="2"/>
+    </row>
+    <row r="4" spans="1:16" ht="18.75" x14ac:dyDescent="0.15">
+      <c r="A4" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4" s="5"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+      <c r="M4" s="2"/>
+      <c r="N4" s="2"/>
+      <c r="O4" s="2"/>
+      <c r="P4" s="2"/>
+    </row>
+    <row r="5" spans="1:16" ht="18.75" x14ac:dyDescent="0.15">
+      <c r="A5" s="33" t="s">
+        <v>142</v>
+      </c>
+      <c r="B5" s="34" t="s">
+        <v>144</v>
+      </c>
+      <c r="C5" s="34"/>
+      <c r="D5" s="34"/>
+      <c r="E5" s="34"/>
+      <c r="F5" s="34"/>
+      <c r="G5" s="32"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2"/>
+      <c r="L5" s="2"/>
+      <c r="M5" s="2"/>
+      <c r="N5" s="2"/>
+      <c r="O5" s="2"/>
+      <c r="P5" s="2"/>
+    </row>
+    <row r="6" spans="1:16" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A6" s="35"/>
+      <c r="B6" s="34"/>
+      <c r="C6" s="34"/>
+      <c r="D6" s="34"/>
+      <c r="E6" s="34"/>
+      <c r="F6" s="34"/>
+      <c r="G6" s="32"/>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2"/>
+      <c r="J6" s="2"/>
+      <c r="K6" s="2"/>
+      <c r="L6" s="2"/>
+      <c r="M6" s="2"/>
+      <c r="N6" s="2"/>
+      <c r="O6" s="2"/>
+      <c r="P6" s="2"/>
+    </row>
+    <row r="7" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A7" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="B7" s="9"/>
+      <c r="C7" s="11"/>
+      <c r="D7" s="10"/>
+      <c r="E7" s="12"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
+      <c r="J7" s="2"/>
+      <c r="K7" s="2"/>
+      <c r="L7" s="2"/>
+      <c r="M7" s="2"/>
+      <c r="N7" s="2"/>
+      <c r="O7" s="2"/>
+      <c r="P7" s="2"/>
+    </row>
+    <row r="8" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A8" s="30"/>
+      <c r="B8" s="27"/>
+      <c r="C8" s="27"/>
+      <c r="D8" s="27"/>
+      <c r="E8" s="21"/>
+      <c r="F8" s="27"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2"/>
+      <c r="K8" s="2"/>
+      <c r="L8" s="2"/>
+      <c r="M8" s="2"/>
+      <c r="N8" s="2"/>
+      <c r="O8" s="2"/>
+      <c r="P8" s="2"/>
+    </row>
+    <row r="9" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A9" s="30" t="s">
+        <v>143</v>
+      </c>
+      <c r="B9" s="27"/>
+      <c r="C9" s="27"/>
+      <c r="D9" s="27"/>
+      <c r="E9" s="21"/>
+      <c r="F9" s="27"/>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
+      <c r="J9" s="2"/>
+      <c r="K9" s="2"/>
+      <c r="L9" s="2"/>
+      <c r="M9" s="2"/>
+      <c r="N9" s="2"/>
+      <c r="O9" s="2"/>
+      <c r="P9" s="2"/>
+    </row>
+    <row r="10" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A10" s="30"/>
+      <c r="B10" s="27"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="21"/>
+      <c r="F10" s="27"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="2"/>
+      <c r="K10" s="2"/>
+      <c r="L10" s="2"/>
+      <c r="M10" s="2"/>
+      <c r="N10" s="2"/>
+      <c r="O10" s="2"/>
+      <c r="P10" s="2"/>
+    </row>
+    <row r="11" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A11" s="30"/>
+      <c r="B11" s="27"/>
+      <c r="C11" s="27"/>
+      <c r="D11" s="27"/>
+      <c r="E11" s="21"/>
+      <c r="F11" s="27"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+      <c r="J11" s="2"/>
+      <c r="K11" s="2"/>
+      <c r="L11" s="2"/>
+      <c r="M11" s="2"/>
+      <c r="N11" s="2"/>
+      <c r="O11" s="2"/>
+      <c r="P11" s="2"/>
+    </row>
+    <row r="12" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A12" s="30"/>
+      <c r="B12" s="27"/>
+      <c r="C12" s="27"/>
+      <c r="D12" s="27"/>
+      <c r="E12" s="21"/>
+      <c r="F12" s="27"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2"/>
+      <c r="K12" s="2"/>
+      <c r="L12" s="2"/>
+      <c r="M12" s="2"/>
+      <c r="N12" s="2"/>
+      <c r="O12" s="2"/>
+      <c r="P12" s="2"/>
+    </row>
+    <row r="13" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A13" s="29" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13" s="13"/>
+      <c r="C13" s="13"/>
+      <c r="D13" s="13"/>
+      <c r="E13" s="14"/>
+      <c r="F13" s="9"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="2"/>
+      <c r="K13" s="2"/>
+      <c r="L13" s="2"/>
+      <c r="M13" s="2"/>
+      <c r="N13" s="2"/>
+      <c r="O13" s="2"/>
+      <c r="P13" s="2"/>
+    </row>
+    <row r="14" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A14" s="29"/>
+      <c r="B14" s="27"/>
+      <c r="C14" s="27"/>
+      <c r="D14" s="27"/>
+      <c r="E14" s="21"/>
+      <c r="F14" s="27"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="2"/>
+      <c r="K14" s="2"/>
+      <c r="L14" s="2"/>
+      <c r="M14" s="2"/>
+      <c r="N14" s="2"/>
+      <c r="O14" s="2"/>
+      <c r="P14" s="2"/>
+    </row>
+    <row r="15" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A15" s="29"/>
+      <c r="B15" s="27"/>
+      <c r="C15" s="27"/>
+      <c r="D15" s="27"/>
+      <c r="E15" s="21"/>
+      <c r="F15" s="27"/>
+      <c r="G15" s="7"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="2"/>
+      <c r="K15" s="2"/>
+      <c r="L15" s="2"/>
+      <c r="M15" s="2"/>
+      <c r="N15" s="2"/>
+      <c r="O15" s="2"/>
+      <c r="P15" s="2"/>
+    </row>
+    <row r="16" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A16" s="29"/>
+      <c r="B16" s="27"/>
+      <c r="C16" s="27"/>
+      <c r="D16" s="27"/>
+      <c r="E16" s="21"/>
+      <c r="F16" s="27"/>
+      <c r="G16" s="7"/>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="2"/>
+      <c r="K16" s="2"/>
+      <c r="L16" s="2"/>
+      <c r="M16" s="2"/>
+      <c r="N16" s="2"/>
+      <c r="O16" s="2"/>
+      <c r="P16" s="2"/>
+    </row>
+    <row r="17" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A17" s="29" t="s">
+        <v>22</v>
+      </c>
+      <c r="B17" s="13"/>
+      <c r="C17" s="13"/>
+      <c r="D17" s="13"/>
+      <c r="E17" s="14"/>
+      <c r="F17" s="13"/>
+      <c r="G17" s="7"/>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
+      <c r="J17" s="2"/>
+      <c r="K17" s="2"/>
+      <c r="L17" s="2"/>
+      <c r="M17" s="2"/>
+      <c r="N17" s="2"/>
+      <c r="O17" s="2"/>
+      <c r="P17" s="2"/>
+    </row>
+    <row r="18" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A18" s="29"/>
+      <c r="B18" s="27"/>
+      <c r="C18" s="27"/>
+      <c r="D18" s="27"/>
+      <c r="E18" s="27"/>
+      <c r="F18" s="28"/>
+      <c r="G18" s="7"/>
+      <c r="H18" s="27"/>
+      <c r="I18" s="27"/>
+      <c r="J18" s="27"/>
+      <c r="K18" s="27"/>
+      <c r="L18" s="27"/>
+      <c r="M18" s="27"/>
+      <c r="N18" s="27"/>
+      <c r="O18" s="27"/>
+      <c r="P18" s="27"/>
+    </row>
+    <row r="19" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A19" s="29"/>
+      <c r="B19" s="9"/>
+      <c r="C19" s="10"/>
+      <c r="D19" s="11"/>
+      <c r="E19" s="12"/>
+      <c r="F19" s="9"/>
+      <c r="G19" s="7"/>
+      <c r="H19" s="27"/>
+      <c r="I19" s="27"/>
+      <c r="J19" s="27"/>
+      <c r="K19" s="27"/>
+      <c r="L19" s="27"/>
+      <c r="M19" s="27"/>
+      <c r="N19" s="27"/>
+      <c r="O19" s="27"/>
+      <c r="P19" s="27"/>
+    </row>
+    <row r="20" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A20" s="30" t="s">
+        <v>105</v>
+      </c>
+      <c r="B20" s="28"/>
+      <c r="C20" s="28"/>
+      <c r="D20" s="28"/>
+      <c r="E20" s="17"/>
+      <c r="F20" s="28"/>
+      <c r="G20" s="7"/>
+      <c r="H20" s="27"/>
+      <c r="I20" s="27"/>
+      <c r="J20" s="27"/>
+      <c r="K20" s="27"/>
+      <c r="L20" s="27"/>
+      <c r="M20" s="27"/>
+      <c r="N20" s="27"/>
+      <c r="O20" s="27"/>
+      <c r="P20" s="27"/>
+    </row>
+    <row r="21" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A21" s="30"/>
+      <c r="B21" s="9"/>
+      <c r="C21" s="9"/>
+      <c r="D21" s="9"/>
+      <c r="E21" s="12"/>
+      <c r="F21" s="9"/>
+      <c r="G21" s="7"/>
+      <c r="H21" s="27"/>
+      <c r="I21" s="27"/>
+      <c r="J21" s="27"/>
+      <c r="K21" s="27"/>
+      <c r="L21" s="27"/>
+      <c r="M21" s="27"/>
+      <c r="N21" s="27"/>
+      <c r="O21" s="27"/>
+      <c r="P21" s="27"/>
+    </row>
+    <row r="22" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A22" s="30"/>
+      <c r="B22" s="15"/>
+      <c r="C22" s="15"/>
+      <c r="D22" s="15"/>
+      <c r="E22" s="16"/>
+      <c r="F22" s="15"/>
+      <c r="G22" s="7"/>
+      <c r="H22" s="27"/>
+      <c r="I22" s="27"/>
+      <c r="J22" s="27"/>
+      <c r="K22" s="27"/>
+      <c r="L22" s="27"/>
+      <c r="M22" s="27"/>
+      <c r="N22" s="27"/>
+      <c r="O22" s="27"/>
+      <c r="P22" s="27"/>
+    </row>
+    <row r="23" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A23" s="30"/>
+      <c r="B23" s="15"/>
+      <c r="C23" s="15"/>
+      <c r="D23" s="15"/>
+      <c r="E23" s="16"/>
+      <c r="F23" s="15"/>
+      <c r="G23" s="7"/>
+    </row>
+    <row r="24" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A24" s="30"/>
+      <c r="B24" s="15"/>
+      <c r="C24" s="15"/>
+      <c r="D24" s="15"/>
+      <c r="E24" s="16"/>
+      <c r="F24" s="15"/>
+      <c r="G24" s="7"/>
+    </row>
+    <row r="25" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A25" s="30" t="s">
+        <v>104</v>
+      </c>
+      <c r="B25" s="28"/>
+      <c r="C25" s="8"/>
+      <c r="D25" s="8"/>
+      <c r="E25" s="28"/>
+      <c r="F25" s="28"/>
+      <c r="G25" s="7"/>
+    </row>
+    <row r="26" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A26" s="30"/>
+      <c r="B26" s="28"/>
+      <c r="C26" s="8"/>
+      <c r="D26" s="8"/>
+      <c r="E26" s="17"/>
+      <c r="F26" s="28"/>
+      <c r="G26" s="7"/>
+    </row>
+    <row r="27" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A27" s="30"/>
+      <c r="B27" s="28"/>
+      <c r="C27" s="8"/>
+      <c r="D27" s="8"/>
+      <c r="E27" s="17"/>
+      <c r="F27" s="28"/>
+      <c r="G27" s="7"/>
+    </row>
+    <row r="28" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A28" s="30"/>
+      <c r="B28" s="9"/>
+      <c r="C28" s="9"/>
+      <c r="D28" s="11"/>
+      <c r="E28" s="12"/>
+      <c r="F28" s="9"/>
+      <c r="G28" s="7"/>
+    </row>
+    <row r="29" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A29" s="30"/>
+      <c r="B29" s="9"/>
+      <c r="C29" s="9"/>
+      <c r="D29" s="9"/>
+      <c r="E29" s="12"/>
+      <c r="F29" s="9"/>
+      <c r="G29" s="7"/>
+    </row>
+    <row r="30" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A30" s="30"/>
+      <c r="B30" s="9"/>
+      <c r="C30" s="9"/>
+      <c r="D30" s="9"/>
+      <c r="E30" s="12"/>
+      <c r="F30" s="9"/>
+      <c r="G30" s="7"/>
+    </row>
+    <row r="31" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A31" s="30"/>
+      <c r="B31" s="9"/>
+      <c r="C31" s="9"/>
+      <c r="D31" s="9"/>
+      <c r="E31" s="12"/>
+      <c r="F31" s="9"/>
+      <c r="G31" s="7"/>
+    </row>
+    <row r="32" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A32" s="30"/>
+      <c r="B32" s="9"/>
+      <c r="C32" s="9"/>
+      <c r="D32" s="9"/>
+      <c r="E32" s="12"/>
+      <c r="F32" s="9"/>
+      <c r="G32" s="7"/>
+    </row>
+    <row r="33" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A33" s="30"/>
+      <c r="B33" s="9"/>
+      <c r="C33" s="9"/>
+      <c r="D33" s="9"/>
+      <c r="E33" s="12"/>
+      <c r="F33" s="9"/>
+      <c r="G33" s="7"/>
+    </row>
+    <row r="34" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A34" s="30"/>
+      <c r="B34" s="9"/>
+      <c r="C34" s="9"/>
+      <c r="D34" s="9"/>
+      <c r="E34" s="12"/>
+      <c r="F34" s="9"/>
+      <c r="G34" s="7"/>
+    </row>
+    <row r="35" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A35" s="30"/>
+      <c r="B35" s="9"/>
+      <c r="C35" s="9"/>
+      <c r="D35" s="9"/>
+      <c r="E35" s="12"/>
+      <c r="F35" s="9"/>
+      <c r="G35" s="7"/>
+    </row>
+    <row r="36" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A36" s="30" t="s">
+        <v>47</v>
+      </c>
+      <c r="B36" s="9"/>
+      <c r="C36" s="9"/>
+      <c r="D36" s="9"/>
+      <c r="E36" s="12"/>
+      <c r="F36" s="9"/>
+      <c r="G36" s="7"/>
+    </row>
+    <row r="37" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A37" s="30"/>
+      <c r="B37" s="9"/>
+      <c r="C37" s="9"/>
+      <c r="D37" s="9"/>
+      <c r="E37" s="12"/>
+      <c r="F37" s="9"/>
+      <c r="G37" s="7"/>
+    </row>
+    <row r="38" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A38" s="30"/>
+      <c r="B38" s="15"/>
+      <c r="C38" s="15"/>
+      <c r="D38" s="15"/>
+      <c r="E38" s="16"/>
+      <c r="F38" s="15"/>
+      <c r="G38" s="7"/>
+    </row>
+    <row r="39" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A39" s="30"/>
+      <c r="B39" s="15"/>
+      <c r="C39" s="15"/>
+      <c r="D39" s="15"/>
+      <c r="E39" s="16"/>
+      <c r="F39" s="15"/>
+    </row>
+    <row r="40" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A40" s="30"/>
+      <c r="B40" s="9"/>
+      <c r="C40" s="9"/>
+      <c r="D40" s="9"/>
+      <c r="E40" s="12"/>
+      <c r="F40" s="9"/>
+    </row>
+    <row r="41" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A41" s="30"/>
+      <c r="B41" s="28"/>
+      <c r="C41" s="28"/>
+      <c r="D41" s="28"/>
+      <c r="E41" s="28"/>
+      <c r="F41" s="28"/>
+    </row>
+    <row r="42" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A42" s="28" t="s">
+        <v>79</v>
+      </c>
+      <c r="B42" s="15"/>
+      <c r="C42" s="15"/>
+      <c r="D42" s="15"/>
+      <c r="E42" s="16"/>
+      <c r="F42" s="15"/>
+    </row>
+    <row r="43" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="44" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="45" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="46" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="47" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="48" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="49" ht="30" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="50" ht="30" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="51" ht="30" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="52" ht="30" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="53" ht="30" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="54" ht="30" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="55" ht="30" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="56" ht="30" customHeight="1" x14ac:dyDescent="0.15"/>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="A36:A41"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="B5:F6"/>
+    <mergeCell ref="A9:A12"/>
+    <mergeCell ref="A1:G3"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="A13:A16"/>
+    <mergeCell ref="A17:A19"/>
+    <mergeCell ref="A20:A24"/>
+    <mergeCell ref="A25:A35"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:R62"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="31" t="s">
         <v>126</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
-      <c r="H1" s="28"/>
-      <c r="I1" s="28"/>
-      <c r="J1" s="28"/>
-      <c r="K1" s="28"/>
-      <c r="L1" s="28"/>
-      <c r="M1" s="28"/>
-      <c r="N1" s="28"/>
-      <c r="O1" s="28"/>
-      <c r="P1" s="28"/>
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
+      <c r="E1" s="29"/>
+      <c r="F1" s="29"/>
+      <c r="G1" s="29"/>
+      <c r="H1" s="29"/>
+      <c r="I1" s="29"/>
+      <c r="J1" s="29"/>
+      <c r="K1" s="29"/>
+      <c r="L1" s="29"/>
+      <c r="M1" s="29"/>
+      <c r="N1" s="29"/>
+      <c r="O1" s="29"/>
+      <c r="P1" s="29"/>
       <c r="Q1" s="23"/>
       <c r="R1" s="23"/>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="A2" s="28"/>
-      <c r="B2" s="28"/>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
-      <c r="F2" s="28"/>
-      <c r="G2" s="28"/>
-      <c r="H2" s="28"/>
-      <c r="I2" s="28"/>
-      <c r="J2" s="28"/>
-      <c r="K2" s="28"/>
-      <c r="L2" s="28"/>
-      <c r="M2" s="28"/>
-      <c r="N2" s="28"/>
-      <c r="O2" s="28"/>
-      <c r="P2" s="28"/>
+      <c r="A2" s="29"/>
+      <c r="B2" s="29"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="29"/>
+      <c r="F2" s="29"/>
+      <c r="G2" s="29"/>
+      <c r="H2" s="29"/>
+      <c r="I2" s="29"/>
+      <c r="J2" s="29"/>
+      <c r="K2" s="29"/>
+      <c r="L2" s="29"/>
+      <c r="M2" s="29"/>
+      <c r="N2" s="29"/>
+      <c r="O2" s="29"/>
+      <c r="P2" s="29"/>
       <c r="Q2" s="23"/>
       <c r="R2" s="23"/>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="A3" s="28"/>
-      <c r="B3" s="28"/>
-      <c r="C3" s="28"/>
-      <c r="D3" s="28"/>
-      <c r="E3" s="28"/>
-      <c r="F3" s="28"/>
-      <c r="G3" s="28"/>
-      <c r="H3" s="28"/>
-      <c r="I3" s="28"/>
-      <c r="J3" s="28"/>
-      <c r="K3" s="28"/>
-      <c r="L3" s="28"/>
-      <c r="M3" s="28"/>
-      <c r="N3" s="28"/>
-      <c r="O3" s="28"/>
-      <c r="P3" s="28"/>
+      <c r="A3" s="29"/>
+      <c r="B3" s="29"/>
+      <c r="C3" s="29"/>
+      <c r="D3" s="29"/>
+      <c r="E3" s="29"/>
+      <c r="F3" s="29"/>
+      <c r="G3" s="29"/>
+      <c r="H3" s="29"/>
+      <c r="I3" s="29"/>
+      <c r="J3" s="29"/>
+      <c r="K3" s="29"/>
+      <c r="L3" s="29"/>
+      <c r="M3" s="29"/>
+      <c r="N3" s="29"/>
+      <c r="O3" s="29"/>
+      <c r="P3" s="29"/>
       <c r="Q3" s="23"/>
       <c r="R3" s="23"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="A4" s="28" t="s">
+      <c r="A4" s="29" t="s">
         <v>118</v>
       </c>
-      <c r="B4" s="28"/>
-      <c r="C4" s="28" t="s">
+      <c r="B4" s="29"/>
+      <c r="C4" s="29" t="s">
         <v>120</v>
       </c>
-      <c r="D4" s="28"/>
-      <c r="E4" s="28"/>
-      <c r="F4" s="28"/>
-      <c r="G4" s="28"/>
-      <c r="H4" s="28"/>
-      <c r="I4" s="28"/>
-      <c r="J4" s="28"/>
-      <c r="K4" s="28"/>
-      <c r="L4" s="28"/>
-      <c r="M4" s="28"/>
-      <c r="N4" s="28"/>
-      <c r="O4" s="28"/>
-      <c r="P4" s="28"/>
+      <c r="D4" s="29"/>
+      <c r="E4" s="29"/>
+      <c r="F4" s="29"/>
+      <c r="G4" s="29"/>
+      <c r="H4" s="29"/>
+      <c r="I4" s="29"/>
+      <c r="J4" s="29"/>
+      <c r="K4" s="29"/>
+      <c r="L4" s="29"/>
+      <c r="M4" s="29"/>
+      <c r="N4" s="29"/>
+      <c r="O4" s="29"/>
+      <c r="P4" s="29"/>
       <c r="Q4" s="23"/>
       <c r="R4" s="23"/>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="A5" s="28"/>
-      <c r="B5" s="28"/>
-      <c r="C5" s="28"/>
-      <c r="D5" s="28"/>
-      <c r="E5" s="28"/>
-      <c r="F5" s="28"/>
-      <c r="G5" s="28"/>
-      <c r="H5" s="28"/>
-      <c r="I5" s="28"/>
-      <c r="J5" s="28"/>
-      <c r="K5" s="28"/>
-      <c r="L5" s="28"/>
-      <c r="M5" s="28"/>
-      <c r="N5" s="28"/>
-      <c r="O5" s="28"/>
-      <c r="P5" s="28"/>
+      <c r="A5" s="29"/>
+      <c r="B5" s="29"/>
+      <c r="C5" s="29"/>
+      <c r="D5" s="29"/>
+      <c r="E5" s="29"/>
+      <c r="F5" s="29"/>
+      <c r="G5" s="29"/>
+      <c r="H5" s="29"/>
+      <c r="I5" s="29"/>
+      <c r="J5" s="29"/>
+      <c r="K5" s="29"/>
+      <c r="L5" s="29"/>
+      <c r="M5" s="29"/>
+      <c r="N5" s="29"/>
+      <c r="O5" s="29"/>
+      <c r="P5" s="29"/>
       <c r="Q5" s="23"/>
       <c r="R5" s="23"/>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="A6" s="28" t="s">
+      <c r="A6" s="29" t="s">
         <v>119</v>
       </c>
-      <c r="B6" s="28"/>
-      <c r="C6" s="28" t="s">
+      <c r="B6" s="29"/>
+      <c r="C6" s="29" t="s">
         <v>121</v>
       </c>
-      <c r="D6" s="28"/>
-      <c r="E6" s="28"/>
-      <c r="F6" s="28"/>
-      <c r="G6" s="28"/>
-      <c r="H6" s="28"/>
-      <c r="I6" s="28"/>
-      <c r="J6" s="28"/>
-      <c r="K6" s="28"/>
-      <c r="L6" s="28"/>
-      <c r="M6" s="28"/>
-      <c r="N6" s="28"/>
-      <c r="O6" s="28"/>
-      <c r="P6" s="28"/>
+      <c r="D6" s="29"/>
+      <c r="E6" s="29"/>
+      <c r="F6" s="29"/>
+      <c r="G6" s="29"/>
+      <c r="H6" s="29"/>
+      <c r="I6" s="29"/>
+      <c r="J6" s="29"/>
+      <c r="K6" s="29"/>
+      <c r="L6" s="29"/>
+      <c r="M6" s="29"/>
+      <c r="N6" s="29"/>
+      <c r="O6" s="29"/>
+      <c r="P6" s="29"/>
       <c r="Q6" s="23"/>
       <c r="R6" s="23"/>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="A7" s="28"/>
-      <c r="B7" s="28"/>
-      <c r="C7" s="28"/>
-      <c r="D7" s="28"/>
-      <c r="E7" s="28"/>
-      <c r="F7" s="28"/>
-      <c r="G7" s="28"/>
-      <c r="H7" s="28"/>
-      <c r="I7" s="28"/>
-      <c r="J7" s="28"/>
-      <c r="K7" s="28"/>
-      <c r="L7" s="28"/>
-      <c r="M7" s="28"/>
-      <c r="N7" s="28"/>
-      <c r="O7" s="28"/>
-      <c r="P7" s="28"/>
+      <c r="A7" s="29"/>
+      <c r="B7" s="29"/>
+      <c r="C7" s="29"/>
+      <c r="D7" s="29"/>
+      <c r="E7" s="29"/>
+      <c r="F7" s="29"/>
+      <c r="G7" s="29"/>
+      <c r="H7" s="29"/>
+      <c r="I7" s="29"/>
+      <c r="J7" s="29"/>
+      <c r="K7" s="29"/>
+      <c r="L7" s="29"/>
+      <c r="M7" s="29"/>
+      <c r="N7" s="29"/>
+      <c r="O7" s="29"/>
+      <c r="P7" s="29"/>
       <c r="Q7" s="23"/>
       <c r="R7" s="23"/>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="A8" s="28"/>
-      <c r="B8" s="28"/>
-      <c r="C8" s="28"/>
-      <c r="D8" s="28"/>
-      <c r="E8" s="28"/>
-      <c r="F8" s="28"/>
-      <c r="G8" s="28"/>
-      <c r="H8" s="28"/>
-      <c r="I8" s="28"/>
-      <c r="J8" s="28"/>
-      <c r="K8" s="28"/>
-      <c r="L8" s="28"/>
-      <c r="M8" s="28"/>
-      <c r="N8" s="28"/>
-      <c r="O8" s="28"/>
-      <c r="P8" s="28"/>
+      <c r="A8" s="29"/>
+      <c r="B8" s="29"/>
+      <c r="C8" s="29"/>
+      <c r="D8" s="29"/>
+      <c r="E8" s="29"/>
+      <c r="F8" s="29"/>
+      <c r="G8" s="29"/>
+      <c r="H8" s="29"/>
+      <c r="I8" s="29"/>
+      <c r="J8" s="29"/>
+      <c r="K8" s="29"/>
+      <c r="L8" s="29"/>
+      <c r="M8" s="29"/>
+      <c r="N8" s="29"/>
+      <c r="O8" s="29"/>
+      <c r="P8" s="29"/>
       <c r="Q8" s="23"/>
       <c r="R8" s="23"/>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="A9" s="28"/>
-      <c r="B9" s="28"/>
-      <c r="C9" s="28"/>
-      <c r="D9" s="28"/>
-      <c r="E9" s="28"/>
-      <c r="F9" s="28"/>
-      <c r="G9" s="28"/>
-      <c r="H9" s="28"/>
-      <c r="I9" s="28"/>
-      <c r="J9" s="28"/>
-      <c r="K9" s="28"/>
-      <c r="L9" s="28"/>
-      <c r="M9" s="28"/>
-      <c r="N9" s="28"/>
-      <c r="O9" s="28"/>
-      <c r="P9" s="28"/>
+      <c r="A9" s="29"/>
+      <c r="B9" s="29"/>
+      <c r="C9" s="29"/>
+      <c r="D9" s="29"/>
+      <c r="E9" s="29"/>
+      <c r="F9" s="29"/>
+      <c r="G9" s="29"/>
+      <c r="H9" s="29"/>
+      <c r="I9" s="29"/>
+      <c r="J9" s="29"/>
+      <c r="K9" s="29"/>
+      <c r="L9" s="29"/>
+      <c r="M9" s="29"/>
+      <c r="N9" s="29"/>
+      <c r="O9" s="29"/>
+      <c r="P9" s="29"/>
       <c r="Q9" s="23"/>
       <c r="R9" s="23"/>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="A10" s="28"/>
-      <c r="B10" s="28"/>
-      <c r="C10" s="28"/>
-      <c r="D10" s="28"/>
-      <c r="E10" s="28"/>
-      <c r="F10" s="28"/>
-      <c r="G10" s="28"/>
-      <c r="H10" s="28"/>
-      <c r="I10" s="28"/>
-      <c r="J10" s="28"/>
-      <c r="K10" s="28"/>
-      <c r="L10" s="28"/>
-      <c r="M10" s="28"/>
-      <c r="N10" s="28"/>
-      <c r="O10" s="28"/>
-      <c r="P10" s="28"/>
+      <c r="A10" s="29"/>
+      <c r="B10" s="29"/>
+      <c r="C10" s="29"/>
+      <c r="D10" s="29"/>
+      <c r="E10" s="29"/>
+      <c r="F10" s="29"/>
+      <c r="G10" s="29"/>
+      <c r="H10" s="29"/>
+      <c r="I10" s="29"/>
+      <c r="J10" s="29"/>
+      <c r="K10" s="29"/>
+      <c r="L10" s="29"/>
+      <c r="M10" s="29"/>
+      <c r="N10" s="29"/>
+      <c r="O10" s="29"/>
+      <c r="P10" s="29"/>
       <c r="Q10" s="23"/>
       <c r="R10" s="23"/>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="A11" s="28"/>
-      <c r="B11" s="28"/>
-      <c r="C11" s="28"/>
-      <c r="D11" s="28"/>
-      <c r="E11" s="28"/>
-      <c r="F11" s="28"/>
-      <c r="G11" s="28"/>
-      <c r="H11" s="28"/>
-      <c r="I11" s="28"/>
-      <c r="J11" s="28"/>
-      <c r="K11" s="28"/>
-      <c r="L11" s="28"/>
-      <c r="M11" s="28"/>
-      <c r="N11" s="28"/>
-      <c r="O11" s="28"/>
-      <c r="P11" s="28"/>
+      <c r="A11" s="29"/>
+      <c r="B11" s="29"/>
+      <c r="C11" s="29"/>
+      <c r="D11" s="29"/>
+      <c r="E11" s="29"/>
+      <c r="F11" s="29"/>
+      <c r="G11" s="29"/>
+      <c r="H11" s="29"/>
+      <c r="I11" s="29"/>
+      <c r="J11" s="29"/>
+      <c r="K11" s="29"/>
+      <c r="L11" s="29"/>
+      <c r="M11" s="29"/>
+      <c r="N11" s="29"/>
+      <c r="O11" s="29"/>
+      <c r="P11" s="29"/>
       <c r="Q11" s="23"/>
       <c r="R11" s="23"/>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="A12" s="28"/>
-      <c r="B12" s="28"/>
-      <c r="C12" s="28"/>
-      <c r="D12" s="28"/>
-      <c r="E12" s="28"/>
-      <c r="F12" s="28"/>
-      <c r="G12" s="28"/>
-      <c r="H12" s="28"/>
-      <c r="I12" s="28"/>
-      <c r="J12" s="28"/>
-      <c r="K12" s="28"/>
-      <c r="L12" s="28"/>
-      <c r="M12" s="28"/>
-      <c r="N12" s="28"/>
-      <c r="O12" s="28"/>
-      <c r="P12" s="28"/>
+      <c r="A12" s="29"/>
+      <c r="B12" s="29"/>
+      <c r="C12" s="29"/>
+      <c r="D12" s="29"/>
+      <c r="E12" s="29"/>
+      <c r="F12" s="29"/>
+      <c r="G12" s="29"/>
+      <c r="H12" s="29"/>
+      <c r="I12" s="29"/>
+      <c r="J12" s="29"/>
+      <c r="K12" s="29"/>
+      <c r="L12" s="29"/>
+      <c r="M12" s="29"/>
+      <c r="N12" s="29"/>
+      <c r="O12" s="29"/>
+      <c r="P12" s="29"/>
       <c r="Q12" s="23"/>
       <c r="R12" s="23"/>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="A13" s="28"/>
-      <c r="B13" s="28"/>
-      <c r="C13" s="28"/>
-      <c r="D13" s="28"/>
-      <c r="E13" s="28"/>
-      <c r="F13" s="28"/>
-      <c r="G13" s="28"/>
-      <c r="H13" s="28"/>
-      <c r="I13" s="28"/>
-      <c r="J13" s="28"/>
-      <c r="K13" s="28"/>
-      <c r="L13" s="28"/>
-      <c r="M13" s="28"/>
-      <c r="N13" s="28"/>
-      <c r="O13" s="28"/>
-      <c r="P13" s="28"/>
+      <c r="A13" s="29"/>
+      <c r="B13" s="29"/>
+      <c r="C13" s="29"/>
+      <c r="D13" s="29"/>
+      <c r="E13" s="29"/>
+      <c r="F13" s="29"/>
+      <c r="G13" s="29"/>
+      <c r="H13" s="29"/>
+      <c r="I13" s="29"/>
+      <c r="J13" s="29"/>
+      <c r="K13" s="29"/>
+      <c r="L13" s="29"/>
+      <c r="M13" s="29"/>
+      <c r="N13" s="29"/>
+      <c r="O13" s="29"/>
+      <c r="P13" s="29"/>
       <c r="Q13" s="23"/>
       <c r="R13" s="23"/>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="A14" s="28"/>
-      <c r="B14" s="28"/>
-      <c r="C14" s="28"/>
-      <c r="D14" s="28"/>
-      <c r="E14" s="28"/>
-      <c r="F14" s="28"/>
-      <c r="G14" s="28"/>
-      <c r="H14" s="28"/>
-      <c r="I14" s="28"/>
-      <c r="J14" s="28"/>
-      <c r="K14" s="28"/>
-      <c r="L14" s="28"/>
-      <c r="M14" s="28"/>
-      <c r="N14" s="28"/>
-      <c r="O14" s="28"/>
-      <c r="P14" s="28"/>
+      <c r="A14" s="29"/>
+      <c r="B14" s="29"/>
+      <c r="C14" s="29"/>
+      <c r="D14" s="29"/>
+      <c r="E14" s="29"/>
+      <c r="F14" s="29"/>
+      <c r="G14" s="29"/>
+      <c r="H14" s="29"/>
+      <c r="I14" s="29"/>
+      <c r="J14" s="29"/>
+      <c r="K14" s="29"/>
+      <c r="L14" s="29"/>
+      <c r="M14" s="29"/>
+      <c r="N14" s="29"/>
+      <c r="O14" s="29"/>
+      <c r="P14" s="29"/>
       <c r="Q14" s="23"/>
       <c r="R14" s="23"/>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="A15" s="28"/>
-      <c r="B15" s="28"/>
-      <c r="C15" s="28"/>
-      <c r="D15" s="28"/>
-      <c r="E15" s="28"/>
-      <c r="F15" s="28"/>
-      <c r="G15" s="28"/>
-      <c r="H15" s="28"/>
-      <c r="I15" s="28"/>
-      <c r="J15" s="28"/>
-      <c r="K15" s="28"/>
-      <c r="L15" s="28"/>
-      <c r="M15" s="28"/>
-      <c r="N15" s="28"/>
-      <c r="O15" s="28"/>
-      <c r="P15" s="28"/>
+      <c r="A15" s="29"/>
+      <c r="B15" s="29"/>
+      <c r="C15" s="29"/>
+      <c r="D15" s="29"/>
+      <c r="E15" s="29"/>
+      <c r="F15" s="29"/>
+      <c r="G15" s="29"/>
+      <c r="H15" s="29"/>
+      <c r="I15" s="29"/>
+      <c r="J15" s="29"/>
+      <c r="K15" s="29"/>
+      <c r="L15" s="29"/>
+      <c r="M15" s="29"/>
+      <c r="N15" s="29"/>
+      <c r="O15" s="29"/>
+      <c r="P15" s="29"/>
       <c r="Q15" s="23"/>
       <c r="R15" s="23"/>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="A16" s="28"/>
-      <c r="B16" s="28"/>
+      <c r="A16" s="29"/>
+      <c r="B16" s="29"/>
       <c r="C16" s="23"/>
       <c r="D16" s="23"/>
       <c r="E16" s="23"/>
@@ -2735,8 +3450,8 @@
       <c r="R16" s="23"/>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="A17" s="28"/>
-      <c r="B17" s="28"/>
+      <c r="A17" s="29"/>
+      <c r="B17" s="29"/>
       <c r="C17" s="23"/>
       <c r="D17" s="23"/>
       <c r="E17" s="23"/>
@@ -2755,8 +3470,8 @@
       <c r="R17" s="23"/>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="A18" s="28"/>
-      <c r="B18" s="28"/>
+      <c r="A18" s="29"/>
+      <c r="B18" s="29"/>
       <c r="C18" s="23"/>
       <c r="D18" s="23"/>
       <c r="E18" s="23"/>
@@ -2775,8 +3490,8 @@
       <c r="R18" s="23"/>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="A19" s="28"/>
-      <c r="B19" s="28"/>
+      <c r="A19" s="29"/>
+      <c r="B19" s="29"/>
       <c r="C19" s="23"/>
       <c r="D19" s="23"/>
       <c r="E19" s="23"/>
@@ -2795,8 +3510,8 @@
       <c r="R19" s="23"/>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="A20" s="28"/>
-      <c r="B20" s="28"/>
+      <c r="A20" s="29"/>
+      <c r="B20" s="29"/>
       <c r="C20" s="23"/>
       <c r="D20" s="23"/>
       <c r="E20" s="23"/>
@@ -3670,401 +4385,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:P20"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
-  <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A1" s="30" t="s">
-        <v>127</v>
-      </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
-      <c r="H1" s="28"/>
-      <c r="I1" s="28"/>
-      <c r="J1" s="28"/>
-      <c r="K1" s="28"/>
-      <c r="L1" s="28"/>
-      <c r="M1" s="28"/>
-      <c r="N1" s="28"/>
-      <c r="O1" s="28"/>
-      <c r="P1" s="28"/>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A2" s="28"/>
-      <c r="B2" s="28"/>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
-      <c r="F2" s="28"/>
-      <c r="G2" s="28"/>
-      <c r="H2" s="28"/>
-      <c r="I2" s="28"/>
-      <c r="J2" s="28"/>
-      <c r="K2" s="28"/>
-      <c r="L2" s="28"/>
-      <c r="M2" s="28"/>
-      <c r="N2" s="28"/>
-      <c r="O2" s="28"/>
-      <c r="P2" s="28"/>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A3" s="28"/>
-      <c r="B3" s="28"/>
-      <c r="C3" s="28"/>
-      <c r="D3" s="28"/>
-      <c r="E3" s="28"/>
-      <c r="F3" s="28"/>
-      <c r="G3" s="28"/>
-      <c r="H3" s="28"/>
-      <c r="I3" s="28"/>
-      <c r="J3" s="28"/>
-      <c r="K3" s="28"/>
-      <c r="L3" s="28"/>
-      <c r="M3" s="28"/>
-      <c r="N3" s="28"/>
-      <c r="O3" s="28"/>
-      <c r="P3" s="28"/>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A4" s="28" t="s">
-        <v>118</v>
-      </c>
-      <c r="B4" s="28"/>
-      <c r="C4" s="29" t="s">
-        <v>131</v>
-      </c>
-      <c r="D4" s="28"/>
-      <c r="E4" s="28"/>
-      <c r="F4" s="28"/>
-      <c r="G4" s="28"/>
-      <c r="H4" s="28"/>
-      <c r="I4" s="28"/>
-      <c r="J4" s="28"/>
-      <c r="K4" s="28"/>
-      <c r="L4" s="28"/>
-      <c r="M4" s="28"/>
-      <c r="N4" s="28"/>
-      <c r="O4" s="28"/>
-      <c r="P4" s="28"/>
-    </row>
-    <row r="5" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="28"/>
-      <c r="B5" s="28"/>
-      <c r="C5" s="28"/>
-      <c r="D5" s="28"/>
-      <c r="E5" s="28"/>
-      <c r="F5" s="28"/>
-      <c r="G5" s="28"/>
-      <c r="H5" s="28"/>
-      <c r="I5" s="28"/>
-      <c r="J5" s="28"/>
-      <c r="K5" s="28"/>
-      <c r="L5" s="28"/>
-      <c r="M5" s="28"/>
-      <c r="N5" s="28"/>
-      <c r="O5" s="28"/>
-      <c r="P5" s="28"/>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A6" s="28" t="s">
-        <v>119</v>
-      </c>
-      <c r="B6" s="28"/>
-      <c r="C6" s="29" t="s">
-        <v>130</v>
-      </c>
-      <c r="D6" s="28"/>
-      <c r="E6" s="28"/>
-      <c r="F6" s="28"/>
-      <c r="G6" s="28"/>
-      <c r="H6" s="28"/>
-      <c r="I6" s="28"/>
-      <c r="J6" s="28"/>
-      <c r="K6" s="28"/>
-      <c r="L6" s="28"/>
-      <c r="M6" s="28"/>
-      <c r="N6" s="28"/>
-      <c r="O6" s="28"/>
-      <c r="P6" s="28"/>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A7" s="28"/>
-      <c r="B7" s="28"/>
-      <c r="C7" s="28"/>
-      <c r="D7" s="28"/>
-      <c r="E7" s="28"/>
-      <c r="F7" s="28"/>
-      <c r="G7" s="28"/>
-      <c r="H7" s="28"/>
-      <c r="I7" s="28"/>
-      <c r="J7" s="28"/>
-      <c r="K7" s="28"/>
-      <c r="L7" s="28"/>
-      <c r="M7" s="28"/>
-      <c r="N7" s="28"/>
-      <c r="O7" s="28"/>
-      <c r="P7" s="28"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A8" s="28"/>
-      <c r="B8" s="28"/>
-      <c r="C8" s="28" t="s">
-        <v>128</v>
-      </c>
-      <c r="D8" s="28"/>
-      <c r="E8" s="28"/>
-      <c r="F8" s="28"/>
-      <c r="G8" s="28"/>
-      <c r="H8" s="28"/>
-      <c r="I8" s="28"/>
-      <c r="J8" s="28"/>
-      <c r="K8" s="28"/>
-      <c r="L8" s="28"/>
-      <c r="M8" s="28"/>
-      <c r="N8" s="28"/>
-      <c r="O8" s="28"/>
-      <c r="P8" s="28"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A9" s="28"/>
-      <c r="B9" s="28"/>
-      <c r="C9" s="28"/>
-      <c r="D9" s="28"/>
-      <c r="E9" s="28"/>
-      <c r="F9" s="28"/>
-      <c r="G9" s="28"/>
-      <c r="H9" s="28"/>
-      <c r="I9" s="28"/>
-      <c r="J9" s="28"/>
-      <c r="K9" s="28"/>
-      <c r="L9" s="28"/>
-      <c r="M9" s="28"/>
-      <c r="N9" s="28"/>
-      <c r="O9" s="28"/>
-      <c r="P9" s="28"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A10" s="28"/>
-      <c r="B10" s="28"/>
-      <c r="C10" s="28" t="s">
-        <v>129</v>
-      </c>
-      <c r="D10" s="28"/>
-      <c r="E10" s="28"/>
-      <c r="F10" s="28"/>
-      <c r="G10" s="28"/>
-      <c r="H10" s="28"/>
-      <c r="I10" s="28"/>
-      <c r="J10" s="28"/>
-      <c r="K10" s="28"/>
-      <c r="L10" s="28"/>
-      <c r="M10" s="28"/>
-      <c r="N10" s="28"/>
-      <c r="O10" s="28"/>
-      <c r="P10" s="28"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A11" s="28"/>
-      <c r="B11" s="28"/>
-      <c r="C11" s="28"/>
-      <c r="D11" s="28"/>
-      <c r="E11" s="28"/>
-      <c r="F11" s="28"/>
-      <c r="G11" s="28"/>
-      <c r="H11" s="28"/>
-      <c r="I11" s="28"/>
-      <c r="J11" s="28"/>
-      <c r="K11" s="28"/>
-      <c r="L11" s="28"/>
-      <c r="M11" s="28"/>
-      <c r="N11" s="28"/>
-      <c r="O11" s="28"/>
-      <c r="P11" s="28"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A12" s="28"/>
-      <c r="B12" s="28"/>
-      <c r="C12" s="28"/>
-      <c r="D12" s="28"/>
-      <c r="E12" s="28"/>
-      <c r="F12" s="28"/>
-      <c r="G12" s="28"/>
-      <c r="H12" s="28"/>
-      <c r="I12" s="28"/>
-      <c r="J12" s="28"/>
-      <c r="K12" s="28"/>
-      <c r="L12" s="28"/>
-      <c r="M12" s="28"/>
-      <c r="N12" s="28"/>
-      <c r="O12" s="28"/>
-      <c r="P12" s="28"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A13" s="28"/>
-      <c r="B13" s="28"/>
-      <c r="C13" s="28"/>
-      <c r="D13" s="28"/>
-      <c r="E13" s="28"/>
-      <c r="F13" s="28"/>
-      <c r="G13" s="28"/>
-      <c r="H13" s="28"/>
-      <c r="I13" s="28"/>
-      <c r="J13" s="28"/>
-      <c r="K13" s="28"/>
-      <c r="L13" s="28"/>
-      <c r="M13" s="28"/>
-      <c r="N13" s="28"/>
-      <c r="O13" s="28"/>
-      <c r="P13" s="28"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A14" s="28"/>
-      <c r="B14" s="28"/>
-      <c r="C14" s="28"/>
-      <c r="D14" s="28"/>
-      <c r="E14" s="28"/>
-      <c r="F14" s="28"/>
-      <c r="G14" s="28"/>
-      <c r="H14" s="28"/>
-      <c r="I14" s="28"/>
-      <c r="J14" s="28"/>
-      <c r="K14" s="28"/>
-      <c r="L14" s="28"/>
-      <c r="M14" s="28"/>
-      <c r="N14" s="28"/>
-      <c r="O14" s="28"/>
-      <c r="P14" s="28"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A15" s="28"/>
-      <c r="B15" s="28"/>
-      <c r="C15" s="28"/>
-      <c r="D15" s="28"/>
-      <c r="E15" s="28"/>
-      <c r="F15" s="28"/>
-      <c r="G15" s="28"/>
-      <c r="H15" s="28"/>
-      <c r="I15" s="28"/>
-      <c r="J15" s="28"/>
-      <c r="K15" s="28"/>
-      <c r="L15" s="28"/>
-      <c r="M15" s="28"/>
-      <c r="N15" s="28"/>
-      <c r="O15" s="28"/>
-      <c r="P15" s="28"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A16" s="28"/>
-      <c r="B16" s="28"/>
-      <c r="C16" s="25"/>
-      <c r="D16" s="25"/>
-      <c r="E16" s="25"/>
-      <c r="F16" s="25"/>
-      <c r="G16" s="25"/>
-      <c r="H16" s="25"/>
-      <c r="I16" s="25"/>
-      <c r="J16" s="25"/>
-      <c r="K16" s="25"/>
-      <c r="L16" s="25"/>
-      <c r="M16" s="25"/>
-      <c r="N16" s="25"/>
-      <c r="O16" s="25"/>
-      <c r="P16" s="25"/>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A17" s="28"/>
-      <c r="B17" s="28"/>
-      <c r="C17" s="25"/>
-      <c r="D17" s="25"/>
-      <c r="E17" s="25"/>
-      <c r="F17" s="25"/>
-      <c r="G17" s="25"/>
-      <c r="H17" s="25"/>
-      <c r="I17" s="25"/>
-      <c r="J17" s="25"/>
-      <c r="K17" s="25"/>
-      <c r="L17" s="25"/>
-      <c r="M17" s="25"/>
-      <c r="N17" s="25"/>
-      <c r="O17" s="25"/>
-      <c r="P17" s="25"/>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A18" s="28"/>
-      <c r="B18" s="28"/>
-      <c r="C18" s="25"/>
-      <c r="D18" s="25"/>
-      <c r="E18" s="25"/>
-      <c r="F18" s="25"/>
-      <c r="G18" s="25"/>
-      <c r="H18" s="25"/>
-      <c r="I18" s="25"/>
-      <c r="J18" s="25"/>
-      <c r="K18" s="25"/>
-      <c r="L18" s="25"/>
-      <c r="M18" s="25"/>
-      <c r="N18" s="25"/>
-      <c r="O18" s="25"/>
-      <c r="P18" s="25"/>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A19" s="28"/>
-      <c r="B19" s="28"/>
-      <c r="C19" s="25"/>
-      <c r="D19" s="25"/>
-      <c r="E19" s="25"/>
-      <c r="F19" s="25"/>
-      <c r="G19" s="25"/>
-      <c r="H19" s="25"/>
-      <c r="I19" s="25"/>
-      <c r="J19" s="25"/>
-      <c r="K19" s="25"/>
-      <c r="L19" s="25"/>
-      <c r="M19" s="25"/>
-      <c r="N19" s="25"/>
-      <c r="O19" s="25"/>
-      <c r="P19" s="25"/>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A20" s="28"/>
-      <c r="B20" s="28"/>
-      <c r="C20" s="25"/>
-      <c r="D20" s="25"/>
-      <c r="E20" s="25"/>
-      <c r="F20" s="25"/>
-      <c r="G20" s="25"/>
-      <c r="H20" s="25"/>
-      <c r="I20" s="25"/>
-      <c r="J20" s="25"/>
-      <c r="K20" s="25"/>
-      <c r="L20" s="25"/>
-      <c r="M20" s="25"/>
-      <c r="N20" s="25"/>
-      <c r="O20" s="25"/>
-      <c r="P20" s="25"/>
-    </row>
-  </sheetData>
-  <mergeCells count="9">
-    <mergeCell ref="A1:P3"/>
-    <mergeCell ref="A4:B5"/>
-    <mergeCell ref="C4:P5"/>
-    <mergeCell ref="A6:B20"/>
-    <mergeCell ref="C6:P7"/>
-    <mergeCell ref="C8:P9"/>
-    <mergeCell ref="C10:P11"/>
-    <mergeCell ref="C12:P13"/>
-    <mergeCell ref="C14:P15"/>
-  </mergeCells>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
 </file>